--- a/artfynd/A 19253-2026 artfynd.xlsx
+++ b/artfynd/A 19253-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ69"/>
+  <dimension ref="A1:AZ108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1526,32 +1526,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128953987</v>
+        <v>136824805</v>
       </c>
       <c r="B10" t="n">
-        <v>96554</v>
+        <v>97588</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>210</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,13 +1561,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668638</v>
+        <v>668745</v>
       </c>
       <c r="R10" t="n">
-        <v>6691674</v>
+        <v>6691868</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1591,17 +1591,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Mycket örtrikt</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1610,28 +1605,22 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
-      </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1648,51 +1637,51 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128953987</t>
+          <t>https://artportalen.se/Sighting/136824805</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128344137</v>
+        <v>136824806</v>
       </c>
       <c r="B11" t="n">
-        <v>93199</v>
+        <v>97588</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>788</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668567</v>
+        <v>668748</v>
       </c>
       <c r="R11" t="n">
-        <v>6691956</v>
+        <v>6691907</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1719,12 +1708,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1739,27 +1728,27 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128344137</t>
+          <t>https://artportalen.se/Sighting/136824806</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128344122</v>
+        <v>136824807</v>
       </c>
       <c r="B12" t="n">
-        <v>91909</v>
+        <v>97588</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1767,34 +1756,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>668359</v>
+        <v>668760</v>
       </c>
       <c r="R12" t="n">
-        <v>6691742</v>
+        <v>6691900</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1821,17 +1810,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1846,49 +1830,49 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128344122</t>
+          <t>https://artportalen.se/Sighting/136824807</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128953971</v>
+        <v>128953987</v>
       </c>
       <c r="B13" t="n">
-        <v>91909</v>
+        <v>96554</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>210</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1898,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>668680</v>
+        <v>668638</v>
       </c>
       <c r="R13" t="n">
-        <v>6691646</v>
+        <v>6691674</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1936,14 +1920,25 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Mycket örtrikt</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -1974,54 +1969,54 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128953971</t>
+          <t>https://artportalen.se/Sighting/128953987</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128953993</v>
+        <v>128344137</v>
       </c>
       <c r="B14" t="n">
-        <v>92564</v>
+        <v>93199</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1339</v>
+        <v>788</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>668664</v>
+        <v>668567</v>
       </c>
       <c r="R14" t="n">
-        <v>6691742</v>
+        <v>6691956</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2045,12 +2040,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2061,84 +2056,69 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128953993</t>
+          <t>https://artportalen.se/Sighting/128344137</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128953972</v>
+        <v>128344122</v>
       </c>
       <c r="B15" t="n">
-        <v>96458</v>
+        <v>91909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2818</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>668638</v>
+        <v>668359</v>
       </c>
       <c r="R15" t="n">
-        <v>6691675</v>
+        <v>6691742</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2162,12 +2142,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2178,84 +2163,69 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128953972</t>
+          <t>https://artportalen.se/Sighting/128344122</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128344130</v>
+        <v>128953971</v>
       </c>
       <c r="B16" t="n">
-        <v>91680</v>
+        <v>91909</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3215</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>668494</v>
+        <v>668680</v>
       </c>
       <c r="R16" t="n">
-        <v>6691650</v>
+        <v>6691646</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2279,12 +2249,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2295,66 +2265,81 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128344130</t>
+          <t>https://artportalen.se/Sighting/128953971</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128344131</v>
+        <v>136824809</v>
       </c>
       <c r="B17" t="n">
-        <v>91680</v>
+        <v>92111</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3215</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>668602</v>
+        <v>668343</v>
       </c>
       <c r="R17" t="n">
-        <v>6691678</v>
+        <v>6691845</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2381,12 +2366,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På bark som hänger från lågan.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2397,31 +2387,46 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128344131</t>
+          <t>https://artportalen.se/Sighting/136824809</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128344132</v>
+        <v>128953993</v>
       </c>
       <c r="B18" t="n">
-        <v>91680</v>
+        <v>92564</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2429,37 +2434,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3215</v>
+        <v>1339</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>668568</v>
+        <v>668664</v>
       </c>
       <c r="R18" t="n">
-        <v>6691712</v>
+        <v>6691742</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2483,12 +2488,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2499,66 +2504,81 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128344132</t>
+          <t>https://artportalen.se/Sighting/128953993</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128344133</v>
+        <v>136824836</v>
       </c>
       <c r="B19" t="n">
-        <v>91680</v>
+        <v>92464</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3215</v>
+        <v>1506</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>668580</v>
+        <v>668657</v>
       </c>
       <c r="R19" t="n">
-        <v>6691920</v>
+        <v>6691706</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2585,12 +2605,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2605,27 +2625,27 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128344133</t>
+          <t>https://artportalen.se/Sighting/136824836</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128953979</v>
+        <v>136824831</v>
       </c>
       <c r="B20" t="n">
-        <v>91680</v>
+        <v>96563</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2633,21 +2653,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3215</v>
+        <v>2812</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2657,13 +2677,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668636</v>
+        <v>668500</v>
       </c>
       <c r="R20" t="n">
-        <v>6691609</v>
+        <v>6691729</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2687,12 +2707,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2718,51 +2738,51 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128953979</t>
+          <t>https://artportalen.se/Sighting/136824831</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128344134</v>
+        <v>136824832</v>
       </c>
       <c r="B21" t="n">
-        <v>93189</v>
+        <v>96563</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4361</v>
+        <v>2812</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>668502</v>
+        <v>668587</v>
       </c>
       <c r="R21" t="n">
-        <v>6691868</v>
+        <v>6691653</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2789,17 +2809,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Tallhällmark</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2814,49 +2829,49 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128344134</t>
+          <t>https://artportalen.se/Sighting/136824832</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128260557</v>
+        <v>136824833</v>
       </c>
       <c r="B22" t="n">
-        <v>93209</v>
+        <v>96563</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4366</v>
+        <v>2812</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2866,13 +2881,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>668414</v>
+        <v>668627</v>
       </c>
       <c r="R22" t="n">
-        <v>6691754</v>
+        <v>6691630</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2896,12 +2911,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2927,38 +2942,38 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260557</t>
+          <t>https://artportalen.se/Sighting/136824833</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128260558</v>
+        <v>128953972</v>
       </c>
       <c r="B23" t="n">
-        <v>93209</v>
+        <v>96458</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4366</v>
+        <v>2818</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2968,13 +2983,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>668442</v>
+        <v>668638</v>
       </c>
       <c r="R23" t="n">
-        <v>6691699</v>
+        <v>6691675</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2998,12 +3013,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3014,6 +3029,21 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3029,51 +3059,51 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260558</t>
+          <t>https://artportalen.se/Sighting/128953972</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128344129</v>
+        <v>136824816</v>
       </c>
       <c r="B24" t="n">
-        <v>93209</v>
+        <v>96686</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4366</v>
+        <v>2818</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>668557</v>
+        <v>668765</v>
       </c>
       <c r="R24" t="n">
-        <v>6691949</v>
+        <v>6691901</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3100,12 +3130,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3116,69 +3146,84 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128344129</t>
+          <t>https://artportalen.se/Sighting/136824816</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127382963</v>
+        <v>128344130</v>
       </c>
       <c r="B25" t="n">
-        <v>93215</v>
+        <v>91680</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4368</v>
+        <v>3215</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>668299</v>
+        <v>668494</v>
       </c>
       <c r="R25" t="n">
-        <v>6691892</v>
+        <v>6691650</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3202,12 +3247,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3222,27 +3267,27 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127382963</t>
+          <t>https://artportalen.se/Sighting/128344130</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128260548</v>
+        <v>128344131</v>
       </c>
       <c r="B26" t="n">
-        <v>92869</v>
+        <v>91680</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3250,37 +3295,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>668572</v>
+        <v>668602</v>
       </c>
       <c r="R26" t="n">
-        <v>6691927</v>
+        <v>6691678</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3324,27 +3369,27 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260548</t>
+          <t>https://artportalen.se/Sighting/128344131</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128344126</v>
+        <v>128344132</v>
       </c>
       <c r="B27" t="n">
-        <v>92869</v>
+        <v>91680</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3352,21 +3397,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3376,10 +3421,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>668368</v>
+        <v>668568</v>
       </c>
       <c r="R27" t="n">
-        <v>6691735</v>
+        <v>6691712</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3437,16 +3482,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128344126</t>
+          <t>https://artportalen.se/Sighting/128344132</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128344127</v>
+        <v>128344133</v>
       </c>
       <c r="B28" t="n">
-        <v>92869</v>
+        <v>91680</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3454,21 +3499,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3478,10 +3523,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>668594</v>
+        <v>668580</v>
       </c>
       <c r="R28" t="n">
-        <v>6691661</v>
+        <v>6691920</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3539,16 +3584,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128344127</t>
+          <t>https://artportalen.se/Sighting/128344133</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128953969</v>
+        <v>128953979</v>
       </c>
       <c r="B29" t="n">
-        <v>91872</v>
+        <v>91680</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3556,21 +3601,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>3215</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3580,10 +3625,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>668650</v>
+        <v>668636</v>
       </c>
       <c r="R29" t="n">
-        <v>6691679</v>
+        <v>6691609</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3641,16 +3686,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128953969</t>
+          <t>https://artportalen.se/Sighting/128953979</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128953970</v>
+        <v>136824828</v>
       </c>
       <c r="B30" t="n">
-        <v>91872</v>
+        <v>87322</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3658,21 +3703,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>3762</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3682,13 +3727,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>668676</v>
+        <v>668740</v>
       </c>
       <c r="R30" t="n">
-        <v>6691606</v>
+        <v>6691904</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3712,12 +3757,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3728,21 +3773,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3758,16 +3788,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128953970</t>
+          <t>https://artportalen.se/Sighting/136824828</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128260549</v>
+        <v>128344134</v>
       </c>
       <c r="B31" t="n">
-        <v>93223</v>
+        <v>93189</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3775,37 +3805,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5448</v>
+        <v>4361</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>668507</v>
+        <v>668502</v>
       </c>
       <c r="R31" t="n">
-        <v>6691854</v>
+        <v>6691868</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3837,6 +3867,11 @@
           <t>2025-09-06</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Tallhällmark</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -3845,58 +3880,53 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>Tallhällmark</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260549</t>
+          <t>https://artportalen.se/Sighting/128344134</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128260564</v>
+        <v>128260557</v>
       </c>
       <c r="B32" t="n">
-        <v>91435</v>
+        <v>93209</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5747</v>
+        <v>4366</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3906,10 +3936,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>668588</v>
+        <v>668414</v>
       </c>
       <c r="R32" t="n">
-        <v>6691696</v>
+        <v>6691754</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3967,38 +3997,38 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260564</t>
+          <t>https://artportalen.se/Sighting/128260557</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128260565</v>
+        <v>128260558</v>
       </c>
       <c r="B33" t="n">
-        <v>91435</v>
+        <v>93209</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5747</v>
+        <v>4366</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4008,10 +4038,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>668592</v>
+        <v>668442</v>
       </c>
       <c r="R33" t="n">
-        <v>6691678</v>
+        <v>6691699</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4069,54 +4099,54 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260565</t>
+          <t>https://artportalen.se/Sighting/128260558</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128953983</v>
+        <v>128344129</v>
       </c>
       <c r="B34" t="n">
-        <v>91435</v>
+        <v>93209</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5747</v>
+        <v>4366</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>668689</v>
+        <v>668557</v>
       </c>
       <c r="R34" t="n">
-        <v>6691641</v>
+        <v>6691949</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4140,12 +4170,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4160,27 +4190,27 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128953983</t>
+          <t>https://artportalen.se/Sighting/128344129</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127382931</v>
+        <v>136824823</v>
       </c>
       <c r="B35" t="n">
-        <v>79946</v>
+        <v>93421</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4188,21 +4218,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>4366</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4212,13 +4242,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>668378</v>
+        <v>668485</v>
       </c>
       <c r="R35" t="n">
-        <v>6691942</v>
+        <v>6691765</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4242,12 +4272,27 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4258,21 +4303,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4288,57 +4318,54 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127382931</t>
+          <t>https://artportalen.se/Sighting/136824823</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128953977</v>
+        <v>136824824</v>
       </c>
       <c r="B36" t="n">
-        <v>80336</v>
+        <v>93421</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6456</v>
+        <v>4366</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>668697</v>
+        <v>668737</v>
       </c>
       <c r="R36" t="n">
-        <v>6691561</v>
+        <v>6691854</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4362,12 +4389,27 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4376,24 +4418,8 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4409,38 +4435,38 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128953977</t>
+          <t>https://artportalen.se/Sighting/136824824</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128953978</v>
+        <v>127382963</v>
       </c>
       <c r="B37" t="n">
-        <v>80336</v>
+        <v>93215</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6456</v>
+        <v>4368</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4450,10 +4476,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>668684</v>
+        <v>668299</v>
       </c>
       <c r="R37" t="n">
-        <v>6691557</v>
+        <v>6691892</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4480,12 +4506,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4496,21 +4522,6 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4526,16 +4537,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128953978</t>
+          <t>https://artportalen.se/Sighting/127382963</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128953973</v>
+        <v>128260548</v>
       </c>
       <c r="B38" t="n">
-        <v>57950</v>
+        <v>92869</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4543,42 +4554,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>4769</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>668704</v>
+        <v>668572</v>
       </c>
       <c r="R38" t="n">
-        <v>6691768</v>
+        <v>6691927</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4602,12 +4608,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4633,16 +4639,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128953973</t>
+          <t>https://artportalen.se/Sighting/128260548</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128953974</v>
+        <v>128344126</v>
       </c>
       <c r="B39" t="n">
-        <v>57950</v>
+        <v>92869</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4650,42 +4656,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>4769</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>668675</v>
+        <v>668368</v>
       </c>
       <c r="R39" t="n">
-        <v>6691565</v>
+        <v>6691735</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4709,12 +4710,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4729,27 +4730,27 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128953974</t>
+          <t>https://artportalen.se/Sighting/128344126</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128260539</v>
+        <v>128344127</v>
       </c>
       <c r="B40" t="n">
-        <v>57141</v>
+        <v>92869</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4757,42 +4758,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>4769</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>668536</v>
+        <v>668594</v>
       </c>
       <c r="R40" t="n">
-        <v>6691824</v>
+        <v>6691661</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4822,11 +4818,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Balgrop med fjädrar</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4841,27 +4832,27 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260539</t>
+          <t>https://artportalen.se/Sighting/128344127</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132894827</v>
+        <v>128953969</v>
       </c>
       <c r="B41" t="n">
-        <v>57162</v>
+        <v>91872</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4869,39 +4860,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Östensbo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>668548</v>
+        <v>668650</v>
       </c>
       <c r="R41" t="n">
-        <v>6691834</v>
+        <v>6691679</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4928,17 +4914,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Lämpligt tjäderhabitat</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4964,16 +4945,16 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132894827</t>
+          <t>https://artportalen.se/Sighting/128953969</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128953999</v>
+        <v>128953970</v>
       </c>
       <c r="B42" t="n">
-        <v>5179</v>
+        <v>91872</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4981,21 +4962,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5008,7 +4989,7 @@
         <v>668676</v>
       </c>
       <c r="R42" t="n">
-        <v>6691605</v>
+        <v>6691606</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5049,7 +5030,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5082,16 +5062,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128953999</t>
+          <t>https://artportalen.se/Sighting/128953970</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125807887</v>
+        <v>136824808</v>
       </c>
       <c r="B43" t="n">
-        <v>4781</v>
+        <v>92074</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5099,37 +5079,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>102306</v>
+        <v>5447</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>668279</v>
+        <v>668651</v>
       </c>
       <c r="R43" t="n">
-        <v>6691905</v>
+        <v>6691678</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5153,12 +5133,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5199,54 +5179,54 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125807887</t>
+          <t>https://artportalen.se/Sighting/136824808</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125807888</v>
+        <v>128260549</v>
       </c>
       <c r="B44" t="n">
-        <v>4781</v>
+        <v>93223</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>102306</v>
+        <v>5448</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>668255</v>
+        <v>668507</v>
       </c>
       <c r="R44" t="n">
-        <v>6691905</v>
+        <v>6691854</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5270,12 +5250,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5287,19 +5267,9 @@
       <c r="AG44" t="b">
         <v>0</v>
       </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Tallhällmark</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5316,38 +5286,38 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125807888</t>
+          <t>https://artportalen.se/Sighting/128260549</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127382960</v>
+        <v>128260564</v>
       </c>
       <c r="B45" t="n">
-        <v>4781</v>
+        <v>91435</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>102306</v>
+        <v>5747</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5357,13 +5327,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>668228</v>
+        <v>668588</v>
       </c>
       <c r="R45" t="n">
-        <v>6691916</v>
+        <v>6691696</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5387,12 +5357,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5403,21 +5373,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5433,38 +5388,38 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127382960</t>
+          <t>https://artportalen.se/Sighting/128260564</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128260581</v>
+        <v>128260565</v>
       </c>
       <c r="B46" t="n">
-        <v>4781</v>
+        <v>91435</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>102306</v>
+        <v>5747</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5474,10 +5429,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>668437</v>
+        <v>668592</v>
       </c>
       <c r="R46" t="n">
-        <v>6691726</v>
+        <v>6691678</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5521,21 +5476,6 @@
       <c r="AG46" t="b">
         <v>0</v>
       </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
@@ -5550,38 +5490,38 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260581</t>
+          <t>https://artportalen.se/Sighting/128260565</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128260582</v>
+        <v>128953983</v>
       </c>
       <c r="B47" t="n">
-        <v>4781</v>
+        <v>91435</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>102306</v>
+        <v>5747</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5591,13 +5531,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>668444</v>
+        <v>668689</v>
       </c>
       <c r="R47" t="n">
-        <v>6691724</v>
+        <v>6691641</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5621,12 +5561,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5637,21 +5577,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5667,38 +5592,38 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260582</t>
+          <t>https://artportalen.se/Sighting/128953983</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128260583</v>
+        <v>136824839</v>
       </c>
       <c r="B48" t="n">
-        <v>4781</v>
+        <v>93445</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>102306</v>
+        <v>5964</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5708,13 +5633,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>668540</v>
+        <v>668732</v>
       </c>
       <c r="R48" t="n">
-        <v>6691905</v>
+        <v>6691872</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5738,12 +5663,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5754,21 +5679,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5784,51 +5694,51 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260583</t>
+          <t>https://artportalen.se/Sighting/136824839</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128344139</v>
+        <v>136824840</v>
       </c>
       <c r="B49" t="n">
-        <v>4781</v>
+        <v>93445</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>102306</v>
+        <v>5964</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>668595</v>
+        <v>668777</v>
       </c>
       <c r="R49" t="n">
-        <v>6691931</v>
+        <v>6691909</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5855,12 +5765,17 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5875,27 +5790,27 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128344139</t>
+          <t>https://artportalen.se/Sighting/136824840</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128260540</v>
+        <v>136824841</v>
       </c>
       <c r="B50" t="n">
-        <v>58114</v>
+        <v>93445</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5903,42 +5818,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>5964</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>668462</v>
+        <v>668789</v>
       </c>
       <c r="R50" t="n">
-        <v>6691745</v>
+        <v>6691922</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5962,12 +5872,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5993,16 +5903,16 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260540</t>
+          <t>https://artportalen.se/Sighting/136824841</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128260541</v>
+        <v>136824829</v>
       </c>
       <c r="B51" t="n">
-        <v>58114</v>
+        <v>93447</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6010,32 +5920,24 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
@@ -6045,10 +5947,10 @@
         <v>668559</v>
       </c>
       <c r="R51" t="n">
-        <v>6691737</v>
+        <v>6691668</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6072,12 +5974,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6103,54 +6005,54 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260541</t>
+          <t>https://artportalen.se/Sighting/136824829</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125853673</v>
+        <v>136824830</v>
       </c>
       <c r="B52" t="n">
-        <v>99035</v>
+        <v>93447</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219790</v>
+        <v>5966</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>668269</v>
+        <v>668441</v>
       </c>
       <c r="R52" t="n">
-        <v>6691918</v>
+        <v>6691846</v>
       </c>
       <c r="S52" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6174,12 +6076,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6194,65 +6096,65 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Eva-Lena1 Rådberg</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Eva-Lena1 Rådberg</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125853673</t>
+          <t>https://artportalen.se/Sighting/136824830</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125855915</v>
+        <v>127382931</v>
       </c>
       <c r="B53" t="n">
-        <v>99035</v>
+        <v>79946</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219790</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>668328</v>
+        <v>668378</v>
       </c>
       <c r="R53" t="n">
-        <v>6691847</v>
+        <v>6691942</v>
       </c>
       <c r="S53" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6276,12 +6178,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6292,31 +6194,46 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125855915</t>
+          <t>https://artportalen.se/Sighting/127382931</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128344142</v>
+        <v>128953977</v>
       </c>
       <c r="B54" t="n">
-        <v>99035</v>
+        <v>80336</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6324,37 +6241,40 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219790</v>
+        <v>6456</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>668540</v>
+        <v>668697</v>
       </c>
       <c r="R54" t="n">
-        <v>6691947</v>
+        <v>6691561</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6378,12 +6298,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6392,80 +6312,87 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128344142</t>
+          <t>https://artportalen.se/Sighting/128953977</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128260575</v>
+        <v>128953978</v>
       </c>
       <c r="B55" t="n">
-        <v>99118</v>
+        <v>80336</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>668568</v>
+        <v>668684</v>
       </c>
       <c r="R55" t="n">
-        <v>6691681</v>
+        <v>6691557</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6489,12 +6416,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6505,6 +6432,21 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6520,54 +6462,59 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260575</t>
+          <t>https://artportalen.se/Sighting/128953978</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128344136</v>
+        <v>128953973</v>
       </c>
       <c r="B56" t="n">
-        <v>99118</v>
+        <v>57950</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>668558</v>
+        <v>668704</v>
       </c>
       <c r="R56" t="n">
-        <v>6691675</v>
+        <v>6691768</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6591,17 +6538,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>21</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6616,27 +6558,27 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128344136</t>
+          <t>https://artportalen.se/Sighting/128953973</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125855908</v>
+        <v>128953974</v>
       </c>
       <c r="B57" t="n">
-        <v>106244</v>
+        <v>57950</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6644,37 +6586,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>668294</v>
+        <v>668675</v>
       </c>
       <c r="R57" t="n">
-        <v>6691884</v>
+        <v>6691565</v>
       </c>
       <c r="S57" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6698,12 +6645,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6718,27 +6665,27 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125855908</t>
+          <t>https://artportalen.se/Sighting/128953974</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128260577</v>
+        <v>128260539</v>
       </c>
       <c r="B58" t="n">
-        <v>106244</v>
+        <v>57141</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6746,34 +6693,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>668565</v>
+        <v>668536</v>
       </c>
       <c r="R58" t="n">
-        <v>6691734</v>
+        <v>6691824</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -6808,6 +6760,11 @@
           <t>2025-09-06</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Balgrop med fjädrar</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -6831,16 +6788,16 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260577</t>
+          <t>https://artportalen.se/Sighting/128260539</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128344138</v>
+        <v>132894827</v>
       </c>
       <c r="B59" t="n">
-        <v>106244</v>
+        <v>57162</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6848,37 +6805,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>668564</v>
+        <v>668548</v>
       </c>
       <c r="R59" t="n">
-        <v>6691753</v>
+        <v>6691834</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6902,12 +6864,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Lämpligt tjäderhabitat</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6922,27 +6889,27 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128344138</t>
+          <t>https://artportalen.se/Sighting/132894827</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132894835</v>
+        <v>136824810</v>
       </c>
       <c r="B60" t="n">
-        <v>106324</v>
+        <v>57195</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6950,37 +6917,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Östensbo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>668570</v>
+        <v>668526</v>
       </c>
       <c r="R60" t="n">
-        <v>6691835</v>
+        <v>6691693</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7004,17 +6976,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Fjäder av tupp.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7040,16 +7012,16 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132894835</t>
+          <t>https://artportalen.se/Sighting/136824810</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128344123</v>
+        <v>128953999</v>
       </c>
       <c r="B61" t="n">
-        <v>104628</v>
+        <v>5179</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7057,37 +7029,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222412</v>
+        <v>100526</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>668604</v>
+        <v>668676</v>
       </c>
       <c r="R61" t="n">
-        <v>6691663</v>
+        <v>6691605</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7111,12 +7083,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7125,33 +7097,49 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128344123</t>
+          <t>https://artportalen.se/Sighting/128953999</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128260592</v>
+        <v>125807887</v>
       </c>
       <c r="B62" t="n">
-        <v>101326</v>
+        <v>4781</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7159,37 +7147,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>668587</v>
+        <v>668279</v>
       </c>
       <c r="R62" t="n">
-        <v>6691690</v>
+        <v>6691905</v>
       </c>
       <c r="S62" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7213,12 +7201,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7229,6 +7217,21 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7244,16 +7247,16 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260592</t>
+          <t>https://artportalen.se/Sighting/125807887</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128260593</v>
+        <v>125807888</v>
       </c>
       <c r="B63" t="n">
-        <v>101326</v>
+        <v>4781</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7261,37 +7264,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>668593</v>
+        <v>668255</v>
       </c>
       <c r="R63" t="n">
-        <v>6691674</v>
+        <v>6691905</v>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7315,12 +7318,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7331,6 +7334,21 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -7346,16 +7364,16 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260593</t>
+          <t>https://artportalen.se/Sighting/125807888</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128953994</v>
+        <v>127382960</v>
       </c>
       <c r="B64" t="n">
-        <v>101325</v>
+        <v>4781</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7363,21 +7381,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7387,10 +7405,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>668674</v>
+        <v>668228</v>
       </c>
       <c r="R64" t="n">
-        <v>6691735</v>
+        <v>6691916</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7417,12 +7435,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7433,6 +7451,21 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -7448,16 +7481,16 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128953994</t>
+          <t>https://artportalen.se/Sighting/127382960</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128953995</v>
+        <v>128260581</v>
       </c>
       <c r="B65" t="n">
-        <v>101325</v>
+        <v>4781</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7465,21 +7498,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7489,13 +7522,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>668644</v>
+        <v>668437</v>
       </c>
       <c r="R65" t="n">
-        <v>6691674</v>
+        <v>6691726</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7519,12 +7552,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7535,6 +7568,21 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -7550,16 +7598,16 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128953995</t>
+          <t>https://artportalen.se/Sighting/128260581</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128953996</v>
+        <v>128260582</v>
       </c>
       <c r="B66" t="n">
-        <v>101325</v>
+        <v>4781</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7567,21 +7615,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7591,13 +7639,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>668650</v>
+        <v>668444</v>
       </c>
       <c r="R66" t="n">
-        <v>6691592</v>
+        <v>6691724</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7621,12 +7669,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7637,6 +7685,21 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -7652,16 +7715,16 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128953996</t>
+          <t>https://artportalen.se/Sighting/128260582</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128953997</v>
+        <v>128260583</v>
       </c>
       <c r="B67" t="n">
-        <v>101325</v>
+        <v>4781</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7669,21 +7732,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7693,13 +7756,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>668641</v>
+        <v>668540</v>
       </c>
       <c r="R67" t="n">
-        <v>6691647</v>
+        <v>6691905</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7723,12 +7786,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7739,6 +7802,21 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -7754,16 +7832,16 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128953997</t>
+          <t>https://artportalen.se/Sighting/128260583</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128953998</v>
+        <v>128344139</v>
       </c>
       <c r="B68" t="n">
-        <v>101325</v>
+        <v>4781</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7771,37 +7849,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>668653</v>
+        <v>668595</v>
       </c>
       <c r="R68" t="n">
-        <v>6691655</v>
+        <v>6691931</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7825,12 +7903,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7845,27 +7923,27 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128953998</t>
+          <t>https://artportalen.se/Sighting/128344139</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128953986</v>
+        <v>136824221</v>
       </c>
       <c r="B69" t="n">
-        <v>80392</v>
+        <v>4783</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7873,21 +7951,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>229497</v>
+        <v>102306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7897,13 +7975,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>668686</v>
+        <v>668354</v>
       </c>
       <c r="R69" t="n">
-        <v>6691559</v>
+        <v>6691795</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7927,12 +8005,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7946,17 +8024,17 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -7972,6 +8050,4036 @@
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136824221</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>128260540</v>
+      </c>
+      <c r="B70" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>668462</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6691745</v>
+      </c>
+      <c r="S70" t="n">
+        <v>25</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128260540</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>128260541</v>
+      </c>
+      <c r="B71" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>668559</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6691737</v>
+      </c>
+      <c r="S71" t="n">
+        <v>25</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128260541</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>136824814</v>
+      </c>
+      <c r="B72" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>668527</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6691698</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136824814</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>125853673</v>
+      </c>
+      <c r="B73" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Östensbo-Bennebo_1, Upl</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>668269</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6691918</v>
+      </c>
+      <c r="S73" t="n">
+        <v>1</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Eva-Lena1 Rådberg</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Eva-Lena1 Rådberg</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125853673</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>125855915</v>
+      </c>
+      <c r="B74" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Östensbo-Bennebo, Upl</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>668328</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6691847</v>
+      </c>
+      <c r="S74" t="n">
+        <v>12</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125855915</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>128344142</v>
+      </c>
+      <c r="B75" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Östensbo-Bennebo_1, Upl</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>668540</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6691947</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Tove Widén</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Tove Widén</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128344142</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>136824822</v>
+      </c>
+      <c r="B76" t="n">
+        <v>99329</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>668779</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6691909</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136824822</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>136824842</v>
+      </c>
+      <c r="B77" t="n">
+        <v>108376</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>668688</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6691747</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136824842</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>136824843</v>
+      </c>
+      <c r="B78" t="n">
+        <v>108376</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>668780</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6691947</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136824843</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>128260575</v>
+      </c>
+      <c r="B79" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>668568</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6691681</v>
+      </c>
+      <c r="S79" t="n">
+        <v>25</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128260575</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>128344136</v>
+      </c>
+      <c r="B80" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Östensbo-Bennebo_1, Upl</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>668558</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6691675</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Tove Widén</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Tove Widén</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128344136</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>125855908</v>
+      </c>
+      <c r="B81" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Östensbo-Bennebo, Upl</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>668294</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6691884</v>
+      </c>
+      <c r="S81" t="n">
+        <v>12</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125855908</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>128260577</v>
+      </c>
+      <c r="B82" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>668565</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6691734</v>
+      </c>
+      <c r="S82" t="n">
+        <v>25</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128260577</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>128344138</v>
+      </c>
+      <c r="B83" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Östensbo-Bennebo_1, Upl</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>668564</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6691753</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Tove Widén</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Tove Widén</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128344138</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>132894835</v>
+      </c>
+      <c r="B84" t="n">
+        <v>106324</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Östensbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>668570</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6691835</v>
+      </c>
+      <c r="S84" t="n">
+        <v>15</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132894835</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>136824837</v>
+      </c>
+      <c r="B85" t="n">
+        <v>106492</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>668380</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6691865</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136824837</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>136824800</v>
+      </c>
+      <c r="B86" t="n">
+        <v>102477</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>668779</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6691909</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136824800</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>136824801</v>
+      </c>
+      <c r="B87" t="n">
+        <v>102477</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>668791</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6691921</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136824801</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>128344123</v>
+      </c>
+      <c r="B88" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Östensbo-Bennebo_1, Upl</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>668604</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6691663</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Tove Widén</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Tove Widén</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128344123</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>136824811</v>
+      </c>
+      <c r="B89" t="n">
+        <v>104874</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>668677</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6691727</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136824811</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>136824812</v>
+      </c>
+      <c r="B90" t="n">
+        <v>104874</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>668727</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6691836</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136824812</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>128260592</v>
+      </c>
+      <c r="B91" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>668587</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6691690</v>
+      </c>
+      <c r="S91" t="n">
+        <v>25</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128260592</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>128260593</v>
+      </c>
+      <c r="B92" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>668593</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6691674</v>
+      </c>
+      <c r="S92" t="n">
+        <v>25</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128260593</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>128953994</v>
+      </c>
+      <c r="B93" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>668674</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6691735</v>
+      </c>
+      <c r="S93" t="n">
+        <v>15</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128953994</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>128953995</v>
+      </c>
+      <c r="B94" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>668644</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6691674</v>
+      </c>
+      <c r="S94" t="n">
+        <v>15</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128953995</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>128953996</v>
+      </c>
+      <c r="B95" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>668650</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6691592</v>
+      </c>
+      <c r="S95" t="n">
+        <v>15</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128953996</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>128953997</v>
+      </c>
+      <c r="B96" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>668641</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6691647</v>
+      </c>
+      <c r="S96" t="n">
+        <v>15</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128953997</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>128953998</v>
+      </c>
+      <c r="B97" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>668653</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6691655</v>
+      </c>
+      <c r="S97" t="n">
+        <v>15</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128953998</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>136824845</v>
+      </c>
+      <c r="B98" t="n">
+        <v>101561</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>668498</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6691758</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136824845</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>136824847</v>
+      </c>
+      <c r="B99" t="n">
+        <v>101561</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>668588</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6691652</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136824847</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>136824848</v>
+      </c>
+      <c r="B100" t="n">
+        <v>101561</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>668632</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6691628</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136824848</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>136824849</v>
+      </c>
+      <c r="B101" t="n">
+        <v>101561</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>668654</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6691662</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136824849</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>136824850</v>
+      </c>
+      <c r="B102" t="n">
+        <v>101561</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>668651</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6691668</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136824850</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>136824851</v>
+      </c>
+      <c r="B103" t="n">
+        <v>101561</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>668681</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6691734</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136824851</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>136824852</v>
+      </c>
+      <c r="B104" t="n">
+        <v>101561</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>668688</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6691747</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136824852</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>136824853</v>
+      </c>
+      <c r="B105" t="n">
+        <v>101561</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>668715</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6691784</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136824853</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>136824854</v>
+      </c>
+      <c r="B106" t="n">
+        <v>101561</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>668727</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6691836</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136824854</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>136824825</v>
+      </c>
+      <c r="B107" t="n">
+        <v>99157</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>668715</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6691784</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136824825</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>128953986</v>
+      </c>
+      <c r="B108" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>668686</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6691559</v>
+      </c>
+      <c r="S108" t="n">
+        <v>15</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128953986</t>
         </is>
@@ -8047,6 +12155,45 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 19253-2026 artfynd.xlsx
+++ b/artfynd/A 19253-2026 artfynd.xlsx
@@ -1529,7 +1529,7 @@
         <v>136824805</v>
       </c>
       <c r="B10" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>136824806</v>
       </c>
       <c r="B11" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>136824807</v>
       </c>
       <c r="B12" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>136824809</v>
       </c>
       <c r="B17" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>136824836</v>
       </c>
       <c r="B19" t="n">
-        <v>92464</v>
+        <v>92466</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>136824831</v>
       </c>
       <c r="B20" t="n">
-        <v>96563</v>
+        <v>96565</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>136824832</v>
       </c>
       <c r="B21" t="n">
-        <v>96563</v>
+        <v>96565</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>136824833</v>
       </c>
       <c r="B22" t="n">
-        <v>96563</v>
+        <v>96565</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>136824816</v>
       </c>
       <c r="B24" t="n">
-        <v>96686</v>
+        <v>96688</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>136824828</v>
       </c>
       <c r="B30" t="n">
-        <v>87322</v>
+        <v>87324</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
         <v>136824823</v>
       </c>
       <c r="B35" t="n">
-        <v>93421</v>
+        <v>93423</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>136824824</v>
       </c>
       <c r="B36" t="n">
-        <v>93421</v>
+        <v>93423</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>136824808</v>
       </c>
       <c r="B43" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>136824839</v>
       </c>
       <c r="B48" t="n">
-        <v>93445</v>
+        <v>93447</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         <v>136824840</v>
       </c>
       <c r="B49" t="n">
-        <v>93445</v>
+        <v>93447</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
         <v>136824841</v>
       </c>
       <c r="B50" t="n">
-        <v>93445</v>
+        <v>93447</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         <v>136824829</v>
       </c>
       <c r="B51" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>136824830</v>
       </c>
       <c r="B52" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -8690,7 +8690,7 @@
         <v>136824822</v>
       </c>
       <c r="B76" t="n">
-        <v>99329</v>
+        <v>99331</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>136824842</v>
       </c>
       <c r="B77" t="n">
-        <v>108376</v>
+        <v>108378</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         <v>136824843</v>
       </c>
       <c r="B78" t="n">
-        <v>108376</v>
+        <v>108378</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>136824837</v>
       </c>
       <c r="B85" t="n">
-        <v>106492</v>
+        <v>106494</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>136824800</v>
       </c>
       <c r="B86" t="n">
-        <v>102477</v>
+        <v>102479</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9831,7 +9831,7 @@
         <v>136824801</v>
       </c>
       <c r="B87" t="n">
-        <v>102477</v>
+        <v>102479</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10035,7 +10035,7 @@
         <v>136824811</v>
       </c>
       <c r="B89" t="n">
-        <v>104874</v>
+        <v>104876</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         <v>136824812</v>
       </c>
       <c r="B90" t="n">
-        <v>104874</v>
+        <v>104876</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10953,7 +10953,7 @@
         <v>136824845</v>
       </c>
       <c r="B98" t="n">
-        <v>101561</v>
+        <v>101563</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11055,7 +11055,7 @@
         <v>136824847</v>
       </c>
       <c r="B99" t="n">
-        <v>101561</v>
+        <v>101563</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11157,7 +11157,7 @@
         <v>136824848</v>
       </c>
       <c r="B100" t="n">
-        <v>101561</v>
+        <v>101563</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         <v>136824849</v>
       </c>
       <c r="B101" t="n">
-        <v>101561</v>
+        <v>101563</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11361,7 +11361,7 @@
         <v>136824850</v>
       </c>
       <c r="B102" t="n">
-        <v>101561</v>
+        <v>101563</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>136824851</v>
       </c>
       <c r="B103" t="n">
-        <v>101561</v>
+        <v>101563</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         <v>136824852</v>
       </c>
       <c r="B104" t="n">
-        <v>101561</v>
+        <v>101563</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11667,7 +11667,7 @@
         <v>136824853</v>
       </c>
       <c r="B105" t="n">
-        <v>101561</v>
+        <v>101563</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11769,7 +11769,7 @@
         <v>136824854</v>
       </c>
       <c r="B106" t="n">
-        <v>101561</v>
+        <v>101563</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11871,7 +11871,7 @@
         <v>136824825</v>
       </c>
       <c r="B107" t="n">
-        <v>99157</v>
+        <v>99159</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>

--- a/artfynd/A 19253-2026 artfynd.xlsx
+++ b/artfynd/A 19253-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ108"/>
+  <dimension ref="A1:AZ120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1975,45 +1975,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128344137</v>
+        <v>136974111</v>
       </c>
       <c r="B14" t="n">
-        <v>93199</v>
+        <v>85699</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>788</v>
+        <v>241</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Alb. &amp; Schwein.) Shear</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>668567</v>
+        <v>668738</v>
       </c>
       <c r="R14" t="n">
-        <v>6691956</v>
+        <v>6691830</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2040,12 +2040,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,53 +2056,68 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128344137</t>
+          <t>https://artportalen.se/Sighting/136974111</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128344122</v>
+        <v>128344137</v>
       </c>
       <c r="B15" t="n">
-        <v>91909</v>
+        <v>93199</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>788</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2112,10 +2127,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>668359</v>
+        <v>668567</v>
       </c>
       <c r="R15" t="n">
-        <v>6691742</v>
+        <v>6691956</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2150,11 +2165,6 @@
           <t>2025-09-06</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2178,13 +2188,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128344122</t>
+          <t>https://artportalen.se/Sighting/128344137</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128953971</v>
+        <v>128344122</v>
       </c>
       <c r="B16" t="n">
         <v>91909</v>
@@ -2215,17 +2225,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>668680</v>
+        <v>668359</v>
       </c>
       <c r="R16" t="n">
-        <v>6691646</v>
+        <v>6691742</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2249,12 +2259,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2265,46 +2280,31 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128953971</t>
+          <t>https://artportalen.se/Sighting/128344122</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136824809</v>
+        <v>128953971</v>
       </c>
       <c r="B17" t="n">
-        <v>92113</v>
+        <v>91909</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2336,13 +2336,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>668343</v>
+        <v>668680</v>
       </c>
       <c r="R17" t="n">
-        <v>6691845</v>
+        <v>6691646</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2366,17 +2366,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På bark som hänger från lågan.</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2417,38 +2412,38 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824809</t>
+          <t>https://artportalen.se/Sighting/128953971</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128953993</v>
+        <v>136824809</v>
       </c>
       <c r="B18" t="n">
-        <v>92564</v>
+        <v>92113</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2458,13 +2453,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>668664</v>
+        <v>668343</v>
       </c>
       <c r="R18" t="n">
-        <v>6691742</v>
+        <v>6691845</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2488,12 +2483,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På bark som hänger från lågan.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2534,38 +2534,38 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128953993</t>
+          <t>https://artportalen.se/Sighting/136824809</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136824836</v>
+        <v>128953993</v>
       </c>
       <c r="B19" t="n">
-        <v>92466</v>
+        <v>92564</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1506</v>
+        <v>1339</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2575,13 +2575,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>668657</v>
+        <v>668664</v>
       </c>
       <c r="R19" t="n">
-        <v>6691706</v>
+        <v>6691742</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2605,12 +2605,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2621,6 +2621,21 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2636,38 +2651,38 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824836</t>
+          <t>https://artportalen.se/Sighting/128953993</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136824831</v>
+        <v>136824836</v>
       </c>
       <c r="B20" t="n">
-        <v>96565</v>
+        <v>92466</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2812</v>
+        <v>1506</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2677,10 +2692,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668500</v>
+        <v>668657</v>
       </c>
       <c r="R20" t="n">
-        <v>6691729</v>
+        <v>6691706</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2738,13 +2753,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824831</t>
+          <t>https://artportalen.se/Sighting/136824836</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>136824832</v>
+        <v>136824831</v>
       </c>
       <c r="B21" t="n">
         <v>96565</v>
@@ -2779,10 +2794,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>668587</v>
+        <v>668500</v>
       </c>
       <c r="R21" t="n">
-        <v>6691653</v>
+        <v>6691729</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2840,13 +2855,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824832</t>
+          <t>https://artportalen.se/Sighting/136824831</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>136824833</v>
+        <v>136824832</v>
       </c>
       <c r="B22" t="n">
         <v>96565</v>
@@ -2881,10 +2896,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>668627</v>
+        <v>668587</v>
       </c>
       <c r="R22" t="n">
-        <v>6691630</v>
+        <v>6691653</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2942,16 +2957,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824833</t>
+          <t>https://artportalen.se/Sighting/136824832</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128953972</v>
+        <v>136824833</v>
       </c>
       <c r="B23" t="n">
-        <v>96458</v>
+        <v>96565</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2959,21 +2974,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2818</v>
+        <v>2812</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2983,13 +2998,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>668638</v>
+        <v>668627</v>
       </c>
       <c r="R23" t="n">
-        <v>6691675</v>
+        <v>6691630</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3013,12 +3028,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3029,21 +3044,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3059,16 +3059,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128953972</t>
+          <t>https://artportalen.se/Sighting/136824833</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>136824816</v>
+        <v>128953972</v>
       </c>
       <c r="B24" t="n">
-        <v>96688</v>
+        <v>96458</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3100,13 +3100,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>668765</v>
+        <v>668638</v>
       </c>
       <c r="R24" t="n">
-        <v>6691901</v>
+        <v>6691675</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3130,12 +3130,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3176,16 +3176,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824816</t>
+          <t>https://artportalen.se/Sighting/128953972</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128344130</v>
+        <v>136824816</v>
       </c>
       <c r="B25" t="n">
-        <v>91680</v>
+        <v>96688</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3193,34 +3193,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3215</v>
+        <v>2818</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>668494</v>
+        <v>668765</v>
       </c>
       <c r="R25" t="n">
-        <v>6691650</v>
+        <v>6691901</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3263,28 +3263,43 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128344130</t>
+          <t>https://artportalen.se/Sighting/136824816</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128344131</v>
+        <v>128344130</v>
       </c>
       <c r="B26" t="n">
         <v>91680</v>
@@ -3319,10 +3334,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>668602</v>
+        <v>668494</v>
       </c>
       <c r="R26" t="n">
-        <v>6691678</v>
+        <v>6691650</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3380,13 +3395,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128344131</t>
+          <t>https://artportalen.se/Sighting/128344130</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128344132</v>
+        <v>128344131</v>
       </c>
       <c r="B27" t="n">
         <v>91680</v>
@@ -3421,10 +3436,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>668568</v>
+        <v>668602</v>
       </c>
       <c r="R27" t="n">
-        <v>6691712</v>
+        <v>6691678</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3482,13 +3497,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128344132</t>
+          <t>https://artportalen.se/Sighting/128344131</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128344133</v>
+        <v>128344132</v>
       </c>
       <c r="B28" t="n">
         <v>91680</v>
@@ -3523,10 +3538,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>668580</v>
+        <v>668568</v>
       </c>
       <c r="R28" t="n">
-        <v>6691920</v>
+        <v>6691712</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3584,13 +3599,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128344133</t>
+          <t>https://artportalen.se/Sighting/128344132</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128953979</v>
+        <v>128344133</v>
       </c>
       <c r="B29" t="n">
         <v>91680</v>
@@ -3621,17 +3636,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>668636</v>
+        <v>668580</v>
       </c>
       <c r="R29" t="n">
-        <v>6691609</v>
+        <v>6691920</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3655,12 +3670,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3675,27 +3690,27 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128953979</t>
+          <t>https://artportalen.se/Sighting/128344133</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>136824828</v>
+        <v>128953979</v>
       </c>
       <c r="B30" t="n">
-        <v>87324</v>
+        <v>91680</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3703,21 +3718,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3762</v>
+        <v>3215</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3727,13 +3742,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>668740</v>
+        <v>668636</v>
       </c>
       <c r="R30" t="n">
-        <v>6691904</v>
+        <v>6691609</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3757,12 +3772,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3788,51 +3803,51 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824828</t>
+          <t>https://artportalen.se/Sighting/128953979</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128344134</v>
+        <v>136974096</v>
       </c>
       <c r="B31" t="n">
-        <v>93189</v>
+        <v>91889</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4361</v>
+        <v>3215</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>668502</v>
+        <v>668578</v>
       </c>
       <c r="R31" t="n">
-        <v>6691868</v>
+        <v>6691698</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3859,17 +3874,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Tallhällmark</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3884,27 +3894,27 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128344134</t>
+          <t>https://artportalen.se/Sighting/136974096</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128260557</v>
+        <v>136974097</v>
       </c>
       <c r="B32" t="n">
-        <v>93209</v>
+        <v>87553</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3912,21 +3922,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4366</v>
+        <v>3739</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3936,13 +3946,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>668414</v>
+        <v>668446</v>
       </c>
       <c r="R32" t="n">
-        <v>6691754</v>
+        <v>6691728</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3966,12 +3976,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3997,38 +4007,38 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260557</t>
+          <t>https://artportalen.se/Sighting/136974097</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128260558</v>
+        <v>136824828</v>
       </c>
       <c r="B33" t="n">
-        <v>93209</v>
+        <v>87324</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4366</v>
+        <v>3762</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4038,13 +4048,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>668442</v>
+        <v>668740</v>
       </c>
       <c r="R33" t="n">
-        <v>6691699</v>
+        <v>6691904</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4068,12 +4078,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4099,51 +4109,51 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260558</t>
+          <t>https://artportalen.se/Sighting/136824828</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128344129</v>
+        <v>136974098</v>
       </c>
       <c r="B34" t="n">
-        <v>93209</v>
+        <v>87324</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4366</v>
+        <v>3762</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>668557</v>
+        <v>668693</v>
       </c>
       <c r="R34" t="n">
-        <v>6691949</v>
+        <v>6691751</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4170,12 +4180,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4190,27 +4200,27 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128344129</t>
+          <t>https://artportalen.se/Sighting/136974098</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>136824823</v>
+        <v>128344134</v>
       </c>
       <c r="B35" t="n">
-        <v>93423</v>
+        <v>93189</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4218,34 +4228,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>668485</v>
+        <v>668502</v>
       </c>
       <c r="R35" t="n">
-        <v>6691765</v>
+        <v>6691868</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4272,27 +4282,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>16:47</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>16:47</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Tallhällmark</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4307,27 +4307,27 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824823</t>
+          <t>https://artportalen.se/Sighting/128344134</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>136824824</v>
+        <v>128260557</v>
       </c>
       <c r="B36" t="n">
-        <v>93423</v>
+        <v>93209</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4359,13 +4359,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>668737</v>
+        <v>668414</v>
       </c>
       <c r="R36" t="n">
-        <v>6691854</v>
+        <v>6691754</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4389,27 +4389,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>17:17</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>17:17</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Granskog</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4435,16 +4420,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824824</t>
+          <t>https://artportalen.se/Sighting/128260557</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127382963</v>
+        <v>128260558</v>
       </c>
       <c r="B37" t="n">
-        <v>93215</v>
+        <v>93209</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4452,21 +4437,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4368</v>
+        <v>4366</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4476,13 +4461,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>668299</v>
+        <v>668442</v>
       </c>
       <c r="R37" t="n">
-        <v>6691892</v>
+        <v>6691699</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4506,12 +4491,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4537,54 +4522,54 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127382963</t>
+          <t>https://artportalen.se/Sighting/128260558</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128260548</v>
+        <v>128344129</v>
       </c>
       <c r="B38" t="n">
-        <v>92869</v>
+        <v>93209</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4769</v>
+        <v>4366</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>668572</v>
+        <v>668557</v>
       </c>
       <c r="R38" t="n">
-        <v>6691927</v>
+        <v>6691949</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4628,62 +4613,62 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260548</t>
+          <t>https://artportalen.se/Sighting/128344129</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128344126</v>
+        <v>136824823</v>
       </c>
       <c r="B39" t="n">
-        <v>92869</v>
+        <v>93423</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4769</v>
+        <v>4366</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>668368</v>
+        <v>668485</v>
       </c>
       <c r="R39" t="n">
-        <v>6691735</v>
+        <v>6691765</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4710,12 +4695,27 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4730,62 +4730,62 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128344126</t>
+          <t>https://artportalen.se/Sighting/136824823</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128344127</v>
+        <v>136824824</v>
       </c>
       <c r="B40" t="n">
-        <v>92869</v>
+        <v>93423</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4769</v>
+        <v>4366</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>668594</v>
+        <v>668737</v>
       </c>
       <c r="R40" t="n">
-        <v>6691661</v>
+        <v>6691854</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4812,12 +4812,27 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4832,49 +4847,49 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128344127</t>
+          <t>https://artportalen.se/Sighting/136824824</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128953969</v>
+        <v>127382963</v>
       </c>
       <c r="B41" t="n">
-        <v>91872</v>
+        <v>93215</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>4368</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4884,10 +4899,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>668650</v>
+        <v>668299</v>
       </c>
       <c r="R41" t="n">
-        <v>6691679</v>
+        <v>6691892</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4914,12 +4929,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4945,16 +4960,16 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128953969</t>
+          <t>https://artportalen.se/Sighting/127382963</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128953970</v>
+        <v>128260548</v>
       </c>
       <c r="B42" t="n">
-        <v>91872</v>
+        <v>92869</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4962,21 +4977,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>4769</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4986,13 +5001,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>668676</v>
+        <v>668572</v>
       </c>
       <c r="R42" t="n">
-        <v>6691606</v>
+        <v>6691927</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5016,12 +5031,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5032,21 +5047,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5062,16 +5062,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128953970</t>
+          <t>https://artportalen.se/Sighting/128260548</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>136824808</v>
+        <v>128344126</v>
       </c>
       <c r="B43" t="n">
-        <v>92076</v>
+        <v>92869</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5079,34 +5079,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>4769</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>668651</v>
+        <v>668368</v>
       </c>
       <c r="R43" t="n">
-        <v>6691678</v>
+        <v>6691735</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5133,12 +5133,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5149,84 +5149,69 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824808</t>
+          <t>https://artportalen.se/Sighting/128344126</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128260549</v>
+        <v>128344127</v>
       </c>
       <c r="B44" t="n">
-        <v>93223</v>
+        <v>92869</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5448</v>
+        <v>4769</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>668507</v>
+        <v>668594</v>
       </c>
       <c r="R44" t="n">
-        <v>6691854</v>
+        <v>6691661</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5266,58 +5251,53 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>Tallhällmark</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260549</t>
+          <t>https://artportalen.se/Sighting/128344127</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128260564</v>
+        <v>128953969</v>
       </c>
       <c r="B45" t="n">
-        <v>91435</v>
+        <v>91872</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5747</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5327,13 +5307,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>668588</v>
+        <v>668650</v>
       </c>
       <c r="R45" t="n">
-        <v>6691696</v>
+        <v>6691679</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5357,12 +5337,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5388,38 +5368,38 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260564</t>
+          <t>https://artportalen.se/Sighting/128953969</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128260565</v>
+        <v>128953970</v>
       </c>
       <c r="B46" t="n">
-        <v>91435</v>
+        <v>91872</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5747</v>
+        <v>5447</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5429,13 +5409,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>668592</v>
+        <v>668676</v>
       </c>
       <c r="R46" t="n">
-        <v>6691678</v>
+        <v>6691606</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5459,12 +5439,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5475,6 +5455,21 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5490,38 +5485,38 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260565</t>
+          <t>https://artportalen.se/Sighting/128953970</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128953983</v>
+        <v>136824808</v>
       </c>
       <c r="B47" t="n">
-        <v>91435</v>
+        <v>92076</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5747</v>
+        <v>5447</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5531,13 +5526,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>668689</v>
+        <v>668651</v>
       </c>
       <c r="R47" t="n">
-        <v>6691641</v>
+        <v>6691678</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5561,12 +5556,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5577,6 +5572,21 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5592,16 +5602,16 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128953983</t>
+          <t>https://artportalen.se/Sighting/136824808</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>136824839</v>
+        <v>128260549</v>
       </c>
       <c r="B48" t="n">
-        <v>93447</v>
+        <v>93223</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5609,21 +5619,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5964</v>
+        <v>5448</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5633,13 +5643,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>668732</v>
+        <v>668507</v>
       </c>
       <c r="R48" t="n">
-        <v>6691872</v>
+        <v>6691854</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5663,12 +5673,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5679,6 +5689,11 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Tallhällmark</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5694,38 +5709,38 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824839</t>
+          <t>https://artportalen.se/Sighting/128260549</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>136824840</v>
+        <v>128260564</v>
       </c>
       <c r="B49" t="n">
-        <v>93447</v>
+        <v>91435</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5964</v>
+        <v>5747</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5735,13 +5750,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>668777</v>
+        <v>668588</v>
       </c>
       <c r="R49" t="n">
-        <v>6691909</v>
+        <v>6691696</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5765,17 +5780,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Granskog</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5801,38 +5811,38 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824840</t>
+          <t>https://artportalen.se/Sighting/128260564</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>136824841</v>
+        <v>128260565</v>
       </c>
       <c r="B50" t="n">
-        <v>93447</v>
+        <v>91435</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5964</v>
+        <v>5747</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5842,13 +5852,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>668789</v>
+        <v>668592</v>
       </c>
       <c r="R50" t="n">
-        <v>6691922</v>
+        <v>6691678</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5872,12 +5882,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5903,38 +5913,38 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824841</t>
+          <t>https://artportalen.se/Sighting/128260565</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>136824829</v>
+        <v>128953983</v>
       </c>
       <c r="B51" t="n">
-        <v>93449</v>
+        <v>91435</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5966</v>
+        <v>5747</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5944,13 +5954,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>668559</v>
+        <v>668689</v>
       </c>
       <c r="R51" t="n">
-        <v>6691668</v>
+        <v>6691641</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5974,12 +5984,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6005,16 +6015,16 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824829</t>
+          <t>https://artportalen.se/Sighting/128953983</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>136824830</v>
+        <v>136824839</v>
       </c>
       <c r="B52" t="n">
-        <v>93449</v>
+        <v>93447</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6022,21 +6032,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5966</v>
+        <v>5964</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6046,10 +6056,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>668441</v>
+        <v>668732</v>
       </c>
       <c r="R52" t="n">
-        <v>6691846</v>
+        <v>6691872</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6107,16 +6117,16 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824830</t>
+          <t>https://artportalen.se/Sighting/136824839</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127382931</v>
+        <v>136824840</v>
       </c>
       <c r="B53" t="n">
-        <v>79946</v>
+        <v>93447</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6124,21 +6134,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>5964</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6148,13 +6158,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>668378</v>
+        <v>668777</v>
       </c>
       <c r="R53" t="n">
-        <v>6691942</v>
+        <v>6691909</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6178,12 +6188,17 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6194,21 +6209,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6224,57 +6224,54 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127382931</t>
+          <t>https://artportalen.se/Sighting/136824840</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128953977</v>
+        <v>136824841</v>
       </c>
       <c r="B54" t="n">
-        <v>80336</v>
+        <v>93447</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6456</v>
+        <v>5964</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>668697</v>
+        <v>668789</v>
       </c>
       <c r="R54" t="n">
-        <v>6691561</v>
+        <v>6691922</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6298,12 +6295,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6312,24 +6309,8 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6345,38 +6326,38 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128953977</t>
+          <t>https://artportalen.se/Sighting/136824841</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128953978</v>
+        <v>136974114</v>
       </c>
       <c r="B55" t="n">
-        <v>80336</v>
+        <v>93447</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6456</v>
+        <v>5964</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6386,13 +6367,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>668684</v>
+        <v>668581</v>
       </c>
       <c r="R55" t="n">
-        <v>6691557</v>
+        <v>6691696</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6416,12 +6397,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6432,21 +6413,6 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6462,59 +6428,54 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128953978</t>
+          <t>https://artportalen.se/Sighting/136974114</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128953973</v>
+        <v>136974115</v>
       </c>
       <c r="B56" t="n">
-        <v>57950</v>
+        <v>93447</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>668704</v>
+        <v>668702</v>
       </c>
       <c r="R56" t="n">
-        <v>6691768</v>
+        <v>6691798</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6538,12 +6499,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6569,59 +6530,54 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128953973</t>
+          <t>https://artportalen.se/Sighting/136974115</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128953974</v>
+        <v>136974117</v>
       </c>
       <c r="B57" t="n">
-        <v>57950</v>
+        <v>93447</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>668675</v>
+        <v>668734</v>
       </c>
       <c r="R57" t="n">
-        <v>6691565</v>
+        <v>6691842</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6645,12 +6601,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6676,59 +6632,54 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128953974</t>
+          <t>https://artportalen.se/Sighting/136974117</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128260539</v>
+        <v>136974118</v>
       </c>
       <c r="B58" t="n">
-        <v>57141</v>
+        <v>93447</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100138</v>
+        <v>5964</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>668536</v>
+        <v>668739</v>
       </c>
       <c r="R58" t="n">
-        <v>6691824</v>
+        <v>6691890</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6752,17 +6703,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Balgrop med fjädrar</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6788,59 +6734,54 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260539</t>
+          <t>https://artportalen.se/Sighting/136974118</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132894827</v>
+        <v>136824829</v>
       </c>
       <c r="B59" t="n">
-        <v>57162</v>
+        <v>93449</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Östensbo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>668548</v>
+        <v>668559</v>
       </c>
       <c r="R59" t="n">
-        <v>6691834</v>
+        <v>6691668</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6864,17 +6805,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Lämpligt tjäderhabitat</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6900,56 +6836,51 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132894827</t>
+          <t>https://artportalen.se/Sighting/136824829</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>136824810</v>
+        <v>136824830</v>
       </c>
       <c r="B60" t="n">
-        <v>57195</v>
+        <v>93449</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>668526</v>
+        <v>668441</v>
       </c>
       <c r="R60" t="n">
-        <v>6691693</v>
+        <v>6691846</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6984,11 +6915,6 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Fjäder av tupp.</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -7012,38 +6938,38 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824810</t>
+          <t>https://artportalen.se/Sighting/136824830</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128953999</v>
+        <v>136974101</v>
       </c>
       <c r="B61" t="n">
-        <v>5179</v>
+        <v>93449</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100526</v>
+        <v>5966</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7053,13 +6979,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>668676</v>
+        <v>668523</v>
       </c>
       <c r="R61" t="n">
-        <v>6691605</v>
+        <v>6691688</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7083,12 +7009,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7097,24 +7023,8 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7130,54 +7040,54 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128953999</t>
+          <t>https://artportalen.se/Sighting/136974101</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125807887</v>
+        <v>136974102</v>
       </c>
       <c r="B62" t="n">
-        <v>4781</v>
+        <v>93449</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>102306</v>
+        <v>5966</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>668279</v>
+        <v>668518</v>
       </c>
       <c r="R62" t="n">
-        <v>6691905</v>
+        <v>6691672</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7201,12 +7111,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7217,21 +7127,6 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7247,51 +7142,51 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125807887</t>
+          <t>https://artportalen.se/Sighting/136974102</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125807888</v>
+        <v>127382931</v>
       </c>
       <c r="B63" t="n">
-        <v>4781</v>
+        <v>79946</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>102306</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>668255</v>
+        <v>668378</v>
       </c>
       <c r="R63" t="n">
-        <v>6691905</v>
+        <v>6691942</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7318,12 +7213,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7337,17 +7232,17 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7364,16 +7259,16 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125807888</t>
+          <t>https://artportalen.se/Sighting/127382931</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127382960</v>
+        <v>128953977</v>
       </c>
       <c r="B64" t="n">
-        <v>4781</v>
+        <v>80336</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7381,34 +7276,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>102306</v>
+        <v>6456</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>668228</v>
+        <v>668697</v>
       </c>
       <c r="R64" t="n">
-        <v>6691916</v>
+        <v>6691561</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7435,12 +7333,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7449,22 +7347,23 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -7481,16 +7380,16 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127382960</t>
+          <t>https://artportalen.se/Sighting/128953977</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128260581</v>
+        <v>128953978</v>
       </c>
       <c r="B65" t="n">
-        <v>4781</v>
+        <v>80336</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7498,21 +7397,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>102306</v>
+        <v>6456</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7522,13 +7421,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>668437</v>
+        <v>668684</v>
       </c>
       <c r="R65" t="n">
-        <v>6691726</v>
+        <v>6691557</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7552,12 +7451,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7571,17 +7470,17 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -7598,16 +7497,16 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260581</t>
+          <t>https://artportalen.se/Sighting/128953978</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128260582</v>
+        <v>128953973</v>
       </c>
       <c r="B66" t="n">
-        <v>4781</v>
+        <v>57950</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7615,37 +7514,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>668444</v>
+        <v>668704</v>
       </c>
       <c r="R66" t="n">
-        <v>6691724</v>
+        <v>6691768</v>
       </c>
       <c r="S66" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7669,12 +7573,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7685,21 +7589,6 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -7715,16 +7604,16 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260582</t>
+          <t>https://artportalen.se/Sighting/128953973</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128260583</v>
+        <v>128953974</v>
       </c>
       <c r="B67" t="n">
-        <v>4781</v>
+        <v>57950</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7732,37 +7621,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>668540</v>
+        <v>668675</v>
       </c>
       <c r="R67" t="n">
-        <v>6691905</v>
+        <v>6691565</v>
       </c>
       <c r="S67" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7786,12 +7680,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7802,21 +7696,6 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -7832,16 +7711,16 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260583</t>
+          <t>https://artportalen.se/Sighting/128953974</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128344139</v>
+        <v>128260539</v>
       </c>
       <c r="B68" t="n">
-        <v>4781</v>
+        <v>57141</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7849,37 +7728,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>102306</v>
+        <v>100138</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>668595</v>
+        <v>668536</v>
       </c>
       <c r="R68" t="n">
-        <v>6691931</v>
+        <v>6691824</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7909,6 +7793,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Balgrop med fjädrar</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7923,27 +7812,27 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128344139</t>
+          <t>https://artportalen.se/Sighting/128260539</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>136824221</v>
+        <v>132894827</v>
       </c>
       <c r="B69" t="n">
-        <v>4783</v>
+        <v>57162</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7951,37 +7840,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>102306</v>
+        <v>100138</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>668354</v>
+        <v>668548</v>
       </c>
       <c r="R69" t="n">
-        <v>6691795</v>
+        <v>6691834</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8005,12 +7899,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Lämpligt tjäderhabitat</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8021,21 +7920,6 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8051,44 +7935,44 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824221</t>
+          <t>https://artportalen.se/Sighting/132894827</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128260540</v>
+        <v>136824810</v>
       </c>
       <c r="B70" t="n">
-        <v>58114</v>
+        <v>57195</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8097,13 +7981,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>668462</v>
+        <v>668526</v>
       </c>
       <c r="R70" t="n">
-        <v>6691745</v>
+        <v>6691693</v>
       </c>
       <c r="S70" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8127,12 +8011,17 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Fjäder av tupp.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8158,62 +8047,54 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260540</t>
+          <t>https://artportalen.se/Sighting/136824810</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128260541</v>
+        <v>128953999</v>
       </c>
       <c r="B71" t="n">
-        <v>58114</v>
+        <v>5179</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>668559</v>
+        <v>668676</v>
       </c>
       <c r="R71" t="n">
-        <v>6691737</v>
+        <v>6691605</v>
       </c>
       <c r="S71" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8237,12 +8118,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8251,8 +8132,24 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -8268,59 +8165,54 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260541</t>
+          <t>https://artportalen.se/Sighting/128953999</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>136824814</v>
+        <v>125807887</v>
       </c>
       <c r="B72" t="n">
-        <v>58169</v>
+        <v>4781</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103021</v>
+        <v>102306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>668527</v>
+        <v>668279</v>
       </c>
       <c r="R72" t="n">
-        <v>6691698</v>
+        <v>6691905</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8344,12 +8236,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8360,6 +8252,21 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -8375,16 +8282,16 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824814</t>
+          <t>https://artportalen.se/Sighting/125807887</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125853673</v>
+        <v>125807888</v>
       </c>
       <c r="B73" t="n">
-        <v>99035</v>
+        <v>4781</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8392,37 +8299,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>219790</v>
+        <v>102306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>668269</v>
+        <v>668255</v>
       </c>
       <c r="R73" t="n">
-        <v>6691918</v>
+        <v>6691905</v>
       </c>
       <c r="S73" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8462,31 +8369,46 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Eva-Lena1 Rådberg</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Eva-Lena1 Rådberg</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125853673</t>
+          <t>https://artportalen.se/Sighting/125807888</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125855915</v>
+        <v>127382960</v>
       </c>
       <c r="B74" t="n">
-        <v>99035</v>
+        <v>4781</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8494,37 +8416,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>219790</v>
+        <v>102306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>668328</v>
+        <v>668228</v>
       </c>
       <c r="R74" t="n">
-        <v>6691847</v>
+        <v>6691916</v>
       </c>
       <c r="S74" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8548,12 +8470,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8564,31 +8486,46 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125855915</t>
+          <t>https://artportalen.se/Sighting/127382960</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128344142</v>
+        <v>128260581</v>
       </c>
       <c r="B75" t="n">
-        <v>99035</v>
+        <v>4781</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8596,37 +8533,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>219790</v>
+        <v>102306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>668540</v>
+        <v>668437</v>
       </c>
       <c r="R75" t="n">
-        <v>6691947</v>
+        <v>6691726</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8666,31 +8603,46 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128344142</t>
+          <t>https://artportalen.se/Sighting/128260581</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>136824822</v>
+        <v>128260582</v>
       </c>
       <c r="B76" t="n">
-        <v>99331</v>
+        <v>4781</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8698,21 +8650,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>219798</v>
+        <v>102306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8722,13 +8674,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>668779</v>
+        <v>668444</v>
       </c>
       <c r="R76" t="n">
-        <v>6691909</v>
+        <v>6691724</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8752,12 +8704,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8768,6 +8720,21 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -8783,16 +8750,16 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824822</t>
+          <t>https://artportalen.se/Sighting/128260582</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>136824842</v>
+        <v>128260583</v>
       </c>
       <c r="B77" t="n">
-        <v>108378</v>
+        <v>4781</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8800,21 +8767,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220083</v>
+        <v>102306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8824,13 +8791,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>668688</v>
+        <v>668540</v>
       </c>
       <c r="R77" t="n">
-        <v>6691747</v>
+        <v>6691905</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8854,12 +8821,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8870,6 +8837,21 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -8885,16 +8867,16 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824842</t>
+          <t>https://artportalen.se/Sighting/128260583</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>136824843</v>
+        <v>128344139</v>
       </c>
       <c r="B78" t="n">
-        <v>108378</v>
+        <v>4781</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8902,34 +8884,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220083</v>
+        <v>102306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>668780</v>
+        <v>668595</v>
       </c>
       <c r="R78" t="n">
-        <v>6691947</v>
+        <v>6691931</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8956,12 +8938,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8976,74 +8958,65 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824843</t>
+          <t>https://artportalen.se/Sighting/128344139</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128260575</v>
+        <v>136824221</v>
       </c>
       <c r="B79" t="n">
-        <v>99118</v>
+        <v>4783</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>668568</v>
+        <v>668354</v>
       </c>
       <c r="R79" t="n">
-        <v>6691681</v>
+        <v>6691795</v>
       </c>
       <c r="S79" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9067,12 +9040,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9083,6 +9056,21 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -9098,54 +9086,59 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260575</t>
+          <t>https://artportalen.se/Sighting/136824221</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128344136</v>
+        <v>128260540</v>
       </c>
       <c r="B80" t="n">
-        <v>99118</v>
+        <v>58114</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>668558</v>
+        <v>668462</v>
       </c>
       <c r="R80" t="n">
-        <v>6691675</v>
+        <v>6691745</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9175,11 +9168,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9194,65 +9182,73 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128344136</t>
+          <t>https://artportalen.se/Sighting/128260540</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125855908</v>
+        <v>128260541</v>
       </c>
       <c r="B81" t="n">
-        <v>106244</v>
+        <v>58114</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>668294</v>
+        <v>668559</v>
       </c>
       <c r="R81" t="n">
-        <v>6691884</v>
+        <v>6691737</v>
       </c>
       <c r="S81" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9276,12 +9272,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9296,65 +9292,70 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125855908</t>
+          <t>https://artportalen.se/Sighting/128260541</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128260577</v>
+        <v>136824814</v>
       </c>
       <c r="B82" t="n">
-        <v>106244</v>
+        <v>58169</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>668565</v>
+        <v>668527</v>
       </c>
       <c r="R82" t="n">
-        <v>6691734</v>
+        <v>6691698</v>
       </c>
       <c r="S82" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9378,12 +9379,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9409,16 +9410,16 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260577</t>
+          <t>https://artportalen.se/Sighting/136824814</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128344138</v>
+        <v>125853673</v>
       </c>
       <c r="B83" t="n">
-        <v>106244</v>
+        <v>99035</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9426,21 +9427,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221144</v>
+        <v>219790</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9450,13 +9451,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>668564</v>
+        <v>668269</v>
       </c>
       <c r="R83" t="n">
-        <v>6691753</v>
+        <v>6691918</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9480,12 +9481,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9500,27 +9501,27 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Eva-Lena1 Rådberg</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Eva-Lena1 Rådberg</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128344138</t>
+          <t>https://artportalen.se/Sighting/125853673</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132894835</v>
+        <v>125855915</v>
       </c>
       <c r="B84" t="n">
-        <v>106324</v>
+        <v>99035</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9528,37 +9529,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221144</v>
+        <v>219790</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Östensbo, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>668570</v>
+        <v>668328</v>
       </c>
       <c r="R84" t="n">
-        <v>6691835</v>
+        <v>6691847</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9582,17 +9583,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9607,27 +9603,27 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132894835</t>
+          <t>https://artportalen.se/Sighting/125855915</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>136824837</v>
+        <v>128344142</v>
       </c>
       <c r="B85" t="n">
-        <v>106494</v>
+        <v>99035</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9635,34 +9631,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>221144</v>
+        <v>219790</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>668380</v>
+        <v>668540</v>
       </c>
       <c r="R85" t="n">
-        <v>6691865</v>
+        <v>6691947</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9689,12 +9685,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9709,49 +9705,49 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824837</t>
+          <t>https://artportalen.se/Sighting/128344142</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>136824800</v>
+        <v>136824822</v>
       </c>
       <c r="B86" t="n">
-        <v>102479</v>
+        <v>99331</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221235</v>
+        <v>219798</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9822,38 +9818,38 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824800</t>
+          <t>https://artportalen.se/Sighting/136824822</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>136824801</v>
+        <v>136824842</v>
       </c>
       <c r="B87" t="n">
-        <v>102479</v>
+        <v>108378</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221235</v>
+        <v>220083</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9863,10 +9859,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>668791</v>
+        <v>668688</v>
       </c>
       <c r="R87" t="n">
-        <v>6691921</v>
+        <v>6691747</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9924,16 +9920,16 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824801</t>
+          <t>https://artportalen.se/Sighting/136824842</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128344123</v>
+        <v>136824843</v>
       </c>
       <c r="B88" t="n">
-        <v>104628</v>
+        <v>108378</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9941,34 +9937,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>222412</v>
+        <v>220083</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>668604</v>
+        <v>668780</v>
       </c>
       <c r="R88" t="n">
-        <v>6691663</v>
+        <v>6691947</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9995,12 +9991,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10015,65 +10011,74 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128344123</t>
+          <t>https://artportalen.se/Sighting/136824843</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>136824811</v>
+        <v>128260575</v>
       </c>
       <c r="B89" t="n">
-        <v>104876</v>
+        <v>99118</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>222412</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>668677</v>
+        <v>668568</v>
       </c>
       <c r="R89" t="n">
-        <v>6691727</v>
+        <v>6691681</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10097,12 +10102,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10128,51 +10133,51 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824811</t>
+          <t>https://artportalen.se/Sighting/128260575</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>136824812</v>
+        <v>128344136</v>
       </c>
       <c r="B90" t="n">
-        <v>104876</v>
+        <v>99118</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>222412</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>668727</v>
+        <v>668558</v>
       </c>
       <c r="R90" t="n">
-        <v>6691836</v>
+        <v>6691675</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10199,12 +10204,17 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>21</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10219,49 +10229,49 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824812</t>
+          <t>https://artportalen.se/Sighting/128344136</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128260592</v>
+        <v>136974104</v>
       </c>
       <c r="B91" t="n">
-        <v>101326</v>
+        <v>99353</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10271,13 +10281,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>668587</v>
+        <v>668583</v>
       </c>
       <c r="R91" t="n">
-        <v>6691690</v>
+        <v>6691676</v>
       </c>
       <c r="S91" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10301,12 +10311,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10332,16 +10342,16 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260592</t>
+          <t>https://artportalen.se/Sighting/136974104</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128260593</v>
+        <v>125855908</v>
       </c>
       <c r="B92" t="n">
-        <v>101326</v>
+        <v>106244</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10349,37 +10359,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>668593</v>
+        <v>668294</v>
       </c>
       <c r="R92" t="n">
-        <v>6691674</v>
+        <v>6691884</v>
       </c>
       <c r="S92" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10403,12 +10413,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10423,27 +10433,27 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260593</t>
+          <t>https://artportalen.se/Sighting/125855908</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128953994</v>
+        <v>128260577</v>
       </c>
       <c r="B93" t="n">
-        <v>101325</v>
+        <v>106244</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10451,21 +10461,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10475,13 +10485,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>668674</v>
+        <v>668565</v>
       </c>
       <c r="R93" t="n">
-        <v>6691735</v>
+        <v>6691734</v>
       </c>
       <c r="S93" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10505,12 +10515,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10536,16 +10546,16 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128953994</t>
+          <t>https://artportalen.se/Sighting/128260577</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128953995</v>
+        <v>128344138</v>
       </c>
       <c r="B94" t="n">
-        <v>101325</v>
+        <v>106244</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10553,37 +10563,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>668644</v>
+        <v>668564</v>
       </c>
       <c r="R94" t="n">
-        <v>6691674</v>
+        <v>6691753</v>
       </c>
       <c r="S94" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10607,12 +10617,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10627,27 +10637,27 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128953995</t>
+          <t>https://artportalen.se/Sighting/128344138</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128953996</v>
+        <v>132894835</v>
       </c>
       <c r="B95" t="n">
-        <v>101325</v>
+        <v>106324</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10655,34 +10665,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>668650</v>
+        <v>668570</v>
       </c>
       <c r="R95" t="n">
-        <v>6691592</v>
+        <v>6691835</v>
       </c>
       <c r="S95" t="n">
         <v>15</v>
@@ -10709,12 +10719,17 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10740,16 +10755,16 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128953996</t>
+          <t>https://artportalen.se/Sighting/132894835</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128953997</v>
+        <v>136824837</v>
       </c>
       <c r="B96" t="n">
-        <v>101325</v>
+        <v>106494</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10757,21 +10772,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10781,13 +10796,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>668641</v>
+        <v>668380</v>
       </c>
       <c r="R96" t="n">
-        <v>6691647</v>
+        <v>6691865</v>
       </c>
       <c r="S96" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10811,12 +10826,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10842,38 +10857,38 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128953997</t>
+          <t>https://artportalen.se/Sighting/136824837</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128953998</v>
+        <v>136824800</v>
       </c>
       <c r="B97" t="n">
-        <v>101325</v>
+        <v>102479</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10883,13 +10898,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>668653</v>
+        <v>668779</v>
       </c>
       <c r="R97" t="n">
-        <v>6691655</v>
+        <v>6691909</v>
       </c>
       <c r="S97" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10913,12 +10928,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10944,38 +10959,38 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128953998</t>
+          <t>https://artportalen.se/Sighting/136824800</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>136824845</v>
+        <v>136824801</v>
       </c>
       <c r="B98" t="n">
-        <v>101563</v>
+        <v>102479</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10985,10 +11000,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>668498</v>
+        <v>668791</v>
       </c>
       <c r="R98" t="n">
-        <v>6691758</v>
+        <v>6691921</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11046,16 +11061,16 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824845</t>
+          <t>https://artportalen.se/Sighting/136824801</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>136824847</v>
+        <v>128344123</v>
       </c>
       <c r="B99" t="n">
-        <v>101563</v>
+        <v>104628</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11063,34 +11078,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>668588</v>
+        <v>668604</v>
       </c>
       <c r="R99" t="n">
-        <v>6691652</v>
+        <v>6691663</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11117,12 +11132,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11137,27 +11152,27 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824847</t>
+          <t>https://artportalen.se/Sighting/128344123</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>136824848</v>
+        <v>136824811</v>
       </c>
       <c r="B100" t="n">
-        <v>101563</v>
+        <v>104876</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11165,21 +11180,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11189,10 +11204,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>668632</v>
+        <v>668677</v>
       </c>
       <c r="R100" t="n">
-        <v>6691628</v>
+        <v>6691727</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11250,16 +11265,16 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824848</t>
+          <t>https://artportalen.se/Sighting/136824811</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>136824849</v>
+        <v>136824812</v>
       </c>
       <c r="B101" t="n">
-        <v>101563</v>
+        <v>104876</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11267,21 +11282,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11291,10 +11306,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>668654</v>
+        <v>668727</v>
       </c>
       <c r="R101" t="n">
-        <v>6691662</v>
+        <v>6691836</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11352,16 +11367,16 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824849</t>
+          <t>https://artportalen.se/Sighting/136824812</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>136824850</v>
+        <v>128260592</v>
       </c>
       <c r="B102" t="n">
-        <v>101563</v>
+        <v>101326</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11393,13 +11408,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>668651</v>
+        <v>668587</v>
       </c>
       <c r="R102" t="n">
-        <v>6691668</v>
+        <v>6691690</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11423,12 +11438,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11454,16 +11469,16 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824850</t>
+          <t>https://artportalen.se/Sighting/128260592</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>136824851</v>
+        <v>128260593</v>
       </c>
       <c r="B103" t="n">
-        <v>101563</v>
+        <v>101326</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11495,13 +11510,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>668681</v>
+        <v>668593</v>
       </c>
       <c r="R103" t="n">
-        <v>6691734</v>
+        <v>6691674</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11525,12 +11540,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11556,16 +11571,16 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824851</t>
+          <t>https://artportalen.se/Sighting/128260593</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>136824852</v>
+        <v>128953994</v>
       </c>
       <c r="B104" t="n">
-        <v>101563</v>
+        <v>101325</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11597,13 +11612,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>668688</v>
+        <v>668674</v>
       </c>
       <c r="R104" t="n">
-        <v>6691747</v>
+        <v>6691735</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11627,12 +11642,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11658,16 +11673,16 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824852</t>
+          <t>https://artportalen.se/Sighting/128953994</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>136824853</v>
+        <v>128953995</v>
       </c>
       <c r="B105" t="n">
-        <v>101563</v>
+        <v>101325</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11699,13 +11714,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>668715</v>
+        <v>668644</v>
       </c>
       <c r="R105" t="n">
-        <v>6691784</v>
+        <v>6691674</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11729,12 +11744,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11760,16 +11775,16 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824853</t>
+          <t>https://artportalen.se/Sighting/128953995</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>136824854</v>
+        <v>128953996</v>
       </c>
       <c r="B106" t="n">
-        <v>101563</v>
+        <v>101325</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11801,13 +11816,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>668727</v>
+        <v>668650</v>
       </c>
       <c r="R106" t="n">
-        <v>6691836</v>
+        <v>6691592</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11831,12 +11846,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11862,16 +11877,16 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824854</t>
+          <t>https://artportalen.se/Sighting/128953996</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>136824825</v>
+        <v>128953997</v>
       </c>
       <c r="B107" t="n">
-        <v>99159</v>
+        <v>101325</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11879,21 +11894,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>223049</v>
+        <v>222498</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11903,13 +11918,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>668715</v>
+        <v>668641</v>
       </c>
       <c r="R107" t="n">
-        <v>6691784</v>
+        <v>6691647</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11933,12 +11948,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11964,16 +11979,16 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824825</t>
+          <t>https://artportalen.se/Sighting/128953997</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128953986</v>
+        <v>128953998</v>
       </c>
       <c r="B108" t="n">
-        <v>80392</v>
+        <v>101325</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11981,21 +11996,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>229497</v>
+        <v>222498</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12005,10 +12020,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>668686</v>
+        <v>668653</v>
       </c>
       <c r="R108" t="n">
-        <v>6691559</v>
+        <v>6691655</v>
       </c>
       <c r="S108" t="n">
         <v>15</v>
@@ -12052,21 +12067,6 @@
       <c r="AG108" t="b">
         <v>0</v>
       </c>
-      <c r="AJ108" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK108" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO108" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
@@ -12081,7 +12081,1251 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/128953998</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>136824845</v>
+      </c>
+      <c r="B109" t="n">
+        <v>101563</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>668498</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6691758</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136824845</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>136824847</v>
+      </c>
+      <c r="B110" t="n">
+        <v>101563</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>668588</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6691652</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136824847</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>136824848</v>
+      </c>
+      <c r="B111" t="n">
+        <v>101563</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>668632</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6691628</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136824848</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>136824849</v>
+      </c>
+      <c r="B112" t="n">
+        <v>101563</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>668654</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6691662</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136824849</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>136824850</v>
+      </c>
+      <c r="B113" t="n">
+        <v>101563</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>668651</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6691668</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136824850</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>136824851</v>
+      </c>
+      <c r="B114" t="n">
+        <v>101563</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>668681</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6691734</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136824851</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>136824852</v>
+      </c>
+      <c r="B115" t="n">
+        <v>101563</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>668688</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6691747</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136824852</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>136824853</v>
+      </c>
+      <c r="B116" t="n">
+        <v>101563</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>668715</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6691784</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136824853</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>136824854</v>
+      </c>
+      <c r="B117" t="n">
+        <v>101563</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>668727</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6691836</v>
+      </c>
+      <c r="S117" t="n">
+        <v>10</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136824854</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>136824825</v>
+      </c>
+      <c r="B118" t="n">
+        <v>99159</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>668715</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6691784</v>
+      </c>
+      <c r="S118" t="n">
+        <v>10</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136824825</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>128953986</v>
+      </c>
+      <c r="B119" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>668686</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6691559</v>
+      </c>
+      <c r="S119" t="n">
+        <v>15</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK119" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/128953986</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>136974125</v>
+      </c>
+      <c r="B120" t="n">
+        <v>87501</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>249228</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Barrfagerspindling</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Cortinarius piceae</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Frøslev &amp; al.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>668444</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6691727</v>
+      </c>
+      <c r="S120" t="n">
+        <v>10</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>KOH brun på hatten. Ingen tydlig reaktion i övrigt. Vit mycelsträng. Ingen tydlig doft.</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136974125</t>
         </is>
       </c>
     </row>
@@ -12194,6 +13438,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 19253-2026 artfynd.xlsx
+++ b/artfynd/A 19253-2026 artfynd.xlsx
@@ -1529,7 +1529,7 @@
         <v>136824805</v>
       </c>
       <c r="B10" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>136824806</v>
       </c>
       <c r="B11" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>136824807</v>
       </c>
       <c r="B12" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>136974111</v>
       </c>
       <c r="B14" t="n">
-        <v>85699</v>
+        <v>85703</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>136824809</v>
       </c>
       <c r="B18" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>136824836</v>
       </c>
       <c r="B20" t="n">
-        <v>92466</v>
+        <v>92468</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>136824831</v>
       </c>
       <c r="B21" t="n">
-        <v>96565</v>
+        <v>96571</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
         <v>136824832</v>
       </c>
       <c r="B22" t="n">
-        <v>96565</v>
+        <v>96571</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>136824833</v>
       </c>
       <c r="B23" t="n">
-        <v>96565</v>
+        <v>96571</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         <v>136824816</v>
       </c>
       <c r="B25" t="n">
-        <v>96688</v>
+        <v>96694</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>136974096</v>
       </c>
       <c r="B31" t="n">
-        <v>91889</v>
+        <v>91891</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
         <v>136974097</v>
       </c>
       <c r="B32" t="n">
-        <v>87553</v>
+        <v>87555</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
         <v>136824828</v>
       </c>
       <c r="B33" t="n">
-        <v>87324</v>
+        <v>87326</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>136974098</v>
       </c>
       <c r="B34" t="n">
-        <v>87324</v>
+        <v>87326</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>136824823</v>
       </c>
       <c r="B39" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>136824824</v>
       </c>
       <c r="B40" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5494,7 +5494,7 @@
         <v>136824808</v>
       </c>
       <c r="B47" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>136824839</v>
       </c>
       <c r="B52" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6126,7 +6126,7 @@
         <v>136824840</v>
       </c>
       <c r="B53" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         <v>136824841</v>
       </c>
       <c r="B54" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>136974114</v>
       </c>
       <c r="B55" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>136974115</v>
       </c>
       <c r="B56" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         <v>136974117</v>
       </c>
       <c r="B57" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6641,7 +6641,7 @@
         <v>136974118</v>
       </c>
       <c r="B58" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>136824829</v>
       </c>
       <c r="B59" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v>136824830</v>
       </c>
       <c r="B60" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>136974101</v>
       </c>
       <c r="B61" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         <v>136974102</v>
       </c>
       <c r="B62" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>136824822</v>
       </c>
       <c r="B86" t="n">
-        <v>99331</v>
+        <v>99337</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>136824842</v>
       </c>
       <c r="B87" t="n">
-        <v>108378</v>
+        <v>108384</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         <v>136824843</v>
       </c>
       <c r="B88" t="n">
-        <v>108378</v>
+        <v>108384</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>136974104</v>
       </c>
       <c r="B91" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10764,7 +10764,7 @@
         <v>136824837</v>
       </c>
       <c r="B96" t="n">
-        <v>106494</v>
+        <v>106500</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10866,7 +10866,7 @@
         <v>136824800</v>
       </c>
       <c r="B97" t="n">
-        <v>102479</v>
+        <v>102485</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10968,7 +10968,7 @@
         <v>136824801</v>
       </c>
       <c r="B98" t="n">
-        <v>102479</v>
+        <v>102485</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>136824811</v>
       </c>
       <c r="B100" t="n">
-        <v>104876</v>
+        <v>104882</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11274,7 +11274,7 @@
         <v>136824812</v>
       </c>
       <c r="B101" t="n">
-        <v>104876</v>
+        <v>104882</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>136824845</v>
       </c>
       <c r="B109" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12192,7 +12192,7 @@
         <v>136824847</v>
       </c>
       <c r="B110" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12294,7 +12294,7 @@
         <v>136824848</v>
       </c>
       <c r="B111" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12396,7 +12396,7 @@
         <v>136824849</v>
       </c>
       <c r="B112" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12498,7 +12498,7 @@
         <v>136824850</v>
       </c>
       <c r="B113" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12600,7 +12600,7 @@
         <v>136824851</v>
       </c>
       <c r="B114" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12702,7 +12702,7 @@
         <v>136824852</v>
       </c>
       <c r="B115" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>136824853</v>
       </c>
       <c r="B116" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12906,7 +12906,7 @@
         <v>136824854</v>
       </c>
       <c r="B117" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13008,7 +13008,7 @@
         <v>136824825</v>
       </c>
       <c r="B118" t="n">
-        <v>99159</v>
+        <v>99165</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13227,7 +13227,7 @@
         <v>136974125</v>
       </c>
       <c r="B120" t="n">
-        <v>87501</v>
+        <v>87503</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>

--- a/artfynd/A 19253-2026 artfynd.xlsx
+++ b/artfynd/A 19253-2026 artfynd.xlsx
@@ -1529,7 +1529,7 @@
         <v>136824805</v>
       </c>
       <c r="B10" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>136824806</v>
       </c>
       <c r="B11" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>136824807</v>
       </c>
       <c r="B12" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>136974111</v>
       </c>
       <c r="B14" t="n">
-        <v>85703</v>
+        <v>85705</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         <v>136824809</v>
       </c>
       <c r="B18" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>136824836</v>
       </c>
       <c r="B20" t="n">
-        <v>92468</v>
+        <v>92470</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>136824831</v>
       </c>
       <c r="B21" t="n">
-        <v>96571</v>
+        <v>96573</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
         <v>136824832</v>
       </c>
       <c r="B22" t="n">
-        <v>96571</v>
+        <v>96573</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>136824833</v>
       </c>
       <c r="B23" t="n">
-        <v>96571</v>
+        <v>96573</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         <v>136824816</v>
       </c>
       <c r="B25" t="n">
-        <v>96694</v>
+        <v>96696</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>136974096</v>
       </c>
       <c r="B31" t="n">
-        <v>91891</v>
+        <v>91893</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
         <v>136974097</v>
       </c>
       <c r="B32" t="n">
-        <v>87555</v>
+        <v>87557</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
         <v>136824828</v>
       </c>
       <c r="B33" t="n">
-        <v>87326</v>
+        <v>87328</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>136974098</v>
       </c>
       <c r="B34" t="n">
-        <v>87326</v>
+        <v>87328</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>136824823</v>
       </c>
       <c r="B39" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>136824824</v>
       </c>
       <c r="B40" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5494,7 +5494,7 @@
         <v>136824808</v>
       </c>
       <c r="B47" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>136824839</v>
       </c>
       <c r="B52" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6126,7 +6126,7 @@
         <v>136824840</v>
       </c>
       <c r="B53" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         <v>136824841</v>
       </c>
       <c r="B54" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>136974114</v>
       </c>
       <c r="B55" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>136974115</v>
       </c>
       <c r="B56" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         <v>136974117</v>
       </c>
       <c r="B57" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6641,7 +6641,7 @@
         <v>136974118</v>
       </c>
       <c r="B58" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>136824829</v>
       </c>
       <c r="B59" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6845,7 +6845,7 @@
         <v>136824830</v>
       </c>
       <c r="B60" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>136974101</v>
       </c>
       <c r="B61" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         <v>136974102</v>
       </c>
       <c r="B62" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>136824822</v>
       </c>
       <c r="B86" t="n">
-        <v>99337</v>
+        <v>99339</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>136824842</v>
       </c>
       <c r="B87" t="n">
-        <v>108384</v>
+        <v>108386</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         <v>136824843</v>
       </c>
       <c r="B88" t="n">
-        <v>108384</v>
+        <v>108386</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>136974104</v>
       </c>
       <c r="B91" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10764,7 +10764,7 @@
         <v>136824837</v>
       </c>
       <c r="B96" t="n">
-        <v>106500</v>
+        <v>106502</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10866,7 +10866,7 @@
         <v>136824800</v>
       </c>
       <c r="B97" t="n">
-        <v>102485</v>
+        <v>102487</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10968,7 +10968,7 @@
         <v>136824801</v>
       </c>
       <c r="B98" t="n">
-        <v>102485</v>
+        <v>102487</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>136824811</v>
       </c>
       <c r="B100" t="n">
-        <v>104882</v>
+        <v>104884</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11274,7 +11274,7 @@
         <v>136824812</v>
       </c>
       <c r="B101" t="n">
-        <v>104882</v>
+        <v>104884</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>136824845</v>
       </c>
       <c r="B109" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12192,7 +12192,7 @@
         <v>136824847</v>
       </c>
       <c r="B110" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12294,7 +12294,7 @@
         <v>136824848</v>
       </c>
       <c r="B111" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12396,7 +12396,7 @@
         <v>136824849</v>
       </c>
       <c r="B112" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12498,7 +12498,7 @@
         <v>136824850</v>
       </c>
       <c r="B113" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12600,7 +12600,7 @@
         <v>136824851</v>
       </c>
       <c r="B114" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12702,7 +12702,7 @@
         <v>136824852</v>
       </c>
       <c r="B115" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>136824853</v>
       </c>
       <c r="B116" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12906,7 +12906,7 @@
         <v>136824854</v>
       </c>
       <c r="B117" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13008,7 +13008,7 @@
         <v>136824825</v>
       </c>
       <c r="B118" t="n">
-        <v>99165</v>
+        <v>99167</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13227,7 +13227,7 @@
         <v>136974125</v>
       </c>
       <c r="B120" t="n">
-        <v>87503</v>
+        <v>87505</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>

--- a/artfynd/A 19253-2026 artfynd.xlsx
+++ b/artfynd/A 19253-2026 artfynd.xlsx
@@ -1529,7 +1529,7 @@
         <v>136824805</v>
       </c>
       <c r="B10" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>136824806</v>
       </c>
       <c r="B11" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>136824807</v>
       </c>
       <c r="B12" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>137073743</v>
       </c>
       <c r="B13" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>137073744</v>
       </c>
       <c r="B14" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>136974111</v>
       </c>
       <c r="B16" t="n">
-        <v>85706</v>
+        <v>85708</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>137077964</v>
       </c>
       <c r="B17" t="n">
-        <v>87379</v>
+        <v>87385</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>137100339</v>
       </c>
       <c r="B18" t="n">
-        <v>87586</v>
+        <v>87592</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>136824809</v>
       </c>
       <c r="B22" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>137073745</v>
       </c>
       <c r="B23" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>137073746</v>
       </c>
       <c r="B24" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>137078005</v>
       </c>
       <c r="B25" t="n">
-        <v>92550</v>
+        <v>92556</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>137073793</v>
       </c>
       <c r="B27" t="n">
-        <v>92792</v>
+        <v>92798</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>136824836</v>
       </c>
       <c r="B28" t="n">
-        <v>92471</v>
+        <v>92477</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136824831</v>
       </c>
       <c r="B29" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>136824832</v>
       </c>
       <c r="B30" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>136824833</v>
       </c>
       <c r="B31" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>137078053</v>
       </c>
       <c r="B32" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>136824816</v>
       </c>
       <c r="B34" t="n">
-        <v>96697</v>
+        <v>96703</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>137073749</v>
       </c>
       <c r="B35" t="n">
-        <v>96697</v>
+        <v>96703</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>137073750</v>
       </c>
       <c r="B36" t="n">
-        <v>96697</v>
+        <v>96703</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>137073751</v>
       </c>
       <c r="B37" t="n">
-        <v>96697</v>
+        <v>96703</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>136974096</v>
       </c>
       <c r="B43" t="n">
-        <v>91894</v>
+        <v>91900</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>136974097</v>
       </c>
       <c r="B44" t="n">
-        <v>87558</v>
+        <v>87564</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         <v>137077497</v>
       </c>
       <c r="B45" t="n">
-        <v>87558</v>
+        <v>87564</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>136824828</v>
       </c>
       <c r="B46" t="n">
-        <v>87329</v>
+        <v>87335</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>136974098</v>
       </c>
       <c r="B47" t="n">
-        <v>87329</v>
+        <v>87335</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>137073761</v>
       </c>
       <c r="B48" t="n">
-        <v>87329</v>
+        <v>87335</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         <v>137073762</v>
       </c>
       <c r="B49" t="n">
-        <v>87329</v>
+        <v>87335</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>137073763</v>
       </c>
       <c r="B50" t="n">
-        <v>87329</v>
+        <v>87335</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>137073764</v>
       </c>
       <c r="B51" t="n">
-        <v>87329</v>
+        <v>87335</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>137073765</v>
       </c>
       <c r="B52" t="n">
-        <v>87329</v>
+        <v>87335</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>137073766</v>
       </c>
       <c r="B53" t="n">
-        <v>87329</v>
+        <v>87335</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         <v>137073767</v>
       </c>
       <c r="B54" t="n">
-        <v>87329</v>
+        <v>87335</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         <v>137077917</v>
       </c>
       <c r="B55" t="n">
-        <v>87329</v>
+        <v>87335</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Björn Bråvander, Ingemar Södergren, Klara Tellebo, Malin Hylland</t>
+          <t>Malin Hylland, Klara Tellebo, Ingemar Södergren, Björn Bråvander</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6545,7 +6545,7 @@
         <v>137078067</v>
       </c>
       <c r="B56" t="n">
-        <v>87329</v>
+        <v>87335</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         <v>137078239</v>
       </c>
       <c r="B57" t="n">
-        <v>87329</v>
+        <v>87335</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         <v>137073794</v>
       </c>
       <c r="B58" t="n">
-        <v>92514</v>
+        <v>92520</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
         <v>136824823</v>
       </c>
       <c r="B63" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         <v>136824824</v>
       </c>
       <c r="B64" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>137073758</v>
       </c>
       <c r="B65" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         <v>137073759</v>
       </c>
       <c r="B66" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>137077540</v>
       </c>
       <c r="B68" t="n">
-        <v>89283</v>
+        <v>89289</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>137073747</v>
       </c>
       <c r="B72" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         <v>137073748</v>
       </c>
       <c r="B73" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>137078402</v>
       </c>
       <c r="B74" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         <v>136824808</v>
       </c>
       <c r="B77" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>137073773</v>
       </c>
       <c r="B82" t="n">
-        <v>91625</v>
+        <v>91631</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>136824839</v>
       </c>
       <c r="B83" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>136824840</v>
       </c>
       <c r="B84" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>136824841</v>
       </c>
       <c r="B85" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         <v>136974114</v>
       </c>
       <c r="B86" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         <v>136974115</v>
       </c>
       <c r="B87" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         <v>136974117</v>
       </c>
       <c r="B88" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10071,7 +10071,7 @@
         <v>136974118</v>
       </c>
       <c r="B89" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10173,7 +10173,7 @@
         <v>137073777</v>
       </c>
       <c r="B90" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
         <v>137073778</v>
       </c>
       <c r="B91" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
         <v>137073779</v>
       </c>
       <c r="B92" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10479,7 +10479,7 @@
         <v>137073780</v>
       </c>
       <c r="B93" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         <v>137073781</v>
       </c>
       <c r="B94" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10683,7 +10683,7 @@
         <v>137073782</v>
       </c>
       <c r="B95" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>137073783</v>
       </c>
       <c r="B96" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>137073784</v>
       </c>
       <c r="B97" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>137073785</v>
       </c>
       <c r="B98" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>137073786</v>
       </c>
       <c r="B99" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11193,7 +11193,7 @@
         <v>137073787</v>
       </c>
       <c r="B100" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11295,7 +11295,7 @@
         <v>137073788</v>
       </c>
       <c r="B101" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11397,7 +11397,7 @@
         <v>137073789</v>
       </c>
       <c r="B102" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
         <v>137077585</v>
       </c>
       <c r="B103" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>137077941</v>
       </c>
       <c r="B104" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>137078025</v>
       </c>
       <c r="B105" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>137078049</v>
       </c>
       <c r="B106" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11990,7 +11990,7 @@
         <v>137078081</v>
       </c>
       <c r="B107" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>136824829</v>
       </c>
       <c r="B108" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>136824830</v>
       </c>
       <c r="B109" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>136974101</v>
       </c>
       <c r="B110" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12425,7 +12425,7 @@
         <v>136974102</v>
       </c>
       <c r="B111" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>137073771</v>
       </c>
       <c r="B112" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -15203,7 +15203,7 @@
         <v>136824822</v>
       </c>
       <c r="B136" t="n">
-        <v>99340</v>
+        <v>99346</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>137073756</v>
       </c>
       <c r="B137" t="n">
-        <v>99340</v>
+        <v>99346</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>137073757</v>
       </c>
       <c r="B138" t="n">
-        <v>99340</v>
+        <v>99346</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15509,7 +15509,7 @@
         <v>137077977</v>
       </c>
       <c r="B139" t="n">
-        <v>99340</v>
+        <v>99346</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15634,7 +15634,7 @@
         <v>136824842</v>
       </c>
       <c r="B140" t="n">
-        <v>108387</v>
+        <v>108393</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>136824843</v>
       </c>
       <c r="B141" t="n">
-        <v>108387</v>
+        <v>108393</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15838,7 +15838,7 @@
         <v>137077952</v>
       </c>
       <c r="B142" t="n">
-        <v>108387</v>
+        <v>108393</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>137073795</v>
       </c>
       <c r="B143" t="n">
-        <v>107073</v>
+        <v>107079</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16275,7 +16275,7 @@
         <v>136974104</v>
       </c>
       <c r="B146" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16790,7 +16790,7 @@
         <v>136824837</v>
       </c>
       <c r="B151" t="n">
-        <v>106503</v>
+        <v>106509</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16892,7 +16892,7 @@
         <v>136824800</v>
       </c>
       <c r="B152" t="n">
-        <v>102488</v>
+        <v>102494</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16994,7 +16994,7 @@
         <v>136824801</v>
       </c>
       <c r="B153" t="n">
-        <v>102488</v>
+        <v>102494</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>137073740</v>
       </c>
       <c r="B154" t="n">
-        <v>102488</v>
+        <v>102494</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17198,7 +17198,7 @@
         <v>137073741</v>
       </c>
       <c r="B155" t="n">
-        <v>102488</v>
+        <v>102494</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17300,7 +17300,7 @@
         <v>137073742</v>
       </c>
       <c r="B156" t="n">
-        <v>102488</v>
+        <v>102494</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17402,7 +17402,7 @@
         <v>137078125</v>
       </c>
       <c r="B157" t="n">
-        <v>102488</v>
+        <v>102494</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17519,7 +17519,7 @@
         <v>137073768</v>
       </c>
       <c r="B158" t="n">
-        <v>106858</v>
+        <v>106864</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17621,7 +17621,7 @@
         <v>137073769</v>
       </c>
       <c r="B159" t="n">
-        <v>106858</v>
+        <v>106864</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17825,7 +17825,7 @@
         <v>136824811</v>
       </c>
       <c r="B161" t="n">
-        <v>104885</v>
+        <v>104891</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17927,7 +17927,7 @@
         <v>136824812</v>
       </c>
       <c r="B162" t="n">
-        <v>104885</v>
+        <v>104891</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>136824845</v>
       </c>
       <c r="B170" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18845,7 +18845,7 @@
         <v>136824847</v>
       </c>
       <c r="B171" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         <v>136824848</v>
       </c>
       <c r="B172" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19049,7 +19049,7 @@
         <v>136824849</v>
       </c>
       <c r="B173" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19151,7 +19151,7 @@
         <v>136824850</v>
       </c>
       <c r="B174" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19253,7 +19253,7 @@
         <v>136824851</v>
       </c>
       <c r="B175" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19355,7 +19355,7 @@
         <v>136824852</v>
       </c>
       <c r="B176" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         <v>136824853</v>
       </c>
       <c r="B177" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19559,7 +19559,7 @@
         <v>136824854</v>
       </c>
       <c r="B178" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>137077942</v>
       </c>
       <c r="B179" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19778,7 +19778,7 @@
         <v>137078051</v>
       </c>
       <c r="B180" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19885,7 +19885,7 @@
         <v>136824825</v>
       </c>
       <c r="B181" t="n">
-        <v>99168</v>
+        <v>99174</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20104,7 +20104,7 @@
         <v>136974125</v>
       </c>
       <c r="B183" t="n">
-        <v>87506</v>
+        <v>87512</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>137076843</v>
       </c>
       <c r="B184" t="n">
-        <v>91592</v>
+        <v>91598</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
         <v>137078162</v>
       </c>
       <c r="B185" t="n">
-        <v>87529</v>
+        <v>87535</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>

--- a/artfynd/A 19253-2026 artfynd.xlsx
+++ b/artfynd/A 19253-2026 artfynd.xlsx
@@ -1529,7 +1529,7 @@
         <v>136824805</v>
       </c>
       <c r="B10" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>136824806</v>
       </c>
       <c r="B11" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>136824807</v>
       </c>
       <c r="B12" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>137073743</v>
       </c>
       <c r="B13" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>137073744</v>
       </c>
       <c r="B14" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>136974111</v>
       </c>
       <c r="B16" t="n">
-        <v>85708</v>
+        <v>85712</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>137077964</v>
       </c>
       <c r="B17" t="n">
-        <v>87385</v>
+        <v>87389</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>137100339</v>
       </c>
       <c r="B18" t="n">
-        <v>87592</v>
+        <v>87596</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>136824809</v>
       </c>
       <c r="B22" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>137073745</v>
       </c>
       <c r="B23" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>137073746</v>
       </c>
       <c r="B24" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>137078005</v>
       </c>
       <c r="B25" t="n">
-        <v>92556</v>
+        <v>92560</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>137073793</v>
       </c>
       <c r="B27" t="n">
-        <v>92798</v>
+        <v>92802</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>136824836</v>
       </c>
       <c r="B28" t="n">
-        <v>92477</v>
+        <v>92481</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136824831</v>
       </c>
       <c r="B29" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>136824832</v>
       </c>
       <c r="B30" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>136824833</v>
       </c>
       <c r="B31" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>137078053</v>
       </c>
       <c r="B32" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>136824816</v>
       </c>
       <c r="B34" t="n">
-        <v>96703</v>
+        <v>96707</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>137073749</v>
       </c>
       <c r="B35" t="n">
-        <v>96703</v>
+        <v>96707</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>137073750</v>
       </c>
       <c r="B36" t="n">
-        <v>96703</v>
+        <v>96707</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>137073751</v>
       </c>
       <c r="B37" t="n">
-        <v>96703</v>
+        <v>96707</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>136974096</v>
       </c>
       <c r="B43" t="n">
-        <v>91900</v>
+        <v>91904</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>136974097</v>
       </c>
       <c r="B44" t="n">
-        <v>87564</v>
+        <v>87568</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         <v>137077497</v>
       </c>
       <c r="B45" t="n">
-        <v>87564</v>
+        <v>87568</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>136824828</v>
       </c>
       <c r="B46" t="n">
-        <v>87335</v>
+        <v>87339</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>136974098</v>
       </c>
       <c r="B47" t="n">
-        <v>87335</v>
+        <v>87339</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>137073761</v>
       </c>
       <c r="B48" t="n">
-        <v>87335</v>
+        <v>87339</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         <v>137073762</v>
       </c>
       <c r="B49" t="n">
-        <v>87335</v>
+        <v>87339</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>137073763</v>
       </c>
       <c r="B50" t="n">
-        <v>87335</v>
+        <v>87339</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>137073764</v>
       </c>
       <c r="B51" t="n">
-        <v>87335</v>
+        <v>87339</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>137073765</v>
       </c>
       <c r="B52" t="n">
-        <v>87335</v>
+        <v>87339</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>137073766</v>
       </c>
       <c r="B53" t="n">
-        <v>87335</v>
+        <v>87339</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         <v>137073767</v>
       </c>
       <c r="B54" t="n">
-        <v>87335</v>
+        <v>87339</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         <v>137077917</v>
       </c>
       <c r="B55" t="n">
-        <v>87335</v>
+        <v>87339</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Malin Hylland, Klara Tellebo, Ingemar Södergren, Björn Bråvander</t>
+          <t>Björn Bråvander, Ingemar Södergren, Klara Tellebo, Malin Hylland</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6545,7 +6545,7 @@
         <v>137078067</v>
       </c>
       <c r="B56" t="n">
-        <v>87335</v>
+        <v>87339</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         <v>137078239</v>
       </c>
       <c r="B57" t="n">
-        <v>87335</v>
+        <v>87339</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         <v>137073794</v>
       </c>
       <c r="B58" t="n">
-        <v>92520</v>
+        <v>92524</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
         <v>136824823</v>
       </c>
       <c r="B63" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         <v>136824824</v>
       </c>
       <c r="B64" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>137073758</v>
       </c>
       <c r="B65" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         <v>137073759</v>
       </c>
       <c r="B66" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>137077540</v>
       </c>
       <c r="B68" t="n">
-        <v>89289</v>
+        <v>89293</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>137073747</v>
       </c>
       <c r="B72" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         <v>137073748</v>
       </c>
       <c r="B73" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>137078402</v>
       </c>
       <c r="B74" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         <v>136824808</v>
       </c>
       <c r="B77" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>137073773</v>
       </c>
       <c r="B82" t="n">
-        <v>91631</v>
+        <v>91635</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>136824839</v>
       </c>
       <c r="B83" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>136824840</v>
       </c>
       <c r="B84" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>136824841</v>
       </c>
       <c r="B85" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         <v>136974114</v>
       </c>
       <c r="B86" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         <v>136974115</v>
       </c>
       <c r="B87" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         <v>136974117</v>
       </c>
       <c r="B88" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10071,7 +10071,7 @@
         <v>136974118</v>
       </c>
       <c r="B89" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10173,7 +10173,7 @@
         <v>137073777</v>
       </c>
       <c r="B90" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
         <v>137073778</v>
       </c>
       <c r="B91" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
         <v>137073779</v>
       </c>
       <c r="B92" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10479,7 +10479,7 @@
         <v>137073780</v>
       </c>
       <c r="B93" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         <v>137073781</v>
       </c>
       <c r="B94" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10683,7 +10683,7 @@
         <v>137073782</v>
       </c>
       <c r="B95" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>137073783</v>
       </c>
       <c r="B96" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>137073784</v>
       </c>
       <c r="B97" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>137073785</v>
       </c>
       <c r="B98" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>137073786</v>
       </c>
       <c r="B99" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11193,7 +11193,7 @@
         <v>137073787</v>
       </c>
       <c r="B100" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11295,7 +11295,7 @@
         <v>137073788</v>
       </c>
       <c r="B101" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11397,7 +11397,7 @@
         <v>137073789</v>
       </c>
       <c r="B102" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
         <v>137077585</v>
       </c>
       <c r="B103" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>137077941</v>
       </c>
       <c r="B104" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>137078025</v>
       </c>
       <c r="B105" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>137078049</v>
       </c>
       <c r="B106" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11990,7 +11990,7 @@
         <v>137078081</v>
       </c>
       <c r="B107" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>136824829</v>
       </c>
       <c r="B108" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>136824830</v>
       </c>
       <c r="B109" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>136974101</v>
       </c>
       <c r="B110" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12425,7 +12425,7 @@
         <v>136974102</v>
       </c>
       <c r="B111" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>137073771</v>
       </c>
       <c r="B112" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -15203,7 +15203,7 @@
         <v>136824822</v>
       </c>
       <c r="B136" t="n">
-        <v>99346</v>
+        <v>99350</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>137073756</v>
       </c>
       <c r="B137" t="n">
-        <v>99346</v>
+        <v>99350</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>137073757</v>
       </c>
       <c r="B138" t="n">
-        <v>99346</v>
+        <v>99350</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15509,7 +15509,7 @@
         <v>137077977</v>
       </c>
       <c r="B139" t="n">
-        <v>99346</v>
+        <v>99350</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15634,7 +15634,7 @@
         <v>136824842</v>
       </c>
       <c r="B140" t="n">
-        <v>108393</v>
+        <v>108397</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>136824843</v>
       </c>
       <c r="B141" t="n">
-        <v>108393</v>
+        <v>108397</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15838,7 +15838,7 @@
         <v>137077952</v>
       </c>
       <c r="B142" t="n">
-        <v>108393</v>
+        <v>108397</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>137073795</v>
       </c>
       <c r="B143" t="n">
-        <v>107079</v>
+        <v>107083</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16275,7 +16275,7 @@
         <v>136974104</v>
       </c>
       <c r="B146" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16790,7 +16790,7 @@
         <v>136824837</v>
       </c>
       <c r="B151" t="n">
-        <v>106509</v>
+        <v>106513</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16892,7 +16892,7 @@
         <v>136824800</v>
       </c>
       <c r="B152" t="n">
-        <v>102494</v>
+        <v>102498</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16994,7 +16994,7 @@
         <v>136824801</v>
       </c>
       <c r="B153" t="n">
-        <v>102494</v>
+        <v>102498</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>137073740</v>
       </c>
       <c r="B154" t="n">
-        <v>102494</v>
+        <v>102498</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17198,7 +17198,7 @@
         <v>137073741</v>
       </c>
       <c r="B155" t="n">
-        <v>102494</v>
+        <v>102498</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17300,7 +17300,7 @@
         <v>137073742</v>
       </c>
       <c r="B156" t="n">
-        <v>102494</v>
+        <v>102498</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17402,7 +17402,7 @@
         <v>137078125</v>
       </c>
       <c r="B157" t="n">
-        <v>102494</v>
+        <v>102498</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17519,7 +17519,7 @@
         <v>137073768</v>
       </c>
       <c r="B158" t="n">
-        <v>106864</v>
+        <v>106868</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17621,7 +17621,7 @@
         <v>137073769</v>
       </c>
       <c r="B159" t="n">
-        <v>106864</v>
+        <v>106868</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17825,7 +17825,7 @@
         <v>136824811</v>
       </c>
       <c r="B161" t="n">
-        <v>104891</v>
+        <v>104895</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17927,7 +17927,7 @@
         <v>136824812</v>
       </c>
       <c r="B162" t="n">
-        <v>104891</v>
+        <v>104895</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>136824845</v>
       </c>
       <c r="B170" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18845,7 +18845,7 @@
         <v>136824847</v>
       </c>
       <c r="B171" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         <v>136824848</v>
       </c>
       <c r="B172" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19049,7 +19049,7 @@
         <v>136824849</v>
       </c>
       <c r="B173" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19151,7 +19151,7 @@
         <v>136824850</v>
       </c>
       <c r="B174" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19253,7 +19253,7 @@
         <v>136824851</v>
       </c>
       <c r="B175" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19355,7 +19355,7 @@
         <v>136824852</v>
       </c>
       <c r="B176" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         <v>136824853</v>
       </c>
       <c r="B177" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19559,7 +19559,7 @@
         <v>136824854</v>
       </c>
       <c r="B178" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>137077942</v>
       </c>
       <c r="B179" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19778,7 +19778,7 @@
         <v>137078051</v>
       </c>
       <c r="B180" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19885,7 +19885,7 @@
         <v>136824825</v>
       </c>
       <c r="B181" t="n">
-        <v>99174</v>
+        <v>99178</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20104,7 +20104,7 @@
         <v>136974125</v>
       </c>
       <c r="B183" t="n">
-        <v>87512</v>
+        <v>87516</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>137076843</v>
       </c>
       <c r="B184" t="n">
-        <v>91598</v>
+        <v>91602</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
         <v>137078162</v>
       </c>
       <c r="B185" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>

--- a/artfynd/A 19253-2026 artfynd.xlsx
+++ b/artfynd/A 19253-2026 artfynd.xlsx
@@ -1529,7 +1529,7 @@
         <v>136824805</v>
       </c>
       <c r="B10" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>136824806</v>
       </c>
       <c r="B11" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>136824807</v>
       </c>
       <c r="B12" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>137073743</v>
       </c>
       <c r="B13" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>137073744</v>
       </c>
       <c r="B14" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136824831</v>
       </c>
       <c r="B29" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>136824832</v>
       </c>
       <c r="B30" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>136824833</v>
       </c>
       <c r="B31" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>137078053</v>
       </c>
       <c r="B32" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>136824816</v>
       </c>
       <c r="B34" t="n">
-        <v>96707</v>
+        <v>96709</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>137073749</v>
       </c>
       <c r="B35" t="n">
-        <v>96707</v>
+        <v>96709</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>137073750</v>
       </c>
       <c r="B36" t="n">
-        <v>96707</v>
+        <v>96709</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>137073751</v>
       </c>
       <c r="B37" t="n">
-        <v>96707</v>
+        <v>96709</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -15203,7 +15203,7 @@
         <v>136824822</v>
       </c>
       <c r="B136" t="n">
-        <v>99350</v>
+        <v>99352</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>137073756</v>
       </c>
       <c r="B137" t="n">
-        <v>99350</v>
+        <v>99352</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>137073757</v>
       </c>
       <c r="B138" t="n">
-        <v>99350</v>
+        <v>99352</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15509,7 +15509,7 @@
         <v>137077977</v>
       </c>
       <c r="B139" t="n">
-        <v>99350</v>
+        <v>99352</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15634,7 +15634,7 @@
         <v>136824842</v>
       </c>
       <c r="B140" t="n">
-        <v>108397</v>
+        <v>108399</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>136824843</v>
       </c>
       <c r="B141" t="n">
-        <v>108397</v>
+        <v>108399</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15838,7 +15838,7 @@
         <v>137077952</v>
       </c>
       <c r="B142" t="n">
-        <v>108397</v>
+        <v>108399</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>137073795</v>
       </c>
       <c r="B143" t="n">
-        <v>107083</v>
+        <v>107085</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16275,7 +16275,7 @@
         <v>136974104</v>
       </c>
       <c r="B146" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16790,7 +16790,7 @@
         <v>136824837</v>
       </c>
       <c r="B151" t="n">
-        <v>106513</v>
+        <v>106515</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16892,7 +16892,7 @@
         <v>136824800</v>
       </c>
       <c r="B152" t="n">
-        <v>102498</v>
+        <v>102500</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16994,7 +16994,7 @@
         <v>136824801</v>
       </c>
       <c r="B153" t="n">
-        <v>102498</v>
+        <v>102500</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>137073740</v>
       </c>
       <c r="B154" t="n">
-        <v>102498</v>
+        <v>102500</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17198,7 +17198,7 @@
         <v>137073741</v>
       </c>
       <c r="B155" t="n">
-        <v>102498</v>
+        <v>102500</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17300,7 +17300,7 @@
         <v>137073742</v>
       </c>
       <c r="B156" t="n">
-        <v>102498</v>
+        <v>102500</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17402,7 +17402,7 @@
         <v>137078125</v>
       </c>
       <c r="B157" t="n">
-        <v>102498</v>
+        <v>102500</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17519,7 +17519,7 @@
         <v>137073768</v>
       </c>
       <c r="B158" t="n">
-        <v>106868</v>
+        <v>106870</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17621,7 +17621,7 @@
         <v>137073769</v>
       </c>
       <c r="B159" t="n">
-        <v>106868</v>
+        <v>106870</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17825,7 +17825,7 @@
         <v>136824811</v>
       </c>
       <c r="B161" t="n">
-        <v>104895</v>
+        <v>104897</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17927,7 +17927,7 @@
         <v>136824812</v>
       </c>
       <c r="B162" t="n">
-        <v>104895</v>
+        <v>104897</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>136824845</v>
       </c>
       <c r="B170" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18845,7 +18845,7 @@
         <v>136824847</v>
       </c>
       <c r="B171" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         <v>136824848</v>
       </c>
       <c r="B172" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19049,7 +19049,7 @@
         <v>136824849</v>
       </c>
       <c r="B173" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19151,7 +19151,7 @@
         <v>136824850</v>
       </c>
       <c r="B174" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19253,7 +19253,7 @@
         <v>136824851</v>
       </c>
       <c r="B175" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19355,7 +19355,7 @@
         <v>136824852</v>
       </c>
       <c r="B176" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         <v>136824853</v>
       </c>
       <c r="B177" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19559,7 +19559,7 @@
         <v>136824854</v>
       </c>
       <c r="B178" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>137077942</v>
       </c>
       <c r="B179" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19778,7 +19778,7 @@
         <v>137078051</v>
       </c>
       <c r="B180" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19885,7 +19885,7 @@
         <v>136824825</v>
       </c>
       <c r="B181" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>

--- a/artfynd/A 19253-2026 artfynd.xlsx
+++ b/artfynd/A 19253-2026 artfynd.xlsx
@@ -1529,7 +1529,7 @@
         <v>136824805</v>
       </c>
       <c r="B10" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>136824806</v>
       </c>
       <c r="B11" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>136824807</v>
       </c>
       <c r="B12" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>137073743</v>
       </c>
       <c r="B13" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>137073744</v>
       </c>
       <c r="B14" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>136974111</v>
       </c>
       <c r="B16" t="n">
-        <v>85712</v>
+        <v>85714</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>137077964</v>
       </c>
       <c r="B17" t="n">
-        <v>87389</v>
+        <v>87391</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>137100339</v>
       </c>
       <c r="B18" t="n">
-        <v>87596</v>
+        <v>87598</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>136824809</v>
       </c>
       <c r="B22" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>137073745</v>
       </c>
       <c r="B23" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>137073746</v>
       </c>
       <c r="B24" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>137078005</v>
       </c>
       <c r="B25" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>137073793</v>
       </c>
       <c r="B27" t="n">
-        <v>92802</v>
+        <v>92804</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>136824836</v>
       </c>
       <c r="B28" t="n">
-        <v>92481</v>
+        <v>92483</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136824831</v>
       </c>
       <c r="B29" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>136824832</v>
       </c>
       <c r="B30" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>136824833</v>
       </c>
       <c r="B31" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>137078053</v>
       </c>
       <c r="B32" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>136824816</v>
       </c>
       <c r="B34" t="n">
-        <v>96709</v>
+        <v>96711</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>137073749</v>
       </c>
       <c r="B35" t="n">
-        <v>96709</v>
+        <v>96711</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>137073750</v>
       </c>
       <c r="B36" t="n">
-        <v>96709</v>
+        <v>96711</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>137073751</v>
       </c>
       <c r="B37" t="n">
-        <v>96709</v>
+        <v>96711</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>136974096</v>
       </c>
       <c r="B43" t="n">
-        <v>91904</v>
+        <v>91906</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>136974097</v>
       </c>
       <c r="B44" t="n">
-        <v>87568</v>
+        <v>87570</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         <v>137077497</v>
       </c>
       <c r="B45" t="n">
-        <v>87568</v>
+        <v>87570</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>136824828</v>
       </c>
       <c r="B46" t="n">
-        <v>87339</v>
+        <v>87341</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>136974098</v>
       </c>
       <c r="B47" t="n">
-        <v>87339</v>
+        <v>87341</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>137073761</v>
       </c>
       <c r="B48" t="n">
-        <v>87339</v>
+        <v>87341</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         <v>137073762</v>
       </c>
       <c r="B49" t="n">
-        <v>87339</v>
+        <v>87341</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>137073763</v>
       </c>
       <c r="B50" t="n">
-        <v>87339</v>
+        <v>87341</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>137073764</v>
       </c>
       <c r="B51" t="n">
-        <v>87339</v>
+        <v>87341</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>137073765</v>
       </c>
       <c r="B52" t="n">
-        <v>87339</v>
+        <v>87341</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>137073766</v>
       </c>
       <c r="B53" t="n">
-        <v>87339</v>
+        <v>87341</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         <v>137073767</v>
       </c>
       <c r="B54" t="n">
-        <v>87339</v>
+        <v>87341</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         <v>137077917</v>
       </c>
       <c r="B55" t="n">
-        <v>87339</v>
+        <v>87341</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>137078067</v>
       </c>
       <c r="B56" t="n">
-        <v>87339</v>
+        <v>87341</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         <v>137078239</v>
       </c>
       <c r="B57" t="n">
-        <v>87339</v>
+        <v>87341</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         <v>137073794</v>
       </c>
       <c r="B58" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
         <v>136824823</v>
       </c>
       <c r="B63" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         <v>136824824</v>
       </c>
       <c r="B64" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>137073758</v>
       </c>
       <c r="B65" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         <v>137073759</v>
       </c>
       <c r="B66" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>137077540</v>
       </c>
       <c r="B68" t="n">
-        <v>89293</v>
+        <v>89295</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>137073747</v>
       </c>
       <c r="B72" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         <v>137073748</v>
       </c>
       <c r="B73" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>137078402</v>
       </c>
       <c r="B74" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         <v>136824808</v>
       </c>
       <c r="B77" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>137073773</v>
       </c>
       <c r="B82" t="n">
-        <v>91635</v>
+        <v>91637</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>136824839</v>
       </c>
       <c r="B83" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>136824840</v>
       </c>
       <c r="B84" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>136824841</v>
       </c>
       <c r="B85" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         <v>136974114</v>
       </c>
       <c r="B86" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         <v>136974115</v>
       </c>
       <c r="B87" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         <v>136974117</v>
       </c>
       <c r="B88" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10071,7 +10071,7 @@
         <v>136974118</v>
       </c>
       <c r="B89" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10173,7 +10173,7 @@
         <v>137073777</v>
       </c>
       <c r="B90" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
         <v>137073778</v>
       </c>
       <c r="B91" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
         <v>137073779</v>
       </c>
       <c r="B92" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10479,7 +10479,7 @@
         <v>137073780</v>
       </c>
       <c r="B93" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         <v>137073781</v>
       </c>
       <c r="B94" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10683,7 +10683,7 @@
         <v>137073782</v>
       </c>
       <c r="B95" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>137073783</v>
       </c>
       <c r="B96" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>137073784</v>
       </c>
       <c r="B97" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>137073785</v>
       </c>
       <c r="B98" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>137073786</v>
       </c>
       <c r="B99" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11193,7 +11193,7 @@
         <v>137073787</v>
       </c>
       <c r="B100" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11295,7 +11295,7 @@
         <v>137073788</v>
       </c>
       <c r="B101" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11397,7 +11397,7 @@
         <v>137073789</v>
       </c>
       <c r="B102" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
         <v>137077585</v>
       </c>
       <c r="B103" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>137077941</v>
       </c>
       <c r="B104" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Björn Bråvander, Ingemar Södergren, Klara Tellebo, Malin Hylland</t>
+          <t>Malin Hylland, Klara Tellebo, Ingemar Södergren, Björn Bråvander</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
@@ -11742,7 +11742,7 @@
         <v>137078025</v>
       </c>
       <c r="B105" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>137078049</v>
       </c>
       <c r="B106" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11990,7 +11990,7 @@
         <v>137078081</v>
       </c>
       <c r="B107" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>136824829</v>
       </c>
       <c r="B108" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>136824830</v>
       </c>
       <c r="B109" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>136974101</v>
       </c>
       <c r="B110" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12425,7 +12425,7 @@
         <v>136974102</v>
       </c>
       <c r="B111" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>137073771</v>
       </c>
       <c r="B112" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -15203,7 +15203,7 @@
         <v>136824822</v>
       </c>
       <c r="B136" t="n">
-        <v>99352</v>
+        <v>99354</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>137073756</v>
       </c>
       <c r="B137" t="n">
-        <v>99352</v>
+        <v>99354</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>137073757</v>
       </c>
       <c r="B138" t="n">
-        <v>99352</v>
+        <v>99354</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15509,7 +15509,7 @@
         <v>137077977</v>
       </c>
       <c r="B139" t="n">
-        <v>99352</v>
+        <v>99354</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15634,7 +15634,7 @@
         <v>136824842</v>
       </c>
       <c r="B140" t="n">
-        <v>108399</v>
+        <v>108401</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>136824843</v>
       </c>
       <c r="B141" t="n">
-        <v>108399</v>
+        <v>108401</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15838,7 +15838,7 @@
         <v>137077952</v>
       </c>
       <c r="B142" t="n">
-        <v>108399</v>
+        <v>108401</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>137073795</v>
       </c>
       <c r="B143" t="n">
-        <v>107085</v>
+        <v>107087</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16275,7 +16275,7 @@
         <v>136974104</v>
       </c>
       <c r="B146" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16790,7 +16790,7 @@
         <v>136824837</v>
       </c>
       <c r="B151" t="n">
-        <v>106515</v>
+        <v>106517</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16892,7 +16892,7 @@
         <v>136824800</v>
       </c>
       <c r="B152" t="n">
-        <v>102500</v>
+        <v>102502</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16994,7 +16994,7 @@
         <v>136824801</v>
       </c>
       <c r="B153" t="n">
-        <v>102500</v>
+        <v>102502</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>137073740</v>
       </c>
       <c r="B154" t="n">
-        <v>102500</v>
+        <v>102502</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17198,7 +17198,7 @@
         <v>137073741</v>
       </c>
       <c r="B155" t="n">
-        <v>102500</v>
+        <v>102502</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17300,7 +17300,7 @@
         <v>137073742</v>
       </c>
       <c r="B156" t="n">
-        <v>102500</v>
+        <v>102502</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17402,7 +17402,7 @@
         <v>137078125</v>
       </c>
       <c r="B157" t="n">
-        <v>102500</v>
+        <v>102502</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17519,7 +17519,7 @@
         <v>137073768</v>
       </c>
       <c r="B158" t="n">
-        <v>106870</v>
+        <v>106872</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17621,7 +17621,7 @@
         <v>137073769</v>
       </c>
       <c r="B159" t="n">
-        <v>106870</v>
+        <v>106872</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17825,7 +17825,7 @@
         <v>136824811</v>
       </c>
       <c r="B161" t="n">
-        <v>104897</v>
+        <v>104899</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17927,7 +17927,7 @@
         <v>136824812</v>
       </c>
       <c r="B162" t="n">
-        <v>104897</v>
+        <v>104899</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>136824845</v>
       </c>
       <c r="B170" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18845,7 +18845,7 @@
         <v>136824847</v>
       </c>
       <c r="B171" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         <v>136824848</v>
       </c>
       <c r="B172" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19049,7 +19049,7 @@
         <v>136824849</v>
       </c>
       <c r="B173" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19151,7 +19151,7 @@
         <v>136824850</v>
       </c>
       <c r="B174" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19253,7 +19253,7 @@
         <v>136824851</v>
       </c>
       <c r="B175" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19355,7 +19355,7 @@
         <v>136824852</v>
       </c>
       <c r="B176" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         <v>136824853</v>
       </c>
       <c r="B177" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19559,7 +19559,7 @@
         <v>136824854</v>
       </c>
       <c r="B178" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>137077942</v>
       </c>
       <c r="B179" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19763,7 +19763,7 @@
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Björn Bråvander, Ingemar Södergren, Klara Tellebo, Malin Hylland</t>
+          <t>Malin Hylland, Klara Tellebo, Ingemar Södergren, Björn Bråvander</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
@@ -19778,7 +19778,7 @@
         <v>137078051</v>
       </c>
       <c r="B180" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19885,7 +19885,7 @@
         <v>136824825</v>
       </c>
       <c r="B181" t="n">
-        <v>99180</v>
+        <v>99182</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20104,7 +20104,7 @@
         <v>136974125</v>
       </c>
       <c r="B183" t="n">
-        <v>87516</v>
+        <v>87518</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>137076843</v>
       </c>
       <c r="B184" t="n">
-        <v>91602</v>
+        <v>91604</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
         <v>137078162</v>
       </c>
       <c r="B185" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>

--- a/artfynd/A 19253-2026 artfynd.xlsx
+++ b/artfynd/A 19253-2026 artfynd.xlsx
@@ -1529,7 +1529,7 @@
         <v>136824805</v>
       </c>
       <c r="B10" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>136824806</v>
       </c>
       <c r="B11" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>136824807</v>
       </c>
       <c r="B12" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>137073743</v>
       </c>
       <c r="B13" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>137073744</v>
       </c>
       <c r="B14" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>136974111</v>
       </c>
       <c r="B16" t="n">
-        <v>85714</v>
+        <v>85727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>137077964</v>
       </c>
       <c r="B17" t="n">
-        <v>87391</v>
+        <v>87404</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>137100339</v>
       </c>
       <c r="B18" t="n">
-        <v>87598</v>
+        <v>87611</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>136824809</v>
       </c>
       <c r="B22" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>137073745</v>
       </c>
       <c r="B23" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>137073746</v>
       </c>
       <c r="B24" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>137078005</v>
       </c>
       <c r="B25" t="n">
-        <v>92562</v>
+        <v>92575</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>137073793</v>
       </c>
       <c r="B27" t="n">
-        <v>92804</v>
+        <v>92817</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>136824836</v>
       </c>
       <c r="B28" t="n">
-        <v>92483</v>
+        <v>92496</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136824831</v>
       </c>
       <c r="B29" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>136824832</v>
       </c>
       <c r="B30" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>136824833</v>
       </c>
       <c r="B31" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>137078053</v>
       </c>
       <c r="B32" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>136824816</v>
       </c>
       <c r="B34" t="n">
-        <v>96711</v>
+        <v>96724</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>137073749</v>
       </c>
       <c r="B35" t="n">
-        <v>96711</v>
+        <v>96724</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>137073750</v>
       </c>
       <c r="B36" t="n">
-        <v>96711</v>
+        <v>96724</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>137073751</v>
       </c>
       <c r="B37" t="n">
-        <v>96711</v>
+        <v>96724</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>136974096</v>
       </c>
       <c r="B43" t="n">
-        <v>91906</v>
+        <v>91919</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>136974097</v>
       </c>
       <c r="B44" t="n">
-        <v>87570</v>
+        <v>87583</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         <v>137077497</v>
       </c>
       <c r="B45" t="n">
-        <v>87570</v>
+        <v>87583</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>136824828</v>
       </c>
       <c r="B46" t="n">
-        <v>87341</v>
+        <v>87354</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>136974098</v>
       </c>
       <c r="B47" t="n">
-        <v>87341</v>
+        <v>87354</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>137073761</v>
       </c>
       <c r="B48" t="n">
-        <v>87341</v>
+        <v>87354</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         <v>137073762</v>
       </c>
       <c r="B49" t="n">
-        <v>87341</v>
+        <v>87354</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>137073763</v>
       </c>
       <c r="B50" t="n">
-        <v>87341</v>
+        <v>87354</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>137073764</v>
       </c>
       <c r="B51" t="n">
-        <v>87341</v>
+        <v>87354</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>137073765</v>
       </c>
       <c r="B52" t="n">
-        <v>87341</v>
+        <v>87354</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>137073766</v>
       </c>
       <c r="B53" t="n">
-        <v>87341</v>
+        <v>87354</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         <v>137073767</v>
       </c>
       <c r="B54" t="n">
-        <v>87341</v>
+        <v>87354</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         <v>137077917</v>
       </c>
       <c r="B55" t="n">
-        <v>87341</v>
+        <v>87354</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>137078067</v>
       </c>
       <c r="B56" t="n">
-        <v>87341</v>
+        <v>87354</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         <v>137078239</v>
       </c>
       <c r="B57" t="n">
-        <v>87341</v>
+        <v>87354</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         <v>137073794</v>
       </c>
       <c r="B58" t="n">
-        <v>92526</v>
+        <v>92539</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
         <v>136824823</v>
       </c>
       <c r="B63" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         <v>136824824</v>
       </c>
       <c r="B64" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>137073758</v>
       </c>
       <c r="B65" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         <v>137073759</v>
       </c>
       <c r="B66" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>137077540</v>
       </c>
       <c r="B68" t="n">
-        <v>89295</v>
+        <v>89308</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>137073747</v>
       </c>
       <c r="B72" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         <v>137073748</v>
       </c>
       <c r="B73" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>137078402</v>
       </c>
       <c r="B74" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         <v>136824808</v>
       </c>
       <c r="B77" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>137073773</v>
       </c>
       <c r="B82" t="n">
-        <v>91637</v>
+        <v>91650</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>136824839</v>
       </c>
       <c r="B83" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>136824840</v>
       </c>
       <c r="B84" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>136824841</v>
       </c>
       <c r="B85" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         <v>136974114</v>
       </c>
       <c r="B86" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         <v>136974115</v>
       </c>
       <c r="B87" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         <v>136974117</v>
       </c>
       <c r="B88" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10071,7 +10071,7 @@
         <v>136974118</v>
       </c>
       <c r="B89" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10173,7 +10173,7 @@
         <v>137073777</v>
       </c>
       <c r="B90" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
         <v>137073778</v>
       </c>
       <c r="B91" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
         <v>137073779</v>
       </c>
       <c r="B92" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10479,7 +10479,7 @@
         <v>137073780</v>
       </c>
       <c r="B93" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         <v>137073781</v>
       </c>
       <c r="B94" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10683,7 +10683,7 @@
         <v>137073782</v>
       </c>
       <c r="B95" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>137073783</v>
       </c>
       <c r="B96" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>137073784</v>
       </c>
       <c r="B97" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>137073785</v>
       </c>
       <c r="B98" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>137073786</v>
       </c>
       <c r="B99" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11193,7 +11193,7 @@
         <v>137073787</v>
       </c>
       <c r="B100" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11295,7 +11295,7 @@
         <v>137073788</v>
       </c>
       <c r="B101" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11397,7 +11397,7 @@
         <v>137073789</v>
       </c>
       <c r="B102" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
         <v>137077585</v>
       </c>
       <c r="B103" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>137077941</v>
       </c>
       <c r="B104" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Malin Hylland, Klara Tellebo, Ingemar Södergren, Björn Bråvander</t>
+          <t>Björn Bråvander, Ingemar Södergren, Klara Tellebo, Malin Hylland</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
@@ -11742,7 +11742,7 @@
         <v>137078025</v>
       </c>
       <c r="B105" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>137078049</v>
       </c>
       <c r="B106" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11990,7 +11990,7 @@
         <v>137078081</v>
       </c>
       <c r="B107" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>136824829</v>
       </c>
       <c r="B108" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>136824830</v>
       </c>
       <c r="B109" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>136974101</v>
       </c>
       <c r="B110" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12425,7 +12425,7 @@
         <v>136974102</v>
       </c>
       <c r="B111" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>137073771</v>
       </c>
       <c r="B112" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         <v>136824810</v>
       </c>
       <c r="B120" t="n">
-        <v>57195</v>
+        <v>57208</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14790,7 +14790,7 @@
         <v>136824814</v>
       </c>
       <c r="B132" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15203,7 +15203,7 @@
         <v>136824822</v>
       </c>
       <c r="B136" t="n">
-        <v>99354</v>
+        <v>99367</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>137073756</v>
       </c>
       <c r="B137" t="n">
-        <v>99354</v>
+        <v>99367</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>137073757</v>
       </c>
       <c r="B138" t="n">
-        <v>99354</v>
+        <v>99367</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15509,7 +15509,7 @@
         <v>137077977</v>
       </c>
       <c r="B139" t="n">
-        <v>99354</v>
+        <v>99367</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15634,7 +15634,7 @@
         <v>136824842</v>
       </c>
       <c r="B140" t="n">
-        <v>108401</v>
+        <v>108414</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>136824843</v>
       </c>
       <c r="B141" t="n">
-        <v>108401</v>
+        <v>108414</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15838,7 +15838,7 @@
         <v>137077952</v>
       </c>
       <c r="B142" t="n">
-        <v>108401</v>
+        <v>108414</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>137073795</v>
       </c>
       <c r="B143" t="n">
-        <v>107087</v>
+        <v>107100</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16275,7 +16275,7 @@
         <v>136974104</v>
       </c>
       <c r="B146" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16790,7 +16790,7 @@
         <v>136824837</v>
       </c>
       <c r="B151" t="n">
-        <v>106517</v>
+        <v>106530</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16892,7 +16892,7 @@
         <v>136824800</v>
       </c>
       <c r="B152" t="n">
-        <v>102502</v>
+        <v>102515</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16994,7 +16994,7 @@
         <v>136824801</v>
       </c>
       <c r="B153" t="n">
-        <v>102502</v>
+        <v>102515</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>137073740</v>
       </c>
       <c r="B154" t="n">
-        <v>102502</v>
+        <v>102515</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17198,7 +17198,7 @@
         <v>137073741</v>
       </c>
       <c r="B155" t="n">
-        <v>102502</v>
+        <v>102515</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17300,7 +17300,7 @@
         <v>137073742</v>
       </c>
       <c r="B156" t="n">
-        <v>102502</v>
+        <v>102515</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17402,7 +17402,7 @@
         <v>137078125</v>
       </c>
       <c r="B157" t="n">
-        <v>102502</v>
+        <v>102515</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17519,7 +17519,7 @@
         <v>137073768</v>
       </c>
       <c r="B158" t="n">
-        <v>106872</v>
+        <v>106885</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17621,7 +17621,7 @@
         <v>137073769</v>
       </c>
       <c r="B159" t="n">
-        <v>106872</v>
+        <v>106885</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17825,7 +17825,7 @@
         <v>136824811</v>
       </c>
       <c r="B161" t="n">
-        <v>104899</v>
+        <v>104912</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17927,7 +17927,7 @@
         <v>136824812</v>
       </c>
       <c r="B162" t="n">
-        <v>104899</v>
+        <v>104912</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>136824845</v>
       </c>
       <c r="B170" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18845,7 +18845,7 @@
         <v>136824847</v>
       </c>
       <c r="B171" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         <v>136824848</v>
       </c>
       <c r="B172" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19049,7 +19049,7 @@
         <v>136824849</v>
       </c>
       <c r="B173" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19151,7 +19151,7 @@
         <v>136824850</v>
       </c>
       <c r="B174" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19253,7 +19253,7 @@
         <v>136824851</v>
       </c>
       <c r="B175" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19355,7 +19355,7 @@
         <v>136824852</v>
       </c>
       <c r="B176" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         <v>136824853</v>
       </c>
       <c r="B177" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19559,7 +19559,7 @@
         <v>136824854</v>
       </c>
       <c r="B178" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>137077942</v>
       </c>
       <c r="B179" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19763,7 +19763,7 @@
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Malin Hylland, Klara Tellebo, Ingemar Södergren, Björn Bråvander</t>
+          <t>Björn Bråvander, Ingemar Södergren, Klara Tellebo, Malin Hylland</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
@@ -19778,7 +19778,7 @@
         <v>137078051</v>
       </c>
       <c r="B180" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19885,7 +19885,7 @@
         <v>136824825</v>
       </c>
       <c r="B181" t="n">
-        <v>99182</v>
+        <v>99195</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20104,7 +20104,7 @@
         <v>136974125</v>
       </c>
       <c r="B183" t="n">
-        <v>87518</v>
+        <v>87531</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>137076843</v>
       </c>
       <c r="B184" t="n">
-        <v>91604</v>
+        <v>91617</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
         <v>137078162</v>
       </c>
       <c r="B185" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>

--- a/artfynd/A 19253-2026 artfynd.xlsx
+++ b/artfynd/A 19253-2026 artfynd.xlsx
@@ -1529,7 +1529,7 @@
         <v>136824805</v>
       </c>
       <c r="B10" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>136824806</v>
       </c>
       <c r="B11" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>136824807</v>
       </c>
       <c r="B12" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>137073743</v>
       </c>
       <c r="B13" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>137073744</v>
       </c>
       <c r="B14" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>136974111</v>
       </c>
       <c r="B16" t="n">
-        <v>85727</v>
+        <v>85729</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>137077964</v>
       </c>
       <c r="B17" t="n">
-        <v>87404</v>
+        <v>87406</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>137100339</v>
       </c>
       <c r="B18" t="n">
-        <v>87611</v>
+        <v>87613</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>136824809</v>
       </c>
       <c r="B22" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>137073745</v>
       </c>
       <c r="B23" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>137073746</v>
       </c>
       <c r="B24" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>137078005</v>
       </c>
       <c r="B25" t="n">
-        <v>92575</v>
+        <v>92577</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>137073793</v>
       </c>
       <c r="B27" t="n">
-        <v>92817</v>
+        <v>92819</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>136824836</v>
       </c>
       <c r="B28" t="n">
-        <v>92496</v>
+        <v>92498</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136824831</v>
       </c>
       <c r="B29" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>136824832</v>
       </c>
       <c r="B30" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>136824833</v>
       </c>
       <c r="B31" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>137078053</v>
       </c>
       <c r="B32" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>136824816</v>
       </c>
       <c r="B34" t="n">
-        <v>96724</v>
+        <v>96726</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>137073749</v>
       </c>
       <c r="B35" t="n">
-        <v>96724</v>
+        <v>96726</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>137073750</v>
       </c>
       <c r="B36" t="n">
-        <v>96724</v>
+        <v>96726</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>137073751</v>
       </c>
       <c r="B37" t="n">
-        <v>96724</v>
+        <v>96726</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>136974096</v>
       </c>
       <c r="B43" t="n">
-        <v>91919</v>
+        <v>91921</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>136974097</v>
       </c>
       <c r="B44" t="n">
-        <v>87583</v>
+        <v>87585</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         <v>137077497</v>
       </c>
       <c r="B45" t="n">
-        <v>87583</v>
+        <v>87585</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>136824828</v>
       </c>
       <c r="B46" t="n">
-        <v>87354</v>
+        <v>87356</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>136974098</v>
       </c>
       <c r="B47" t="n">
-        <v>87354</v>
+        <v>87356</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>137073761</v>
       </c>
       <c r="B48" t="n">
-        <v>87354</v>
+        <v>87356</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         <v>137073762</v>
       </c>
       <c r="B49" t="n">
-        <v>87354</v>
+        <v>87356</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>137073763</v>
       </c>
       <c r="B50" t="n">
-        <v>87354</v>
+        <v>87356</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>137073764</v>
       </c>
       <c r="B51" t="n">
-        <v>87354</v>
+        <v>87356</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>137073765</v>
       </c>
       <c r="B52" t="n">
-        <v>87354</v>
+        <v>87356</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>137073766</v>
       </c>
       <c r="B53" t="n">
-        <v>87354</v>
+        <v>87356</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         <v>137073767</v>
       </c>
       <c r="B54" t="n">
-        <v>87354</v>
+        <v>87356</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         <v>137077917</v>
       </c>
       <c r="B55" t="n">
-        <v>87354</v>
+        <v>87356</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>137078067</v>
       </c>
       <c r="B56" t="n">
-        <v>87354</v>
+        <v>87356</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         <v>137078239</v>
       </c>
       <c r="B57" t="n">
-        <v>87354</v>
+        <v>87356</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         <v>137073794</v>
       </c>
       <c r="B58" t="n">
-        <v>92539</v>
+        <v>92541</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
         <v>136824823</v>
       </c>
       <c r="B63" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         <v>136824824</v>
       </c>
       <c r="B64" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>137073758</v>
       </c>
       <c r="B65" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         <v>137073759</v>
       </c>
       <c r="B66" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>137077540</v>
       </c>
       <c r="B68" t="n">
-        <v>89308</v>
+        <v>89310</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>137073747</v>
       </c>
       <c r="B72" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         <v>137073748</v>
       </c>
       <c r="B73" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>137078402</v>
       </c>
       <c r="B74" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         <v>136824808</v>
       </c>
       <c r="B77" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>137073773</v>
       </c>
       <c r="B82" t="n">
-        <v>91650</v>
+        <v>91652</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>136824839</v>
       </c>
       <c r="B83" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>136824840</v>
       </c>
       <c r="B84" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>136824841</v>
       </c>
       <c r="B85" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         <v>136974114</v>
       </c>
       <c r="B86" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         <v>136974115</v>
       </c>
       <c r="B87" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         <v>136974117</v>
       </c>
       <c r="B88" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10071,7 +10071,7 @@
         <v>136974118</v>
       </c>
       <c r="B89" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10173,7 +10173,7 @@
         <v>137073777</v>
       </c>
       <c r="B90" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
         <v>137073778</v>
       </c>
       <c r="B91" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
         <v>137073779</v>
       </c>
       <c r="B92" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10479,7 +10479,7 @@
         <v>137073780</v>
       </c>
       <c r="B93" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         <v>137073781</v>
       </c>
       <c r="B94" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10683,7 +10683,7 @@
         <v>137073782</v>
       </c>
       <c r="B95" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>137073783</v>
       </c>
       <c r="B96" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>137073784</v>
       </c>
       <c r="B97" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>137073785</v>
       </c>
       <c r="B98" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>137073786</v>
       </c>
       <c r="B99" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11193,7 +11193,7 @@
         <v>137073787</v>
       </c>
       <c r="B100" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11295,7 +11295,7 @@
         <v>137073788</v>
       </c>
       <c r="B101" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11397,7 +11397,7 @@
         <v>137073789</v>
       </c>
       <c r="B102" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
         <v>137077585</v>
       </c>
       <c r="B103" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>137077941</v>
       </c>
       <c r="B104" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>137078025</v>
       </c>
       <c r="B105" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>137078049</v>
       </c>
       <c r="B106" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11990,7 +11990,7 @@
         <v>137078081</v>
       </c>
       <c r="B107" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>136824829</v>
       </c>
       <c r="B108" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>136824830</v>
       </c>
       <c r="B109" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>136974101</v>
       </c>
       <c r="B110" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12425,7 +12425,7 @@
         <v>136974102</v>
       </c>
       <c r="B111" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>137073771</v>
       </c>
       <c r="B112" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         <v>136824810</v>
       </c>
       <c r="B120" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13448,11 +13448,7 @@
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
@@ -14790,7 +14786,7 @@
         <v>136824814</v>
       </c>
       <c r="B132" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14816,11 +14812,7 @@
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
@@ -15203,7 +15195,7 @@
         <v>136824822</v>
       </c>
       <c r="B136" t="n">
-        <v>99367</v>
+        <v>99369</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15305,7 +15297,7 @@
         <v>137073756</v>
       </c>
       <c r="B137" t="n">
-        <v>99367</v>
+        <v>99369</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15407,7 +15399,7 @@
         <v>137073757</v>
       </c>
       <c r="B138" t="n">
-        <v>99367</v>
+        <v>99369</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15509,7 +15501,7 @@
         <v>137077977</v>
       </c>
       <c r="B139" t="n">
-        <v>99367</v>
+        <v>99369</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15634,7 +15626,7 @@
         <v>136824842</v>
       </c>
       <c r="B140" t="n">
-        <v>108414</v>
+        <v>108416</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15736,7 +15728,7 @@
         <v>136824843</v>
       </c>
       <c r="B141" t="n">
-        <v>108414</v>
+        <v>108416</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15838,7 +15830,7 @@
         <v>137077952</v>
       </c>
       <c r="B142" t="n">
-        <v>108414</v>
+        <v>108416</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15955,7 +15947,7 @@
         <v>137073795</v>
       </c>
       <c r="B143" t="n">
-        <v>107100</v>
+        <v>107102</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16275,7 +16267,7 @@
         <v>136974104</v>
       </c>
       <c r="B146" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16790,7 +16782,7 @@
         <v>136824837</v>
       </c>
       <c r="B151" t="n">
-        <v>106530</v>
+        <v>106532</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16892,7 +16884,7 @@
         <v>136824800</v>
       </c>
       <c r="B152" t="n">
-        <v>102515</v>
+        <v>102517</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16994,7 +16986,7 @@
         <v>136824801</v>
       </c>
       <c r="B153" t="n">
-        <v>102515</v>
+        <v>102517</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17096,7 +17088,7 @@
         <v>137073740</v>
       </c>
       <c r="B154" t="n">
-        <v>102515</v>
+        <v>102517</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17198,7 +17190,7 @@
         <v>137073741</v>
       </c>
       <c r="B155" t="n">
-        <v>102515</v>
+        <v>102517</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17300,7 +17292,7 @@
         <v>137073742</v>
       </c>
       <c r="B156" t="n">
-        <v>102515</v>
+        <v>102517</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17402,7 +17394,7 @@
         <v>137078125</v>
       </c>
       <c r="B157" t="n">
-        <v>102515</v>
+        <v>102517</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17519,7 +17511,7 @@
         <v>137073768</v>
       </c>
       <c r="B158" t="n">
-        <v>106885</v>
+        <v>106887</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17621,7 +17613,7 @@
         <v>137073769</v>
       </c>
       <c r="B159" t="n">
-        <v>106885</v>
+        <v>106887</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17825,7 +17817,7 @@
         <v>136824811</v>
       </c>
       <c r="B161" t="n">
-        <v>104912</v>
+        <v>104914</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17927,7 +17919,7 @@
         <v>136824812</v>
       </c>
       <c r="B162" t="n">
-        <v>104912</v>
+        <v>104914</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18743,7 +18735,7 @@
         <v>136824845</v>
       </c>
       <c r="B170" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18845,7 +18837,7 @@
         <v>136824847</v>
       </c>
       <c r="B171" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18947,7 +18939,7 @@
         <v>136824848</v>
       </c>
       <c r="B172" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19049,7 +19041,7 @@
         <v>136824849</v>
       </c>
       <c r="B173" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19151,7 +19143,7 @@
         <v>136824850</v>
       </c>
       <c r="B174" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19253,7 +19245,7 @@
         <v>136824851</v>
       </c>
       <c r="B175" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19355,7 +19347,7 @@
         <v>136824852</v>
       </c>
       <c r="B176" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19457,7 +19449,7 @@
         <v>136824853</v>
       </c>
       <c r="B177" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19559,7 +19551,7 @@
         <v>136824854</v>
       </c>
       <c r="B178" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19661,7 +19653,7 @@
         <v>137077942</v>
       </c>
       <c r="B179" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19778,7 +19770,7 @@
         <v>137078051</v>
       </c>
       <c r="B180" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19885,7 +19877,7 @@
         <v>136824825</v>
       </c>
       <c r="B181" t="n">
-        <v>99195</v>
+        <v>99197</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20104,7 +20096,7 @@
         <v>136974125</v>
       </c>
       <c r="B183" t="n">
-        <v>87531</v>
+        <v>87533</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20211,7 +20203,7 @@
         <v>137076843</v>
       </c>
       <c r="B184" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20349,7 +20341,7 @@
         <v>137078162</v>
       </c>
       <c r="B185" t="n">
-        <v>87554</v>
+        <v>87556</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>

--- a/artfynd/A 19253-2026 artfynd.xlsx
+++ b/artfynd/A 19253-2026 artfynd.xlsx
@@ -1529,7 +1529,7 @@
         <v>136824805</v>
       </c>
       <c r="B10" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>136824806</v>
       </c>
       <c r="B11" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>136824807</v>
       </c>
       <c r="B12" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>137073743</v>
       </c>
       <c r="B13" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>137073744</v>
       </c>
       <c r="B14" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>136974111</v>
       </c>
       <c r="B16" t="n">
-        <v>85729</v>
+        <v>85732</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>137077964</v>
       </c>
       <c r="B17" t="n">
-        <v>87406</v>
+        <v>87409</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>137100339</v>
       </c>
       <c r="B18" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>136824809</v>
       </c>
       <c r="B22" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>137073745</v>
       </c>
       <c r="B23" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>137073746</v>
       </c>
       <c r="B24" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>137078005</v>
       </c>
       <c r="B25" t="n">
-        <v>92577</v>
+        <v>92580</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>137073793</v>
       </c>
       <c r="B27" t="n">
-        <v>92819</v>
+        <v>92822</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>136824836</v>
       </c>
       <c r="B28" t="n">
-        <v>92498</v>
+        <v>92501</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136824831</v>
       </c>
       <c r="B29" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>136824832</v>
       </c>
       <c r="B30" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>136824833</v>
       </c>
       <c r="B31" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>137078053</v>
       </c>
       <c r="B32" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>136824816</v>
       </c>
       <c r="B34" t="n">
-        <v>96726</v>
+        <v>96729</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>137073749</v>
       </c>
       <c r="B35" t="n">
-        <v>96726</v>
+        <v>96729</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>137073750</v>
       </c>
       <c r="B36" t="n">
-        <v>96726</v>
+        <v>96729</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>137073751</v>
       </c>
       <c r="B37" t="n">
-        <v>96726</v>
+        <v>96729</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>136974096</v>
       </c>
       <c r="B43" t="n">
-        <v>91921</v>
+        <v>91924</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>136974097</v>
       </c>
       <c r="B44" t="n">
-        <v>87585</v>
+        <v>87588</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         <v>137077497</v>
       </c>
       <c r="B45" t="n">
-        <v>87585</v>
+        <v>87588</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>136824828</v>
       </c>
       <c r="B46" t="n">
-        <v>87356</v>
+        <v>87359</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>136974098</v>
       </c>
       <c r="B47" t="n">
-        <v>87356</v>
+        <v>87359</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>137073761</v>
       </c>
       <c r="B48" t="n">
-        <v>87356</v>
+        <v>87359</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         <v>137073762</v>
       </c>
       <c r="B49" t="n">
-        <v>87356</v>
+        <v>87359</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>137073763</v>
       </c>
       <c r="B50" t="n">
-        <v>87356</v>
+        <v>87359</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>137073764</v>
       </c>
       <c r="B51" t="n">
-        <v>87356</v>
+        <v>87359</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>137073765</v>
       </c>
       <c r="B52" t="n">
-        <v>87356</v>
+        <v>87359</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>137073766</v>
       </c>
       <c r="B53" t="n">
-        <v>87356</v>
+        <v>87359</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         <v>137073767</v>
       </c>
       <c r="B54" t="n">
-        <v>87356</v>
+        <v>87359</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         <v>137077917</v>
       </c>
       <c r="B55" t="n">
-        <v>87356</v>
+        <v>87359</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>137078067</v>
       </c>
       <c r="B56" t="n">
-        <v>87356</v>
+        <v>87359</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         <v>137078239</v>
       </c>
       <c r="B57" t="n">
-        <v>87356</v>
+        <v>87359</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         <v>137073794</v>
       </c>
       <c r="B58" t="n">
-        <v>92541</v>
+        <v>92544</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
         <v>136824823</v>
       </c>
       <c r="B63" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         <v>136824824</v>
       </c>
       <c r="B64" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>137073758</v>
       </c>
       <c r="B65" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         <v>137073759</v>
       </c>
       <c r="B66" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>137077540</v>
       </c>
       <c r="B68" t="n">
-        <v>89310</v>
+        <v>89313</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>137073747</v>
       </c>
       <c r="B72" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         <v>137073748</v>
       </c>
       <c r="B73" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>137078402</v>
       </c>
       <c r="B74" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         <v>136824808</v>
       </c>
       <c r="B77" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>137073773</v>
       </c>
       <c r="B82" t="n">
-        <v>91652</v>
+        <v>91655</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>136824839</v>
       </c>
       <c r="B83" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>136824840</v>
       </c>
       <c r="B84" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>136824841</v>
       </c>
       <c r="B85" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         <v>136974114</v>
       </c>
       <c r="B86" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         <v>136974115</v>
       </c>
       <c r="B87" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         <v>136974117</v>
       </c>
       <c r="B88" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10071,7 +10071,7 @@
         <v>136974118</v>
       </c>
       <c r="B89" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10173,7 +10173,7 @@
         <v>137073777</v>
       </c>
       <c r="B90" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
         <v>137073778</v>
       </c>
       <c r="B91" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
         <v>137073779</v>
       </c>
       <c r="B92" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10479,7 +10479,7 @@
         <v>137073780</v>
       </c>
       <c r="B93" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         <v>137073781</v>
       </c>
       <c r="B94" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10683,7 +10683,7 @@
         <v>137073782</v>
       </c>
       <c r="B95" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>137073783</v>
       </c>
       <c r="B96" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>137073784</v>
       </c>
       <c r="B97" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>137073785</v>
       </c>
       <c r="B98" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>137073786</v>
       </c>
       <c r="B99" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11193,7 +11193,7 @@
         <v>137073787</v>
       </c>
       <c r="B100" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11295,7 +11295,7 @@
         <v>137073788</v>
       </c>
       <c r="B101" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11397,7 +11397,7 @@
         <v>137073789</v>
       </c>
       <c r="B102" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
         <v>137077585</v>
       </c>
       <c r="B103" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>137077941</v>
       </c>
       <c r="B104" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>137078025</v>
       </c>
       <c r="B105" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>137078049</v>
       </c>
       <c r="B106" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11990,7 +11990,7 @@
         <v>137078081</v>
       </c>
       <c r="B107" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>136824829</v>
       </c>
       <c r="B108" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>136824830</v>
       </c>
       <c r="B109" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>136974101</v>
       </c>
       <c r="B110" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12425,7 +12425,7 @@
         <v>136974102</v>
       </c>
       <c r="B111" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>137073771</v>
       </c>
       <c r="B112" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>136824822</v>
       </c>
       <c r="B136" t="n">
-        <v>99369</v>
+        <v>99372</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15297,7 +15297,7 @@
         <v>137073756</v>
       </c>
       <c r="B137" t="n">
-        <v>99369</v>
+        <v>99372</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>137073757</v>
       </c>
       <c r="B138" t="n">
-        <v>99369</v>
+        <v>99372</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15501,7 +15501,7 @@
         <v>137077977</v>
       </c>
       <c r="B139" t="n">
-        <v>99369</v>
+        <v>99372</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15626,7 +15626,7 @@
         <v>136824842</v>
       </c>
       <c r="B140" t="n">
-        <v>108416</v>
+        <v>108421</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>136824843</v>
       </c>
       <c r="B141" t="n">
-        <v>108416</v>
+        <v>108421</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15830,7 +15830,7 @@
         <v>137077952</v>
       </c>
       <c r="B142" t="n">
-        <v>108416</v>
+        <v>108421</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>137073795</v>
       </c>
       <c r="B143" t="n">
-        <v>107102</v>
+        <v>107106</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16267,7 +16267,7 @@
         <v>136974104</v>
       </c>
       <c r="B146" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16782,7 +16782,7 @@
         <v>136824837</v>
       </c>
       <c r="B151" t="n">
-        <v>106532</v>
+        <v>106536</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16884,7 +16884,7 @@
         <v>136824800</v>
       </c>
       <c r="B152" t="n">
-        <v>102517</v>
+        <v>102520</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
         <v>136824801</v>
       </c>
       <c r="B153" t="n">
-        <v>102517</v>
+        <v>102520</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17088,7 +17088,7 @@
         <v>137073740</v>
       </c>
       <c r="B154" t="n">
-        <v>102517</v>
+        <v>102520</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17190,7 +17190,7 @@
         <v>137073741</v>
       </c>
       <c r="B155" t="n">
-        <v>102517</v>
+        <v>102520</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17292,7 +17292,7 @@
         <v>137073742</v>
       </c>
       <c r="B156" t="n">
-        <v>102517</v>
+        <v>102520</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17394,7 +17394,7 @@
         <v>137078125</v>
       </c>
       <c r="B157" t="n">
-        <v>102517</v>
+        <v>102520</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17511,7 +17511,7 @@
         <v>137073768</v>
       </c>
       <c r="B158" t="n">
-        <v>106887</v>
+        <v>106891</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17613,7 +17613,7 @@
         <v>137073769</v>
       </c>
       <c r="B159" t="n">
-        <v>106887</v>
+        <v>106891</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17817,7 +17817,7 @@
         <v>136824811</v>
       </c>
       <c r="B161" t="n">
-        <v>104914</v>
+        <v>104917</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17919,7 +17919,7 @@
         <v>136824812</v>
       </c>
       <c r="B162" t="n">
-        <v>104914</v>
+        <v>104917</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18735,7 +18735,7 @@
         <v>136824845</v>
       </c>
       <c r="B170" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18837,7 +18837,7 @@
         <v>136824847</v>
       </c>
       <c r="B171" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>136824848</v>
       </c>
       <c r="B172" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19041,7 +19041,7 @@
         <v>136824849</v>
       </c>
       <c r="B173" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         <v>136824850</v>
       </c>
       <c r="B174" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19245,7 +19245,7 @@
         <v>136824851</v>
       </c>
       <c r="B175" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19347,7 +19347,7 @@
         <v>136824852</v>
       </c>
       <c r="B176" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19449,7 +19449,7 @@
         <v>136824853</v>
       </c>
       <c r="B177" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>136824854</v>
       </c>
       <c r="B178" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19653,7 +19653,7 @@
         <v>137077942</v>
       </c>
       <c r="B179" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19770,7 +19770,7 @@
         <v>137078051</v>
       </c>
       <c r="B180" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19877,7 +19877,7 @@
         <v>136824825</v>
       </c>
       <c r="B181" t="n">
-        <v>99197</v>
+        <v>99200</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20096,7 +20096,7 @@
         <v>136974125</v>
       </c>
       <c r="B183" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20203,7 +20203,7 @@
         <v>137076843</v>
       </c>
       <c r="B184" t="n">
-        <v>91619</v>
+        <v>91622</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20341,7 +20341,7 @@
         <v>137078162</v>
       </c>
       <c r="B185" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>

--- a/artfynd/A 19253-2026 artfynd.xlsx
+++ b/artfynd/A 19253-2026 artfynd.xlsx
@@ -1529,7 +1529,7 @@
         <v>136824805</v>
       </c>
       <c r="B10" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>136824806</v>
       </c>
       <c r="B11" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>136824807</v>
       </c>
       <c r="B12" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>137073743</v>
       </c>
       <c r="B13" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>137073744</v>
       </c>
       <c r="B14" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>136974111</v>
       </c>
       <c r="B16" t="n">
-        <v>85732</v>
+        <v>85742</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>137077964</v>
       </c>
       <c r="B17" t="n">
-        <v>87409</v>
+        <v>87419</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>137100339</v>
       </c>
       <c r="B18" t="n">
-        <v>87616</v>
+        <v>87626</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>136824809</v>
       </c>
       <c r="B22" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>137073745</v>
       </c>
       <c r="B23" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>137073746</v>
       </c>
       <c r="B24" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>137078005</v>
       </c>
       <c r="B25" t="n">
-        <v>92580</v>
+        <v>92590</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>137073793</v>
       </c>
       <c r="B27" t="n">
-        <v>92822</v>
+        <v>92832</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>136824836</v>
       </c>
       <c r="B28" t="n">
-        <v>92501</v>
+        <v>92511</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136824831</v>
       </c>
       <c r="B29" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>136824832</v>
       </c>
       <c r="B30" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>136824833</v>
       </c>
       <c r="B31" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>137078053</v>
       </c>
       <c r="B32" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>136824816</v>
       </c>
       <c r="B34" t="n">
-        <v>96729</v>
+        <v>96739</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>137073749</v>
       </c>
       <c r="B35" t="n">
-        <v>96729</v>
+        <v>96739</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>137073750</v>
       </c>
       <c r="B36" t="n">
-        <v>96729</v>
+        <v>96739</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>137073751</v>
       </c>
       <c r="B37" t="n">
-        <v>96729</v>
+        <v>96739</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>136974096</v>
       </c>
       <c r="B43" t="n">
-        <v>91924</v>
+        <v>91934</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>136974097</v>
       </c>
       <c r="B44" t="n">
-        <v>87588</v>
+        <v>87598</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         <v>137077497</v>
       </c>
       <c r="B45" t="n">
-        <v>87588</v>
+        <v>87598</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>136824828</v>
       </c>
       <c r="B46" t="n">
-        <v>87359</v>
+        <v>87369</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>136974098</v>
       </c>
       <c r="B47" t="n">
-        <v>87359</v>
+        <v>87369</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>137073761</v>
       </c>
       <c r="B48" t="n">
-        <v>87359</v>
+        <v>87369</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         <v>137073762</v>
       </c>
       <c r="B49" t="n">
-        <v>87359</v>
+        <v>87369</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>137073763</v>
       </c>
       <c r="B50" t="n">
-        <v>87359</v>
+        <v>87369</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>137073764</v>
       </c>
       <c r="B51" t="n">
-        <v>87359</v>
+        <v>87369</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>137073765</v>
       </c>
       <c r="B52" t="n">
-        <v>87359</v>
+        <v>87369</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>137073766</v>
       </c>
       <c r="B53" t="n">
-        <v>87359</v>
+        <v>87369</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         <v>137073767</v>
       </c>
       <c r="B54" t="n">
-        <v>87359</v>
+        <v>87369</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         <v>137077917</v>
       </c>
       <c r="B55" t="n">
-        <v>87359</v>
+        <v>87369</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>137078067</v>
       </c>
       <c r="B56" t="n">
-        <v>87359</v>
+        <v>87369</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         <v>137078239</v>
       </c>
       <c r="B57" t="n">
-        <v>87359</v>
+        <v>87369</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         <v>137073794</v>
       </c>
       <c r="B58" t="n">
-        <v>92544</v>
+        <v>92554</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
         <v>136824823</v>
       </c>
       <c r="B63" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         <v>136824824</v>
       </c>
       <c r="B64" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>137073758</v>
       </c>
       <c r="B65" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         <v>137073759</v>
       </c>
       <c r="B66" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>137077540</v>
       </c>
       <c r="B68" t="n">
-        <v>89313</v>
+        <v>89323</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>137073747</v>
       </c>
       <c r="B72" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         <v>137073748</v>
       </c>
       <c r="B73" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>137078402</v>
       </c>
       <c r="B74" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         <v>136824808</v>
       </c>
       <c r="B77" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>137073773</v>
       </c>
       <c r="B82" t="n">
-        <v>91655</v>
+        <v>91665</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>136824839</v>
       </c>
       <c r="B83" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>136824840</v>
       </c>
       <c r="B84" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>136824841</v>
       </c>
       <c r="B85" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         <v>136974114</v>
       </c>
       <c r="B86" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         <v>136974115</v>
       </c>
       <c r="B87" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         <v>136974117</v>
       </c>
       <c r="B88" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10071,7 +10071,7 @@
         <v>136974118</v>
       </c>
       <c r="B89" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10173,7 +10173,7 @@
         <v>137073777</v>
       </c>
       <c r="B90" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
         <v>137073778</v>
       </c>
       <c r="B91" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
         <v>137073779</v>
       </c>
       <c r="B92" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10479,7 +10479,7 @@
         <v>137073780</v>
       </c>
       <c r="B93" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         <v>137073781</v>
       </c>
       <c r="B94" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10683,7 +10683,7 @@
         <v>137073782</v>
       </c>
       <c r="B95" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>137073783</v>
       </c>
       <c r="B96" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>137073784</v>
       </c>
       <c r="B97" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>137073785</v>
       </c>
       <c r="B98" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>137073786</v>
       </c>
       <c r="B99" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11193,7 +11193,7 @@
         <v>137073787</v>
       </c>
       <c r="B100" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11295,7 +11295,7 @@
         <v>137073788</v>
       </c>
       <c r="B101" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11397,7 +11397,7 @@
         <v>137073789</v>
       </c>
       <c r="B102" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
         <v>137077585</v>
       </c>
       <c r="B103" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>137077941</v>
       </c>
       <c r="B104" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>137078025</v>
       </c>
       <c r="B105" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>137078049</v>
       </c>
       <c r="B106" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11990,7 +11990,7 @@
         <v>137078081</v>
       </c>
       <c r="B107" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>136824829</v>
       </c>
       <c r="B108" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>136824830</v>
       </c>
       <c r="B109" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>136974101</v>
       </c>
       <c r="B110" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12425,7 +12425,7 @@
         <v>136974102</v>
       </c>
       <c r="B111" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>137073771</v>
       </c>
       <c r="B112" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         <v>136824810</v>
       </c>
       <c r="B120" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>136824221</v>
       </c>
       <c r="B129" t="n">
-        <v>4783</v>
+        <v>4789</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14786,7 +14786,7 @@
         <v>136824814</v>
       </c>
       <c r="B132" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>136824822</v>
       </c>
       <c r="B136" t="n">
-        <v>99372</v>
+        <v>99382</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15297,7 +15297,7 @@
         <v>137073756</v>
       </c>
       <c r="B137" t="n">
-        <v>99372</v>
+        <v>99382</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>137073757</v>
       </c>
       <c r="B138" t="n">
-        <v>99372</v>
+        <v>99382</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15501,7 +15501,7 @@
         <v>137077977</v>
       </c>
       <c r="B139" t="n">
-        <v>99372</v>
+        <v>99382</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15626,7 +15626,7 @@
         <v>136824842</v>
       </c>
       <c r="B140" t="n">
-        <v>108421</v>
+        <v>108442</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>136824843</v>
       </c>
       <c r="B141" t="n">
-        <v>108421</v>
+        <v>108442</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15830,7 +15830,7 @@
         <v>137077952</v>
       </c>
       <c r="B142" t="n">
-        <v>108421</v>
+        <v>108442</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>137073795</v>
       </c>
       <c r="B143" t="n">
-        <v>107106</v>
+        <v>107126</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16267,7 +16267,7 @@
         <v>136974104</v>
       </c>
       <c r="B146" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16782,7 +16782,7 @@
         <v>136824837</v>
       </c>
       <c r="B151" t="n">
-        <v>106536</v>
+        <v>106556</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16884,7 +16884,7 @@
         <v>136824800</v>
       </c>
       <c r="B152" t="n">
-        <v>102520</v>
+        <v>102535</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
         <v>136824801</v>
       </c>
       <c r="B153" t="n">
-        <v>102520</v>
+        <v>102535</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17088,7 +17088,7 @@
         <v>137073740</v>
       </c>
       <c r="B154" t="n">
-        <v>102520</v>
+        <v>102535</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17190,7 +17190,7 @@
         <v>137073741</v>
       </c>
       <c r="B155" t="n">
-        <v>102520</v>
+        <v>102535</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17292,7 +17292,7 @@
         <v>137073742</v>
       </c>
       <c r="B156" t="n">
-        <v>102520</v>
+        <v>102535</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17394,7 +17394,7 @@
         <v>137078125</v>
       </c>
       <c r="B157" t="n">
-        <v>102520</v>
+        <v>102535</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17511,7 +17511,7 @@
         <v>137073768</v>
       </c>
       <c r="B158" t="n">
-        <v>106891</v>
+        <v>106911</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17613,7 +17613,7 @@
         <v>137073769</v>
       </c>
       <c r="B159" t="n">
-        <v>106891</v>
+        <v>106911</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17817,7 +17817,7 @@
         <v>136824811</v>
       </c>
       <c r="B161" t="n">
-        <v>104917</v>
+        <v>104936</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17919,7 +17919,7 @@
         <v>136824812</v>
       </c>
       <c r="B162" t="n">
-        <v>104917</v>
+        <v>104936</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18735,7 +18735,7 @@
         <v>136824845</v>
       </c>
       <c r="B170" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18837,7 +18837,7 @@
         <v>136824847</v>
       </c>
       <c r="B171" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>136824848</v>
       </c>
       <c r="B172" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19041,7 +19041,7 @@
         <v>136824849</v>
       </c>
       <c r="B173" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         <v>136824850</v>
       </c>
       <c r="B174" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19245,7 +19245,7 @@
         <v>136824851</v>
       </c>
       <c r="B175" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19347,7 +19347,7 @@
         <v>136824852</v>
       </c>
       <c r="B176" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19449,7 +19449,7 @@
         <v>136824853</v>
       </c>
       <c r="B177" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>136824854</v>
       </c>
       <c r="B178" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19653,7 +19653,7 @@
         <v>137077942</v>
       </c>
       <c r="B179" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19770,7 +19770,7 @@
         <v>137078051</v>
       </c>
       <c r="B180" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19877,7 +19877,7 @@
         <v>136824825</v>
       </c>
       <c r="B181" t="n">
-        <v>99200</v>
+        <v>99210</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20096,7 +20096,7 @@
         <v>136974125</v>
       </c>
       <c r="B183" t="n">
-        <v>87536</v>
+        <v>87546</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20203,7 +20203,7 @@
         <v>137076843</v>
       </c>
       <c r="B184" t="n">
-        <v>91622</v>
+        <v>91632</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20341,7 +20341,7 @@
         <v>137078162</v>
       </c>
       <c r="B185" t="n">
-        <v>87559</v>
+        <v>87569</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>

--- a/artfynd/A 19253-2026 artfynd.xlsx
+++ b/artfynd/A 19253-2026 artfynd.xlsx
@@ -1529,7 +1529,7 @@
         <v>136824805</v>
       </c>
       <c r="B10" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>136824806</v>
       </c>
       <c r="B11" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>136824807</v>
       </c>
       <c r="B12" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>137073743</v>
       </c>
       <c r="B13" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>137073744</v>
       </c>
       <c r="B14" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>137077964</v>
       </c>
       <c r="B17" t="n">
-        <v>87419</v>
+        <v>87420</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>137100339</v>
       </c>
       <c r="B18" t="n">
-        <v>87626</v>
+        <v>87627</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>136824809</v>
       </c>
       <c r="B22" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>137073745</v>
       </c>
       <c r="B23" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>137073746</v>
       </c>
       <c r="B24" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>137078005</v>
       </c>
       <c r="B25" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>137073793</v>
       </c>
       <c r="B27" t="n">
-        <v>92832</v>
+        <v>92833</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>136824836</v>
       </c>
       <c r="B28" t="n">
-        <v>92511</v>
+        <v>92512</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136824831</v>
       </c>
       <c r="B29" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>136824832</v>
       </c>
       <c r="B30" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>136824833</v>
       </c>
       <c r="B31" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>137078053</v>
       </c>
       <c r="B32" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>136824816</v>
       </c>
       <c r="B34" t="n">
-        <v>96739</v>
+        <v>96740</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>137073749</v>
       </c>
       <c r="B35" t="n">
-        <v>96739</v>
+        <v>96740</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>137073750</v>
       </c>
       <c r="B36" t="n">
-        <v>96739</v>
+        <v>96740</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>137073751</v>
       </c>
       <c r="B37" t="n">
-        <v>96739</v>
+        <v>96740</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>136974096</v>
       </c>
       <c r="B43" t="n">
-        <v>91934</v>
+        <v>91935</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>136974097</v>
       </c>
       <c r="B44" t="n">
-        <v>87598</v>
+        <v>87599</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         <v>137077497</v>
       </c>
       <c r="B45" t="n">
-        <v>87598</v>
+        <v>87599</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>136824828</v>
       </c>
       <c r="B46" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>136974098</v>
       </c>
       <c r="B47" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>137073761</v>
       </c>
       <c r="B48" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         <v>137073762</v>
       </c>
       <c r="B49" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>137073763</v>
       </c>
       <c r="B50" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>137073764</v>
       </c>
       <c r="B51" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>137073765</v>
       </c>
       <c r="B52" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>137073766</v>
       </c>
       <c r="B53" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         <v>137073767</v>
       </c>
       <c r="B54" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         <v>137077917</v>
       </c>
       <c r="B55" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>137078067</v>
       </c>
       <c r="B56" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         <v>137078239</v>
       </c>
       <c r="B57" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         <v>137073794</v>
       </c>
       <c r="B58" t="n">
-        <v>92554</v>
+        <v>92555</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
         <v>136824823</v>
       </c>
       <c r="B63" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         <v>136824824</v>
       </c>
       <c r="B64" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>137073758</v>
       </c>
       <c r="B65" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         <v>137073759</v>
       </c>
       <c r="B66" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>137077540</v>
       </c>
       <c r="B68" t="n">
-        <v>89323</v>
+        <v>89324</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>137073747</v>
       </c>
       <c r="B72" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         <v>137073748</v>
       </c>
       <c r="B73" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>137078402</v>
       </c>
       <c r="B74" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         <v>136824808</v>
       </c>
       <c r="B77" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>137073773</v>
       </c>
       <c r="B82" t="n">
-        <v>91665</v>
+        <v>91666</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>136824839</v>
       </c>
       <c r="B83" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>136824840</v>
       </c>
       <c r="B84" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>136824841</v>
       </c>
       <c r="B85" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         <v>136974114</v>
       </c>
       <c r="B86" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         <v>136974115</v>
       </c>
       <c r="B87" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         <v>136974117</v>
       </c>
       <c r="B88" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10071,7 +10071,7 @@
         <v>136974118</v>
       </c>
       <c r="B89" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10173,7 +10173,7 @@
         <v>137073777</v>
       </c>
       <c r="B90" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
         <v>137073778</v>
       </c>
       <c r="B91" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
         <v>137073779</v>
       </c>
       <c r="B92" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10479,7 +10479,7 @@
         <v>137073780</v>
       </c>
       <c r="B93" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         <v>137073781</v>
       </c>
       <c r="B94" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10683,7 +10683,7 @@
         <v>137073782</v>
       </c>
       <c r="B95" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>137073783</v>
       </c>
       <c r="B96" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>137073784</v>
       </c>
       <c r="B97" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>137073785</v>
       </c>
       <c r="B98" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>137073786</v>
       </c>
       <c r="B99" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11193,7 +11193,7 @@
         <v>137073787</v>
       </c>
       <c r="B100" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11295,7 +11295,7 @@
         <v>137073788</v>
       </c>
       <c r="B101" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11397,7 +11397,7 @@
         <v>137073789</v>
       </c>
       <c r="B102" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
         <v>137077585</v>
       </c>
       <c r="B103" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>137077941</v>
       </c>
       <c r="B104" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>137078025</v>
       </c>
       <c r="B105" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>137078049</v>
       </c>
       <c r="B106" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11990,7 +11990,7 @@
         <v>137078081</v>
       </c>
       <c r="B107" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>136824829</v>
       </c>
       <c r="B108" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>136824830</v>
       </c>
       <c r="B109" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>136974101</v>
       </c>
       <c r="B110" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12425,7 +12425,7 @@
         <v>136974102</v>
       </c>
       <c r="B111" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>137073771</v>
       </c>
       <c r="B112" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>136824822</v>
       </c>
       <c r="B136" t="n">
-        <v>99382</v>
+        <v>99383</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15297,7 +15297,7 @@
         <v>137073756</v>
       </c>
       <c r="B137" t="n">
-        <v>99382</v>
+        <v>99383</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>137073757</v>
       </c>
       <c r="B138" t="n">
-        <v>99382</v>
+        <v>99383</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15501,7 +15501,7 @@
         <v>137077977</v>
       </c>
       <c r="B139" t="n">
-        <v>99382</v>
+        <v>99383</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15626,7 +15626,7 @@
         <v>136824842</v>
       </c>
       <c r="B140" t="n">
-        <v>108442</v>
+        <v>108443</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>136824843</v>
       </c>
       <c r="B141" t="n">
-        <v>108442</v>
+        <v>108443</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15830,7 +15830,7 @@
         <v>137077952</v>
       </c>
       <c r="B142" t="n">
-        <v>108442</v>
+        <v>108443</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>137073795</v>
       </c>
       <c r="B143" t="n">
-        <v>107126</v>
+        <v>107127</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16267,7 +16267,7 @@
         <v>136974104</v>
       </c>
       <c r="B146" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16782,7 +16782,7 @@
         <v>136824837</v>
       </c>
       <c r="B151" t="n">
-        <v>106556</v>
+        <v>106557</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16884,7 +16884,7 @@
         <v>136824800</v>
       </c>
       <c r="B152" t="n">
-        <v>102535</v>
+        <v>102536</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
         <v>136824801</v>
       </c>
       <c r="B153" t="n">
-        <v>102535</v>
+        <v>102536</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17088,7 +17088,7 @@
         <v>137073740</v>
       </c>
       <c r="B154" t="n">
-        <v>102535</v>
+        <v>102536</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17190,7 +17190,7 @@
         <v>137073741</v>
       </c>
       <c r="B155" t="n">
-        <v>102535</v>
+        <v>102536</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17292,7 +17292,7 @@
         <v>137073742</v>
       </c>
       <c r="B156" t="n">
-        <v>102535</v>
+        <v>102536</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17394,7 +17394,7 @@
         <v>137078125</v>
       </c>
       <c r="B157" t="n">
-        <v>102535</v>
+        <v>102536</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17511,7 +17511,7 @@
         <v>137073768</v>
       </c>
       <c r="B158" t="n">
-        <v>106911</v>
+        <v>106912</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17613,7 +17613,7 @@
         <v>137073769</v>
       </c>
       <c r="B159" t="n">
-        <v>106911</v>
+        <v>106912</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17817,7 +17817,7 @@
         <v>136824811</v>
       </c>
       <c r="B161" t="n">
-        <v>104936</v>
+        <v>104937</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17919,7 +17919,7 @@
         <v>136824812</v>
       </c>
       <c r="B162" t="n">
-        <v>104936</v>
+        <v>104937</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18735,7 +18735,7 @@
         <v>136824845</v>
       </c>
       <c r="B170" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18837,7 +18837,7 @@
         <v>136824847</v>
       </c>
       <c r="B171" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>136824848</v>
       </c>
       <c r="B172" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19041,7 +19041,7 @@
         <v>136824849</v>
       </c>
       <c r="B173" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         <v>136824850</v>
       </c>
       <c r="B174" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19245,7 +19245,7 @@
         <v>136824851</v>
       </c>
       <c r="B175" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19347,7 +19347,7 @@
         <v>136824852</v>
       </c>
       <c r="B176" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19449,7 +19449,7 @@
         <v>136824853</v>
       </c>
       <c r="B177" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>136824854</v>
       </c>
       <c r="B178" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19653,7 +19653,7 @@
         <v>137077942</v>
       </c>
       <c r="B179" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19770,7 +19770,7 @@
         <v>137078051</v>
       </c>
       <c r="B180" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19877,7 +19877,7 @@
         <v>136824825</v>
       </c>
       <c r="B181" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20096,7 +20096,7 @@
         <v>136974125</v>
       </c>
       <c r="B183" t="n">
-        <v>87546</v>
+        <v>87547</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20203,7 +20203,7 @@
         <v>137076843</v>
       </c>
       <c r="B184" t="n">
-        <v>91632</v>
+        <v>91633</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20341,7 +20341,7 @@
         <v>137078162</v>
       </c>
       <c r="B185" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>

--- a/artfynd/A 19253-2026 artfynd.xlsx
+++ b/artfynd/A 19253-2026 artfynd.xlsx
@@ -1529,7 +1529,7 @@
         <v>136824805</v>
       </c>
       <c r="B10" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>136824806</v>
       </c>
       <c r="B11" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>136824807</v>
       </c>
       <c r="B12" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>137073743</v>
       </c>
       <c r="B13" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>137073744</v>
       </c>
       <c r="B14" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>136974111</v>
       </c>
       <c r="B16" t="n">
-        <v>85742</v>
+        <v>85745</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>137077964</v>
       </c>
       <c r="B17" t="n">
-        <v>87420</v>
+        <v>87423</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>137100339</v>
       </c>
       <c r="B18" t="n">
-        <v>87627</v>
+        <v>87630</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>136824809</v>
       </c>
       <c r="B22" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>137073745</v>
       </c>
       <c r="B23" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>137073746</v>
       </c>
       <c r="B24" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>137078005</v>
       </c>
       <c r="B25" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>137073793</v>
       </c>
       <c r="B27" t="n">
-        <v>92833</v>
+        <v>92836</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>136824836</v>
       </c>
       <c r="B28" t="n">
-        <v>92512</v>
+        <v>92515</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136824831</v>
       </c>
       <c r="B29" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>136824832</v>
       </c>
       <c r="B30" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>136824833</v>
       </c>
       <c r="B31" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>137078053</v>
       </c>
       <c r="B32" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>136824816</v>
       </c>
       <c r="B34" t="n">
-        <v>96740</v>
+        <v>96745</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>137073749</v>
       </c>
       <c r="B35" t="n">
-        <v>96740</v>
+        <v>96745</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>137073750</v>
       </c>
       <c r="B36" t="n">
-        <v>96740</v>
+        <v>96745</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>137073751</v>
       </c>
       <c r="B37" t="n">
-        <v>96740</v>
+        <v>96745</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>136974096</v>
       </c>
       <c r="B43" t="n">
-        <v>91935</v>
+        <v>91938</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>136974097</v>
       </c>
       <c r="B44" t="n">
-        <v>87599</v>
+        <v>87602</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         <v>137077497</v>
       </c>
       <c r="B45" t="n">
-        <v>87599</v>
+        <v>87602</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>136824828</v>
       </c>
       <c r="B46" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>136974098</v>
       </c>
       <c r="B47" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>137073761</v>
       </c>
       <c r="B48" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         <v>137073762</v>
       </c>
       <c r="B49" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>137073763</v>
       </c>
       <c r="B50" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>137073764</v>
       </c>
       <c r="B51" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>137073765</v>
       </c>
       <c r="B52" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>137073766</v>
       </c>
       <c r="B53" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         <v>137073767</v>
       </c>
       <c r="B54" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         <v>137077917</v>
       </c>
       <c r="B55" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>137078067</v>
       </c>
       <c r="B56" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         <v>137078239</v>
       </c>
       <c r="B57" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         <v>137073794</v>
       </c>
       <c r="B58" t="n">
-        <v>92555</v>
+        <v>92558</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
         <v>136824823</v>
       </c>
       <c r="B63" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         <v>136824824</v>
       </c>
       <c r="B64" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>137073758</v>
       </c>
       <c r="B65" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         <v>137073759</v>
       </c>
       <c r="B66" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>137077540</v>
       </c>
       <c r="B68" t="n">
-        <v>89324</v>
+        <v>89327</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>137073747</v>
       </c>
       <c r="B72" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         <v>137073748</v>
       </c>
       <c r="B73" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>137078402</v>
       </c>
       <c r="B74" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         <v>136824808</v>
       </c>
       <c r="B77" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>137073773</v>
       </c>
       <c r="B82" t="n">
-        <v>91666</v>
+        <v>91669</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>136824839</v>
       </c>
       <c r="B83" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>136824840</v>
       </c>
       <c r="B84" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>136824841</v>
       </c>
       <c r="B85" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         <v>136974114</v>
       </c>
       <c r="B86" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         <v>136974115</v>
       </c>
       <c r="B87" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         <v>136974117</v>
       </c>
       <c r="B88" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10071,7 +10071,7 @@
         <v>136974118</v>
       </c>
       <c r="B89" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10173,7 +10173,7 @@
         <v>137073777</v>
       </c>
       <c r="B90" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
         <v>137073778</v>
       </c>
       <c r="B91" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
         <v>137073779</v>
       </c>
       <c r="B92" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10479,7 +10479,7 @@
         <v>137073780</v>
       </c>
       <c r="B93" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         <v>137073781</v>
       </c>
       <c r="B94" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10683,7 +10683,7 @@
         <v>137073782</v>
       </c>
       <c r="B95" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>137073783</v>
       </c>
       <c r="B96" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>137073784</v>
       </c>
       <c r="B97" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>137073785</v>
       </c>
       <c r="B98" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>137073786</v>
       </c>
       <c r="B99" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11193,7 +11193,7 @@
         <v>137073787</v>
       </c>
       <c r="B100" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11295,7 +11295,7 @@
         <v>137073788</v>
       </c>
       <c r="B101" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11397,7 +11397,7 @@
         <v>137073789</v>
       </c>
       <c r="B102" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
         <v>137077585</v>
       </c>
       <c r="B103" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>137077941</v>
       </c>
       <c r="B104" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>137078025</v>
       </c>
       <c r="B105" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>137078049</v>
       </c>
       <c r="B106" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11990,7 +11990,7 @@
         <v>137078081</v>
       </c>
       <c r="B107" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>136824829</v>
       </c>
       <c r="B108" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>136824830</v>
       </c>
       <c r="B109" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>136974101</v>
       </c>
       <c r="B110" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12425,7 +12425,7 @@
         <v>136974102</v>
       </c>
       <c r="B111" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>137073771</v>
       </c>
       <c r="B112" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         <v>136824810</v>
       </c>
       <c r="B120" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14786,7 +14786,7 @@
         <v>136824814</v>
       </c>
       <c r="B132" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>136824822</v>
       </c>
       <c r="B136" t="n">
-        <v>99383</v>
+        <v>99388</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15297,7 +15297,7 @@
         <v>137073756</v>
       </c>
       <c r="B137" t="n">
-        <v>99383</v>
+        <v>99388</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>137073757</v>
       </c>
       <c r="B138" t="n">
-        <v>99383</v>
+        <v>99388</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15501,7 +15501,7 @@
         <v>137077977</v>
       </c>
       <c r="B139" t="n">
-        <v>99383</v>
+        <v>99388</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15626,7 +15626,7 @@
         <v>136824842</v>
       </c>
       <c r="B140" t="n">
-        <v>108443</v>
+        <v>108448</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>136824843</v>
       </c>
       <c r="B141" t="n">
-        <v>108443</v>
+        <v>108448</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15830,7 +15830,7 @@
         <v>137077952</v>
       </c>
       <c r="B142" t="n">
-        <v>108443</v>
+        <v>108448</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>137073795</v>
       </c>
       <c r="B143" t="n">
-        <v>107127</v>
+        <v>107132</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16267,7 +16267,7 @@
         <v>136974104</v>
       </c>
       <c r="B146" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16782,7 +16782,7 @@
         <v>136824837</v>
       </c>
       <c r="B151" t="n">
-        <v>106557</v>
+        <v>106562</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16884,7 +16884,7 @@
         <v>136824800</v>
       </c>
       <c r="B152" t="n">
-        <v>102536</v>
+        <v>102541</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
         <v>136824801</v>
       </c>
       <c r="B153" t="n">
-        <v>102536</v>
+        <v>102541</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17088,7 +17088,7 @@
         <v>137073740</v>
       </c>
       <c r="B154" t="n">
-        <v>102536</v>
+        <v>102541</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17190,7 +17190,7 @@
         <v>137073741</v>
       </c>
       <c r="B155" t="n">
-        <v>102536</v>
+        <v>102541</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17292,7 +17292,7 @@
         <v>137073742</v>
       </c>
       <c r="B156" t="n">
-        <v>102536</v>
+        <v>102541</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17394,7 +17394,7 @@
         <v>137078125</v>
       </c>
       <c r="B157" t="n">
-        <v>102536</v>
+        <v>102541</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17511,7 +17511,7 @@
         <v>137073768</v>
       </c>
       <c r="B158" t="n">
-        <v>106912</v>
+        <v>106917</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17613,7 +17613,7 @@
         <v>137073769</v>
       </c>
       <c r="B159" t="n">
-        <v>106912</v>
+        <v>106917</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17817,7 +17817,7 @@
         <v>136824811</v>
       </c>
       <c r="B161" t="n">
-        <v>104937</v>
+        <v>104942</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17919,7 +17919,7 @@
         <v>136824812</v>
       </c>
       <c r="B162" t="n">
-        <v>104937</v>
+        <v>104942</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18735,7 +18735,7 @@
         <v>136824845</v>
       </c>
       <c r="B170" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18837,7 +18837,7 @@
         <v>136824847</v>
       </c>
       <c r="B171" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>136824848</v>
       </c>
       <c r="B172" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19041,7 +19041,7 @@
         <v>136824849</v>
       </c>
       <c r="B173" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         <v>136824850</v>
       </c>
       <c r="B174" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19245,7 +19245,7 @@
         <v>136824851</v>
       </c>
       <c r="B175" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19347,7 +19347,7 @@
         <v>136824852</v>
       </c>
       <c r="B176" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19449,7 +19449,7 @@
         <v>136824853</v>
       </c>
       <c r="B177" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>136824854</v>
       </c>
       <c r="B178" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19653,7 +19653,7 @@
         <v>137077942</v>
       </c>
       <c r="B179" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19770,7 +19770,7 @@
         <v>137078051</v>
       </c>
       <c r="B180" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19877,7 +19877,7 @@
         <v>136824825</v>
       </c>
       <c r="B181" t="n">
-        <v>99211</v>
+        <v>99216</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20096,7 +20096,7 @@
         <v>136974125</v>
       </c>
       <c r="B183" t="n">
-        <v>87547</v>
+        <v>87550</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20203,7 +20203,7 @@
         <v>137076843</v>
       </c>
       <c r="B184" t="n">
-        <v>91633</v>
+        <v>91636</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20341,7 +20341,7 @@
         <v>137078162</v>
       </c>
       <c r="B185" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>

--- a/artfynd/A 19253-2026 artfynd.xlsx
+++ b/artfynd/A 19253-2026 artfynd.xlsx
@@ -1529,7 +1529,7 @@
         <v>136824805</v>
       </c>
       <c r="B10" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>136824806</v>
       </c>
       <c r="B11" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>136824807</v>
       </c>
       <c r="B12" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>137073743</v>
       </c>
       <c r="B13" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>137073744</v>
       </c>
       <c r="B14" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>136824809</v>
       </c>
       <c r="B22" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>137073745</v>
       </c>
       <c r="B23" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>137073746</v>
       </c>
       <c r="B24" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>137078005</v>
       </c>
       <c r="B25" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>137073793</v>
       </c>
       <c r="B27" t="n">
-        <v>92836</v>
+        <v>92838</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>136824836</v>
       </c>
       <c r="B28" t="n">
-        <v>92515</v>
+        <v>92517</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136824831</v>
       </c>
       <c r="B29" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>136824832</v>
       </c>
       <c r="B30" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>136824833</v>
       </c>
       <c r="B31" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>137078053</v>
       </c>
       <c r="B32" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>136824816</v>
       </c>
       <c r="B34" t="n">
-        <v>96745</v>
+        <v>96747</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>137073749</v>
       </c>
       <c r="B35" t="n">
-        <v>96745</v>
+        <v>96747</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>137073750</v>
       </c>
       <c r="B36" t="n">
-        <v>96745</v>
+        <v>96747</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>137073751</v>
       </c>
       <c r="B37" t="n">
-        <v>96745</v>
+        <v>96747</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>136974096</v>
       </c>
       <c r="B43" t="n">
-        <v>91938</v>
+        <v>91940</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         <v>137073794</v>
       </c>
       <c r="B58" t="n">
-        <v>92558</v>
+        <v>92560</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
         <v>136824823</v>
       </c>
       <c r="B63" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         <v>136824824</v>
       </c>
       <c r="B64" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>137073758</v>
       </c>
       <c r="B65" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         <v>137073759</v>
       </c>
       <c r="B66" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>137073747</v>
       </c>
       <c r="B72" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         <v>137073748</v>
       </c>
       <c r="B73" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>137078402</v>
       </c>
       <c r="B74" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         <v>136824808</v>
       </c>
       <c r="B77" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>137073773</v>
       </c>
       <c r="B82" t="n">
-        <v>91669</v>
+        <v>91671</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>136824839</v>
       </c>
       <c r="B83" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>136824840</v>
       </c>
       <c r="B84" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>136824841</v>
       </c>
       <c r="B85" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         <v>136974114</v>
       </c>
       <c r="B86" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         <v>136974115</v>
       </c>
       <c r="B87" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         <v>136974117</v>
       </c>
       <c r="B88" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10071,7 +10071,7 @@
         <v>136974118</v>
       </c>
       <c r="B89" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10173,7 +10173,7 @@
         <v>137073777</v>
       </c>
       <c r="B90" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
         <v>137073778</v>
       </c>
       <c r="B91" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
         <v>137073779</v>
       </c>
       <c r="B92" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10479,7 +10479,7 @@
         <v>137073780</v>
       </c>
       <c r="B93" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         <v>137073781</v>
       </c>
       <c r="B94" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10683,7 +10683,7 @@
         <v>137073782</v>
       </c>
       <c r="B95" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>137073783</v>
       </c>
       <c r="B96" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>137073784</v>
       </c>
       <c r="B97" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>137073785</v>
       </c>
       <c r="B98" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>137073786</v>
       </c>
       <c r="B99" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11193,7 +11193,7 @@
         <v>137073787</v>
       </c>
       <c r="B100" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11295,7 +11295,7 @@
         <v>137073788</v>
       </c>
       <c r="B101" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11397,7 +11397,7 @@
         <v>137073789</v>
       </c>
       <c r="B102" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
         <v>137077585</v>
       </c>
       <c r="B103" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>137077941</v>
       </c>
       <c r="B104" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>137078025</v>
       </c>
       <c r="B105" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>137078049</v>
       </c>
       <c r="B106" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11990,7 +11990,7 @@
         <v>137078081</v>
       </c>
       <c r="B107" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>136824829</v>
       </c>
       <c r="B108" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>136824830</v>
       </c>
       <c r="B109" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>136974101</v>
       </c>
       <c r="B110" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12425,7 +12425,7 @@
         <v>136974102</v>
       </c>
       <c r="B111" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>137073771</v>
       </c>
       <c r="B112" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>136824822</v>
       </c>
       <c r="B136" t="n">
-        <v>99388</v>
+        <v>99390</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15297,7 +15297,7 @@
         <v>137073756</v>
       </c>
       <c r="B137" t="n">
-        <v>99388</v>
+        <v>99390</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>137073757</v>
       </c>
       <c r="B138" t="n">
-        <v>99388</v>
+        <v>99390</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15501,7 +15501,7 @@
         <v>137077977</v>
       </c>
       <c r="B139" t="n">
-        <v>99388</v>
+        <v>99390</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15626,7 +15626,7 @@
         <v>136824842</v>
       </c>
       <c r="B140" t="n">
-        <v>108448</v>
+        <v>108451</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>136824843</v>
       </c>
       <c r="B141" t="n">
-        <v>108448</v>
+        <v>108451</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15830,7 +15830,7 @@
         <v>137077952</v>
       </c>
       <c r="B142" t="n">
-        <v>108448</v>
+        <v>108451</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>137073795</v>
       </c>
       <c r="B143" t="n">
-        <v>107132</v>
+        <v>107135</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16267,7 +16267,7 @@
         <v>136974104</v>
       </c>
       <c r="B146" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16782,7 +16782,7 @@
         <v>136824837</v>
       </c>
       <c r="B151" t="n">
-        <v>106562</v>
+        <v>106565</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16884,7 +16884,7 @@
         <v>136824800</v>
       </c>
       <c r="B152" t="n">
-        <v>102541</v>
+        <v>102544</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
         <v>136824801</v>
       </c>
       <c r="B153" t="n">
-        <v>102541</v>
+        <v>102544</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17088,7 +17088,7 @@
         <v>137073740</v>
       </c>
       <c r="B154" t="n">
-        <v>102541</v>
+        <v>102544</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17190,7 +17190,7 @@
         <v>137073741</v>
       </c>
       <c r="B155" t="n">
-        <v>102541</v>
+        <v>102544</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17292,7 +17292,7 @@
         <v>137073742</v>
       </c>
       <c r="B156" t="n">
-        <v>102541</v>
+        <v>102544</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17394,7 +17394,7 @@
         <v>137078125</v>
       </c>
       <c r="B157" t="n">
-        <v>102541</v>
+        <v>102544</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17511,7 +17511,7 @@
         <v>137073768</v>
       </c>
       <c r="B158" t="n">
-        <v>106917</v>
+        <v>106920</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17613,7 +17613,7 @@
         <v>137073769</v>
       </c>
       <c r="B159" t="n">
-        <v>106917</v>
+        <v>106920</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17817,7 +17817,7 @@
         <v>136824811</v>
       </c>
       <c r="B161" t="n">
-        <v>104942</v>
+        <v>104945</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17919,7 +17919,7 @@
         <v>136824812</v>
       </c>
       <c r="B162" t="n">
-        <v>104942</v>
+        <v>104945</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18735,7 +18735,7 @@
         <v>136824845</v>
       </c>
       <c r="B170" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18837,7 +18837,7 @@
         <v>136824847</v>
       </c>
       <c r="B171" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>136824848</v>
       </c>
       <c r="B172" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19041,7 +19041,7 @@
         <v>136824849</v>
       </c>
       <c r="B173" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         <v>136824850</v>
       </c>
       <c r="B174" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19245,7 +19245,7 @@
         <v>136824851</v>
       </c>
       <c r="B175" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19347,7 +19347,7 @@
         <v>136824852</v>
       </c>
       <c r="B176" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19449,7 +19449,7 @@
         <v>136824853</v>
       </c>
       <c r="B177" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>136824854</v>
       </c>
       <c r="B178" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19653,7 +19653,7 @@
         <v>137077942</v>
       </c>
       <c r="B179" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19770,7 +19770,7 @@
         <v>137078051</v>
       </c>
       <c r="B180" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19877,7 +19877,7 @@
         <v>136824825</v>
       </c>
       <c r="B181" t="n">
-        <v>99216</v>
+        <v>99218</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20203,7 +20203,7 @@
         <v>137076843</v>
       </c>
       <c r="B184" t="n">
-        <v>91636</v>
+        <v>91638</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>

--- a/artfynd/A 19253-2026 artfynd.xlsx
+++ b/artfynd/A 19253-2026 artfynd.xlsx
@@ -1529,7 +1529,7 @@
         <v>136824805</v>
       </c>
       <c r="B10" t="n">
-        <v>97649</v>
+        <v>97655</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>136824806</v>
       </c>
       <c r="B11" t="n">
-        <v>97649</v>
+        <v>97655</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>136824807</v>
       </c>
       <c r="B12" t="n">
-        <v>97649</v>
+        <v>97655</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>137073743</v>
       </c>
       <c r="B13" t="n">
-        <v>97649</v>
+        <v>97655</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>137073744</v>
       </c>
       <c r="B14" t="n">
-        <v>97649</v>
+        <v>97655</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>136974111</v>
       </c>
       <c r="B16" t="n">
-        <v>85745</v>
+        <v>85750</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>137077964</v>
       </c>
       <c r="B17" t="n">
-        <v>87423</v>
+        <v>87428</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>137100339</v>
       </c>
       <c r="B18" t="n">
-        <v>87630</v>
+        <v>87635</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>136824809</v>
       </c>
       <c r="B22" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>137073745</v>
       </c>
       <c r="B23" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>137073746</v>
       </c>
       <c r="B24" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>137078005</v>
       </c>
       <c r="B25" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>137073793</v>
       </c>
       <c r="B27" t="n">
-        <v>92838</v>
+        <v>92843</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>136824836</v>
       </c>
       <c r="B28" t="n">
-        <v>92517</v>
+        <v>92522</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136824831</v>
       </c>
       <c r="B29" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>136824832</v>
       </c>
       <c r="B30" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>136824833</v>
       </c>
       <c r="B31" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>137078053</v>
       </c>
       <c r="B32" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>136824816</v>
       </c>
       <c r="B34" t="n">
-        <v>96747</v>
+        <v>96753</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>137073749</v>
       </c>
       <c r="B35" t="n">
-        <v>96747</v>
+        <v>96753</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>137073750</v>
       </c>
       <c r="B36" t="n">
-        <v>96747</v>
+        <v>96753</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>137073751</v>
       </c>
       <c r="B37" t="n">
-        <v>96747</v>
+        <v>96753</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>136974096</v>
       </c>
       <c r="B43" t="n">
-        <v>91940</v>
+        <v>91945</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>136974097</v>
       </c>
       <c r="B44" t="n">
-        <v>87602</v>
+        <v>87607</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         <v>137077497</v>
       </c>
       <c r="B45" t="n">
-        <v>87602</v>
+        <v>87607</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>136824828</v>
       </c>
       <c r="B46" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>136974098</v>
       </c>
       <c r="B47" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>137073761</v>
       </c>
       <c r="B48" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         <v>137073762</v>
       </c>
       <c r="B49" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>137073763</v>
       </c>
       <c r="B50" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>137073764</v>
       </c>
       <c r="B51" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>137073765</v>
       </c>
       <c r="B52" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>137073766</v>
       </c>
       <c r="B53" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         <v>137073767</v>
       </c>
       <c r="B54" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         <v>137077917</v>
       </c>
       <c r="B55" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>137078067</v>
       </c>
       <c r="B56" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         <v>137078239</v>
       </c>
       <c r="B57" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         <v>137073794</v>
       </c>
       <c r="B58" t="n">
-        <v>92560</v>
+        <v>92565</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
         <v>136824823</v>
       </c>
       <c r="B63" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7430,7 +7430,7 @@
         <v>136824824</v>
       </c>
       <c r="B64" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>137073758</v>
       </c>
       <c r="B65" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         <v>137073759</v>
       </c>
       <c r="B66" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>137077540</v>
       </c>
       <c r="B68" t="n">
-        <v>89327</v>
+        <v>89332</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>137073747</v>
       </c>
       <c r="B72" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         <v>137073748</v>
       </c>
       <c r="B73" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>137078402</v>
       </c>
       <c r="B74" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         <v>136824808</v>
       </c>
       <c r="B77" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>137073773</v>
       </c>
       <c r="B82" t="n">
-        <v>91671</v>
+        <v>91676</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>136824839</v>
       </c>
       <c r="B83" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>136824840</v>
       </c>
       <c r="B84" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>136824841</v>
       </c>
       <c r="B85" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         <v>136974114</v>
       </c>
       <c r="B86" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         <v>136974115</v>
       </c>
       <c r="B87" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         <v>136974117</v>
       </c>
       <c r="B88" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10071,7 +10071,7 @@
         <v>136974118</v>
       </c>
       <c r="B89" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10173,7 +10173,7 @@
         <v>137073777</v>
       </c>
       <c r="B90" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
         <v>137073778</v>
       </c>
       <c r="B91" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
         <v>137073779</v>
       </c>
       <c r="B92" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10479,7 +10479,7 @@
         <v>137073780</v>
       </c>
       <c r="B93" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         <v>137073781</v>
       </c>
       <c r="B94" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10683,7 +10683,7 @@
         <v>137073782</v>
       </c>
       <c r="B95" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10785,7 +10785,7 @@
         <v>137073783</v>
       </c>
       <c r="B96" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>137073784</v>
       </c>
       <c r="B97" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>137073785</v>
       </c>
       <c r="B98" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>137073786</v>
       </c>
       <c r="B99" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11193,7 +11193,7 @@
         <v>137073787</v>
       </c>
       <c r="B100" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11295,7 +11295,7 @@
         <v>137073788</v>
       </c>
       <c r="B101" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11397,7 +11397,7 @@
         <v>137073789</v>
       </c>
       <c r="B102" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
         <v>137077585</v>
       </c>
       <c r="B103" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>137077941</v>
       </c>
       <c r="B104" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>137078025</v>
       </c>
       <c r="B105" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>137078049</v>
       </c>
       <c r="B106" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11990,7 +11990,7 @@
         <v>137078081</v>
       </c>
       <c r="B107" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>136824829</v>
       </c>
       <c r="B108" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>136824830</v>
       </c>
       <c r="B109" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12323,7 +12323,7 @@
         <v>136974101</v>
       </c>
       <c r="B110" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12425,7 +12425,7 @@
         <v>136974102</v>
       </c>
       <c r="B111" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12527,7 +12527,7 @@
         <v>137073771</v>
       </c>
       <c r="B112" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14786,7 +14786,7 @@
         <v>136824814</v>
       </c>
       <c r="B132" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>136824822</v>
       </c>
       <c r="B136" t="n">
-        <v>99390</v>
+        <v>99396</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15297,7 +15297,7 @@
         <v>137073756</v>
       </c>
       <c r="B137" t="n">
-        <v>99390</v>
+        <v>99396</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>137073757</v>
       </c>
       <c r="B138" t="n">
-        <v>99390</v>
+        <v>99396</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15501,7 +15501,7 @@
         <v>137077977</v>
       </c>
       <c r="B139" t="n">
-        <v>99390</v>
+        <v>99396</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15626,7 +15626,7 @@
         <v>136824842</v>
       </c>
       <c r="B140" t="n">
-        <v>108451</v>
+        <v>108457</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>136824843</v>
       </c>
       <c r="B141" t="n">
-        <v>108451</v>
+        <v>108457</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15830,7 +15830,7 @@
         <v>137077952</v>
       </c>
       <c r="B142" t="n">
-        <v>108451</v>
+        <v>108457</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>137073795</v>
       </c>
       <c r="B143" t="n">
-        <v>107135</v>
+        <v>107141</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16267,7 +16267,7 @@
         <v>136974104</v>
       </c>
       <c r="B146" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16782,7 +16782,7 @@
         <v>136824837</v>
       </c>
       <c r="B151" t="n">
-        <v>106565</v>
+        <v>106571</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16884,7 +16884,7 @@
         <v>136824800</v>
       </c>
       <c r="B152" t="n">
-        <v>102544</v>
+        <v>102550</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
         <v>136824801</v>
       </c>
       <c r="B153" t="n">
-        <v>102544</v>
+        <v>102550</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17088,7 +17088,7 @@
         <v>137073740</v>
       </c>
       <c r="B154" t="n">
-        <v>102544</v>
+        <v>102550</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17190,7 +17190,7 @@
         <v>137073741</v>
       </c>
       <c r="B155" t="n">
-        <v>102544</v>
+        <v>102550</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17292,7 +17292,7 @@
         <v>137073742</v>
       </c>
       <c r="B156" t="n">
-        <v>102544</v>
+        <v>102550</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17394,7 +17394,7 @@
         <v>137078125</v>
       </c>
       <c r="B157" t="n">
-        <v>102544</v>
+        <v>102550</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17511,7 +17511,7 @@
         <v>137073768</v>
       </c>
       <c r="B158" t="n">
-        <v>106920</v>
+        <v>106926</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17613,7 +17613,7 @@
         <v>137073769</v>
       </c>
       <c r="B159" t="n">
-        <v>106920</v>
+        <v>106926</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17817,7 +17817,7 @@
         <v>136824811</v>
       </c>
       <c r="B161" t="n">
-        <v>104945</v>
+        <v>104951</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17919,7 +17919,7 @@
         <v>136824812</v>
       </c>
       <c r="B162" t="n">
-        <v>104945</v>
+        <v>104951</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18735,7 +18735,7 @@
         <v>136824845</v>
       </c>
       <c r="B170" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18837,7 +18837,7 @@
         <v>136824847</v>
       </c>
       <c r="B171" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>136824848</v>
       </c>
       <c r="B172" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19041,7 +19041,7 @@
         <v>136824849</v>
       </c>
       <c r="B173" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         <v>136824850</v>
       </c>
       <c r="B174" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19245,7 +19245,7 @@
         <v>136824851</v>
       </c>
       <c r="B175" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19347,7 +19347,7 @@
         <v>136824852</v>
       </c>
       <c r="B176" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19449,7 +19449,7 @@
         <v>136824853</v>
       </c>
       <c r="B177" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>136824854</v>
       </c>
       <c r="B178" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19653,7 +19653,7 @@
         <v>137077942</v>
       </c>
       <c r="B179" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19770,7 +19770,7 @@
         <v>137078051</v>
       </c>
       <c r="B180" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19877,7 +19877,7 @@
         <v>136824825</v>
       </c>
       <c r="B181" t="n">
-        <v>99218</v>
+        <v>99224</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20096,7 +20096,7 @@
         <v>136974125</v>
       </c>
       <c r="B183" t="n">
-        <v>87550</v>
+        <v>87555</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20203,7 +20203,7 @@
         <v>137076843</v>
       </c>
       <c r="B184" t="n">
-        <v>91638</v>
+        <v>91643</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20341,7 +20341,7 @@
         <v>137078162</v>
       </c>
       <c r="B185" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>

--- a/artfynd/A 19253-2026 artfynd.xlsx
+++ b/artfynd/A 19253-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ185"/>
+  <dimension ref="A1:AZ186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5274,48 +5274,55 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>136974097</v>
+        <v>137411764</v>
       </c>
       <c r="B44" t="n">
-        <v>87607</v>
+        <v>87644</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3739</v>
+        <v>3624</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Quél.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>668446</v>
+        <v>668622</v>
       </c>
       <c r="R44" t="n">
-        <v>6691728</v>
+        <v>6691620</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5339,12 +5346,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5353,30 +5370,45 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Under gran och tall; kalk</t>
+        </is>
+      </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>Kollekt</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Björn Bråvander, Ingemar Södergren, Klara Tellebo, Malin Hylland</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136974097</t>
+          <t>https://artportalen.se/Sighting/137411764</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>137077497</v>
+        <v>136974097</v>
       </c>
       <c r="B45" t="n">
         <v>87607</v>
@@ -5404,31 +5436,20 @@
           <t>Quél.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>668665</v>
+        <v>668446</v>
       </c>
       <c r="R45" t="n">
-        <v>6691952</v>
+        <v>6691728</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5452,22 +5473,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>12:03</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>12:03</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5476,72 +5487,82 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Björn Bråvander, Ingemar Södergren, Klara Tellebo, Malin Hylland</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137077497</t>
+          <t>https://artportalen.se/Sighting/136974097</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>136824828</v>
+        <v>137077497</v>
       </c>
       <c r="B46" t="n">
-        <v>87378</v>
+        <v>87607</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3762</v>
+        <v>3739</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>668740</v>
+        <v>668665</v>
       </c>
       <c r="R46" t="n">
-        <v>6691904</v>
+        <v>6691952</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5565,12 +5586,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5579,30 +5610,31 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Björn Bråvander, Ingemar Södergren, Klara Tellebo, Malin Hylland</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824828</t>
+          <t>https://artportalen.se/Sighting/137077497</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>136974098</v>
+        <v>136824828</v>
       </c>
       <c r="B47" t="n">
         <v>87378</v>
@@ -5637,10 +5669,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>668693</v>
+        <v>668740</v>
       </c>
       <c r="R47" t="n">
-        <v>6691751</v>
+        <v>6691904</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5667,12 +5699,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5698,13 +5730,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136974098</t>
+          <t>https://artportalen.se/Sighting/136824828</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>137073761</v>
+        <v>136974098</v>
       </c>
       <c r="B48" t="n">
         <v>87378</v>
@@ -5739,10 +5771,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>668739</v>
+        <v>668693</v>
       </c>
       <c r="R48" t="n">
-        <v>6691898</v>
+        <v>6691751</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5769,12 +5801,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5794,19 +5826,19 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Björn Bråvander, Malin Hylland, Klara Tellebo</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073761</t>
+          <t>https://artportalen.se/Sighting/136974098</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>137073762</v>
+        <v>137073761</v>
       </c>
       <c r="B49" t="n">
         <v>87378</v>
@@ -5841,10 +5873,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>668763</v>
+        <v>668739</v>
       </c>
       <c r="R49" t="n">
-        <v>6691904</v>
+        <v>6691898</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5902,13 +5934,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073762</t>
+          <t>https://artportalen.se/Sighting/137073761</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>137073763</v>
+        <v>137073762</v>
       </c>
       <c r="B50" t="n">
         <v>87378</v>
@@ -5943,10 +5975,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>668704</v>
+        <v>668763</v>
       </c>
       <c r="R50" t="n">
-        <v>6691755</v>
+        <v>6691904</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6004,13 +6036,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073763</t>
+          <t>https://artportalen.se/Sighting/137073762</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>137073764</v>
+        <v>137073763</v>
       </c>
       <c r="B51" t="n">
         <v>87378</v>
@@ -6045,10 +6077,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>668654</v>
+        <v>668704</v>
       </c>
       <c r="R51" t="n">
-        <v>6691652</v>
+        <v>6691755</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6106,13 +6138,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073764</t>
+          <t>https://artportalen.se/Sighting/137073763</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>137073765</v>
+        <v>137073764</v>
       </c>
       <c r="B52" t="n">
         <v>87378</v>
@@ -6147,10 +6179,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>668574</v>
+        <v>668654</v>
       </c>
       <c r="R52" t="n">
-        <v>6691641</v>
+        <v>6691652</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6208,13 +6240,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073765</t>
+          <t>https://artportalen.se/Sighting/137073764</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>137073766</v>
+        <v>137073765</v>
       </c>
       <c r="B53" t="n">
         <v>87378</v>
@@ -6249,10 +6281,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>668563</v>
+        <v>668574</v>
       </c>
       <c r="R53" t="n">
-        <v>6691645</v>
+        <v>6691641</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6310,13 +6342,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073766</t>
+          <t>https://artportalen.se/Sighting/137073765</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>137073767</v>
+        <v>137073766</v>
       </c>
       <c r="B54" t="n">
         <v>87378</v>
@@ -6351,10 +6383,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>668592</v>
+        <v>668563</v>
       </c>
       <c r="R54" t="n">
-        <v>6691692</v>
+        <v>6691645</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6412,13 +6444,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073767</t>
+          <t>https://artportalen.se/Sighting/137073766</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>137077917</v>
+        <v>137073767</v>
       </c>
       <c r="B55" t="n">
         <v>87378</v>
@@ -6446,31 +6478,20 @@
           <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>668737</v>
+        <v>668592</v>
       </c>
       <c r="R55" t="n">
-        <v>6691901</v>
+        <v>6691692</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6497,52 +6518,41 @@
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>13:24</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>13:24</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Björn Bråvander, Ingemar Södergren, Klara Tellebo, Malin Hylland</t>
+          <t>Ingemar Södergren, Björn Bråvander, Malin Hylland, Klara Tellebo</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137077917</t>
+          <t>https://artportalen.se/Sighting/137073767</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>137078067</v>
+        <v>137077917</v>
       </c>
       <c r="B56" t="n">
         <v>87378</v>
@@ -6572,7 +6582,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6588,10 +6598,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>668823</v>
+        <v>668737</v>
       </c>
       <c r="R56" t="n">
-        <v>6691892</v>
+        <v>6691901</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6623,7 +6633,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6633,7 +6643,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6660,13 +6670,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137078067</t>
+          <t>https://artportalen.se/Sighting/137077917</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>137078239</v>
+        <v>137078067</v>
       </c>
       <c r="B57" t="n">
         <v>87378</v>
@@ -6696,7 +6706,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6712,10 +6722,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>668692</v>
+        <v>668823</v>
       </c>
       <c r="R57" t="n">
-        <v>6691756</v>
+        <v>6691892</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6745,9 +6755,19 @@
           <t>2026-10-04</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6774,16 +6794,16 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137078239</t>
+          <t>https://artportalen.se/Sighting/137078067</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>137073794</v>
+        <v>137078239</v>
       </c>
       <c r="B58" t="n">
-        <v>92565</v>
+        <v>87378</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6791,37 +6811,48 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4217</v>
+        <v>3762</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>668738</v>
+        <v>668692</v>
       </c>
       <c r="R58" t="n">
-        <v>6691827</v>
+        <v>6691756</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6859,83 +6890,69 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Björn Bråvander, Malin Hylland, Klara Tellebo</t>
+          <t>Björn Bråvander, Ingemar Södergren, Klara Tellebo, Malin Hylland</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073794</t>
+          <t>https://artportalen.se/Sighting/137078239</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128344134</v>
+        <v>137073794</v>
       </c>
       <c r="B59" t="n">
-        <v>93189</v>
+        <v>92565</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4361</v>
+        <v>4217</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>668502</v>
+        <v>668738</v>
       </c>
       <c r="R59" t="n">
-        <v>6691868</v>
+        <v>6691827</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6962,17 +6979,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Tallhällmark</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6983,31 +6995,46 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren, Björn Bråvander, Malin Hylland, Klara Tellebo</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128344134</t>
+          <t>https://artportalen.se/Sighting/137073794</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128260557</v>
+        <v>128344134</v>
       </c>
       <c r="B60" t="n">
-        <v>93209</v>
+        <v>93189</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7015,37 +7042,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>668414</v>
+        <v>668502</v>
       </c>
       <c r="R60" t="n">
-        <v>6691754</v>
+        <v>6691868</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7075,6 +7102,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Tallhällmark</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7089,24 +7121,24 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260557</t>
+          <t>https://artportalen.se/Sighting/128344134</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128260558</v>
+        <v>128260557</v>
       </c>
       <c r="B61" t="n">
         <v>93209</v>
@@ -7141,10 +7173,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>668442</v>
+        <v>668414</v>
       </c>
       <c r="R61" t="n">
-        <v>6691699</v>
+        <v>6691754</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7202,13 +7234,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260558</t>
+          <t>https://artportalen.se/Sighting/128260557</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128344129</v>
+        <v>128260558</v>
       </c>
       <c r="B62" t="n">
         <v>93209</v>
@@ -7239,17 +7271,17 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>668557</v>
+        <v>668442</v>
       </c>
       <c r="R62" t="n">
-        <v>6691949</v>
+        <v>6691699</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7293,27 +7325,27 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128344129</t>
+          <t>https://artportalen.se/Sighting/128260558</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>136824823</v>
+        <v>128344129</v>
       </c>
       <c r="B63" t="n">
-        <v>93481</v>
+        <v>93209</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7341,14 +7373,14 @@
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>668485</v>
+        <v>668557</v>
       </c>
       <c r="R63" t="n">
-        <v>6691765</v>
+        <v>6691949</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7375,27 +7407,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>16:47</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>16:47</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7410,24 +7427,24 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824823</t>
+          <t>https://artportalen.se/Sighting/128344129</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>136824824</v>
+        <v>136824823</v>
       </c>
       <c r="B64" t="n">
         <v>93481</v>
@@ -7462,10 +7479,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>668737</v>
+        <v>668485</v>
       </c>
       <c r="R64" t="n">
-        <v>6691854</v>
+        <v>6691765</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7497,7 +7514,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7507,12 +7524,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7538,13 +7555,13 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824824</t>
+          <t>https://artportalen.se/Sighting/136824823</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>137073758</v>
+        <v>136824824</v>
       </c>
       <c r="B65" t="n">
         <v>93481</v>
@@ -7579,10 +7596,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>668751</v>
+        <v>668737</v>
       </c>
       <c r="R65" t="n">
-        <v>6691899</v>
+        <v>6691854</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7609,12 +7626,27 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7634,19 +7666,19 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Björn Bråvander, Malin Hylland, Klara Tellebo</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073758</t>
+          <t>https://artportalen.se/Sighting/136824824</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>137073759</v>
+        <v>137073758</v>
       </c>
       <c r="B66" t="n">
         <v>93481</v>
@@ -7681,10 +7713,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>668734</v>
+        <v>668751</v>
       </c>
       <c r="R66" t="n">
-        <v>6691852</v>
+        <v>6691899</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7742,16 +7774,16 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073759</t>
+          <t>https://artportalen.se/Sighting/137073758</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127382963</v>
+        <v>137073759</v>
       </c>
       <c r="B67" t="n">
-        <v>93215</v>
+        <v>93481</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7759,21 +7791,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4368</v>
+        <v>4366</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7783,13 +7815,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>668299</v>
+        <v>668734</v>
       </c>
       <c r="R67" t="n">
-        <v>6691892</v>
+        <v>6691852</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7813,12 +7845,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7838,71 +7870,60 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Ingemar Södergren, Björn Bråvander, Malin Hylland, Klara Tellebo</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127382963</t>
+          <t>https://artportalen.se/Sighting/137073759</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>137077540</v>
+        <v>127382963</v>
       </c>
       <c r="B68" t="n">
-        <v>89332</v>
+        <v>93215</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4383</v>
+        <v>4368</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Småvaxing</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hygrocybe insipida</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(J.E.Lange) M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>668653</v>
+        <v>668299</v>
       </c>
       <c r="R68" t="n">
-        <v>6691945</v>
+        <v>6691892</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7926,22 +7947,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>12:05</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>12:05</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7950,34 +7961,33 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Björn Bråvander, Ingemar Södergren, Klara Tellebo, Malin Hylland</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137077540</t>
+          <t>https://artportalen.se/Sighting/127382963</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128260548</v>
+        <v>137077540</v>
       </c>
       <c r="B69" t="n">
-        <v>92869</v>
+        <v>89332</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7985,37 +7995,48 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4769</v>
+        <v>4383</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Småvaxing</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hygrocybe insipida</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(J.E.Lange) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>668572</v>
+        <v>668653</v>
       </c>
       <c r="R69" t="n">
-        <v>6691927</v>
+        <v>6691945</v>
       </c>
       <c r="S69" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8039,12 +8060,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8053,30 +8084,31 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Björn Bråvander, Ingemar Södergren, Klara Tellebo, Malin Hylland</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260548</t>
+          <t>https://artportalen.se/Sighting/137077540</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128344126</v>
+        <v>128260548</v>
       </c>
       <c r="B70" t="n">
         <v>92869</v>
@@ -8107,17 +8139,17 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>668368</v>
+        <v>668572</v>
       </c>
       <c r="R70" t="n">
-        <v>6691735</v>
+        <v>6691927</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8161,24 +8193,24 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128344126</t>
+          <t>https://artportalen.se/Sighting/128260548</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128344127</v>
+        <v>128344126</v>
       </c>
       <c r="B71" t="n">
         <v>92869</v>
@@ -8213,10 +8245,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>668594</v>
+        <v>668368</v>
       </c>
       <c r="R71" t="n">
-        <v>6691661</v>
+        <v>6691735</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8274,16 +8306,16 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128344127</t>
+          <t>https://artportalen.se/Sighting/128344126</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>137073747</v>
+        <v>128344127</v>
       </c>
       <c r="B72" t="n">
-        <v>93140</v>
+        <v>92869</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8311,14 +8343,14 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>668704</v>
+        <v>668594</v>
       </c>
       <c r="R72" t="n">
-        <v>6691657</v>
+        <v>6691661</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8345,12 +8377,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8365,24 +8397,24 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Björn Bråvander, Malin Hylland, Klara Tellebo</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073747</t>
+          <t>https://artportalen.se/Sighting/128344127</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>137073748</v>
+        <v>137073747</v>
       </c>
       <c r="B73" t="n">
         <v>93140</v>
@@ -8417,10 +8449,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>668709</v>
+        <v>668704</v>
       </c>
       <c r="R73" t="n">
-        <v>6691655</v>
+        <v>6691657</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8478,13 +8510,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073748</t>
+          <t>https://artportalen.se/Sighting/137073747</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>137078402</v>
+        <v>137073748</v>
       </c>
       <c r="B74" t="n">
         <v>93140</v>
@@ -8513,22 +8545,19 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>668618</v>
+        <v>668709</v>
       </c>
       <c r="R74" t="n">
-        <v>6691630</v>
+        <v>6691655</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8566,34 +8595,33 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Björn Bråvander, Ingemar Södergren, Klara Tellebo, Malin Hylland</t>
+          <t>Ingemar Södergren, Björn Bråvander, Malin Hylland, Klara Tellebo</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137078402</t>
+          <t>https://artportalen.se/Sighting/137073748</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128953969</v>
+        <v>137078402</v>
       </c>
       <c r="B75" t="n">
-        <v>91872</v>
+        <v>93140</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8601,37 +8629,40 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5447</v>
+        <v>4769</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>668650</v>
+        <v>668618</v>
       </c>
       <c r="R75" t="n">
-        <v>6691679</v>
+        <v>6691630</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8655,12 +8686,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8669,30 +8700,31 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Björn Bråvander, Ingemar Södergren, Klara Tellebo, Malin Hylland</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128953969</t>
+          <t>https://artportalen.se/Sighting/137078402</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128953970</v>
+        <v>128953969</v>
       </c>
       <c r="B76" t="n">
         <v>91872</v>
@@ -8727,10 +8759,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>668676</v>
+        <v>668650</v>
       </c>
       <c r="R76" t="n">
-        <v>6691606</v>
+        <v>6691679</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8774,21 +8806,6 @@
       <c r="AG76" t="b">
         <v>0</v>
       </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
@@ -8803,16 +8820,16 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128953970</t>
+          <t>https://artportalen.se/Sighting/128953969</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>136824808</v>
+        <v>128953970</v>
       </c>
       <c r="B77" t="n">
-        <v>92132</v>
+        <v>91872</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8844,13 +8861,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>668651</v>
+        <v>668676</v>
       </c>
       <c r="R77" t="n">
-        <v>6691678</v>
+        <v>6691606</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8874,12 +8891,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8920,38 +8937,38 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824808</t>
+          <t>https://artportalen.se/Sighting/128953970</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128260549</v>
+        <v>136824808</v>
       </c>
       <c r="B78" t="n">
-        <v>93223</v>
+        <v>92132</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5448</v>
+        <v>5447</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8961,13 +8978,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>668507</v>
+        <v>668651</v>
       </c>
       <c r="R78" t="n">
-        <v>6691854</v>
+        <v>6691678</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8991,12 +9008,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9008,9 +9025,19 @@
       <c r="AG78" t="b">
         <v>0</v>
       </c>
-      <c r="AI78" t="inlineStr">
-        <is>
-          <t>Tallhällmark</t>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9027,38 +9054,38 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260549</t>
+          <t>https://artportalen.se/Sighting/136824808</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128260564</v>
+        <v>128260549</v>
       </c>
       <c r="B79" t="n">
-        <v>91435</v>
+        <v>93223</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5747</v>
+        <v>5448</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9068,10 +9095,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>668588</v>
+        <v>668507</v>
       </c>
       <c r="R79" t="n">
-        <v>6691696</v>
+        <v>6691854</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9115,6 +9142,11 @@
       <c r="AG79" t="b">
         <v>0</v>
       </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>Tallhällmark</t>
+        </is>
+      </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
@@ -9129,13 +9161,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260564</t>
+          <t>https://artportalen.se/Sighting/128260549</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128260565</v>
+        <v>128260564</v>
       </c>
       <c r="B80" t="n">
         <v>91435</v>
@@ -9170,10 +9202,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>668592</v>
+        <v>668588</v>
       </c>
       <c r="R80" t="n">
-        <v>6691678</v>
+        <v>6691696</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9231,13 +9263,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260565</t>
+          <t>https://artportalen.se/Sighting/128260564</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128953983</v>
+        <v>128260565</v>
       </c>
       <c r="B81" t="n">
         <v>91435</v>
@@ -9272,13 +9304,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>668689</v>
+        <v>668592</v>
       </c>
       <c r="R81" t="n">
-        <v>6691641</v>
+        <v>6691678</v>
       </c>
       <c r="S81" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9302,12 +9334,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9333,16 +9365,16 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128953983</t>
+          <t>https://artportalen.se/Sighting/128260565</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>137073773</v>
+        <v>128953983</v>
       </c>
       <c r="B82" t="n">
-        <v>91676</v>
+        <v>91435</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9374,13 +9406,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>668693</v>
+        <v>668689</v>
       </c>
       <c r="R82" t="n">
-        <v>6691645</v>
+        <v>6691641</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9404,22 +9436,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>15:38</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>15:38</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9439,44 +9461,44 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Björn Bråvander, Malin Hylland, Klara Tellebo</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073773</t>
+          <t>https://artportalen.se/Sighting/128953983</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>136824839</v>
+        <v>137073773</v>
       </c>
       <c r="B83" t="n">
-        <v>93505</v>
+        <v>91676</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5964</v>
+        <v>5747</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9486,10 +9508,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>668732</v>
+        <v>668693</v>
       </c>
       <c r="R83" t="n">
-        <v>6691872</v>
+        <v>6691645</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9516,12 +9538,22 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9541,19 +9573,19 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Ingemar Södergren, Björn Bråvander, Malin Hylland, Klara Tellebo</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824839</t>
+          <t>https://artportalen.se/Sighting/137073773</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>136824840</v>
+        <v>136824839</v>
       </c>
       <c r="B84" t="n">
         <v>93505</v>
@@ -9588,10 +9620,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>668777</v>
+        <v>668732</v>
       </c>
       <c r="R84" t="n">
-        <v>6691909</v>
+        <v>6691872</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9626,11 +9658,6 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -9654,13 +9681,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824840</t>
+          <t>https://artportalen.se/Sighting/136824839</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>136824841</v>
+        <v>136824840</v>
       </c>
       <c r="B85" t="n">
         <v>93505</v>
@@ -9695,10 +9722,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>668789</v>
+        <v>668777</v>
       </c>
       <c r="R85" t="n">
-        <v>6691922</v>
+        <v>6691909</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9733,6 +9760,11 @@
           <t>2026-09-23</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -9756,13 +9788,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824841</t>
+          <t>https://artportalen.se/Sighting/136824840</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>136974114</v>
+        <v>136824841</v>
       </c>
       <c r="B86" t="n">
         <v>93505</v>
@@ -9797,10 +9829,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>668581</v>
+        <v>668789</v>
       </c>
       <c r="R86" t="n">
-        <v>6691696</v>
+        <v>6691922</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9827,12 +9859,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9858,13 +9890,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136974114</t>
+          <t>https://artportalen.se/Sighting/136824841</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>136974115</v>
+        <v>136974114</v>
       </c>
       <c r="B87" t="n">
         <v>93505</v>
@@ -9899,10 +9931,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>668702</v>
+        <v>668581</v>
       </c>
       <c r="R87" t="n">
-        <v>6691798</v>
+        <v>6691696</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9960,13 +9992,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136974115</t>
+          <t>https://artportalen.se/Sighting/136974114</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>136974117</v>
+        <v>136974115</v>
       </c>
       <c r="B88" t="n">
         <v>93505</v>
@@ -10001,10 +10033,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>668734</v>
+        <v>668702</v>
       </c>
       <c r="R88" t="n">
-        <v>6691842</v>
+        <v>6691798</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10062,13 +10094,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136974117</t>
+          <t>https://artportalen.se/Sighting/136974115</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>136974118</v>
+        <v>136974117</v>
       </c>
       <c r="B89" t="n">
         <v>93505</v>
@@ -10103,10 +10135,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>668739</v>
+        <v>668734</v>
       </c>
       <c r="R89" t="n">
-        <v>6691890</v>
+        <v>6691842</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10164,13 +10196,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136974118</t>
+          <t>https://artportalen.se/Sighting/136974117</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>137073777</v>
+        <v>136974118</v>
       </c>
       <c r="B90" t="n">
         <v>93505</v>
@@ -10205,10 +10237,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>668748</v>
+        <v>668739</v>
       </c>
       <c r="R90" t="n">
-        <v>6691889</v>
+        <v>6691890</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10235,12 +10267,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10260,19 +10292,19 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Björn Bråvander, Malin Hylland, Klara Tellebo</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073777</t>
+          <t>https://artportalen.se/Sighting/136974118</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>137073778</v>
+        <v>137073777</v>
       </c>
       <c r="B91" t="n">
         <v>93505</v>
@@ -10307,10 +10339,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>668762</v>
+        <v>668748</v>
       </c>
       <c r="R91" t="n">
-        <v>6691899</v>
+        <v>6691889</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10368,13 +10400,13 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073778</t>
+          <t>https://artportalen.se/Sighting/137073777</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>137073779</v>
+        <v>137073778</v>
       </c>
       <c r="B92" t="n">
         <v>93505</v>
@@ -10409,10 +10441,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>668765</v>
+        <v>668762</v>
       </c>
       <c r="R92" t="n">
-        <v>6691894</v>
+        <v>6691899</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10470,13 +10502,13 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073779</t>
+          <t>https://artportalen.se/Sighting/137073778</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>137073780</v>
+        <v>137073779</v>
       </c>
       <c r="B93" t="n">
         <v>93505</v>
@@ -10511,10 +10543,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>668764</v>
+        <v>668765</v>
       </c>
       <c r="R93" t="n">
-        <v>6691884</v>
+        <v>6691894</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10572,13 +10604,13 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073780</t>
+          <t>https://artportalen.se/Sighting/137073779</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>137073781</v>
+        <v>137073780</v>
       </c>
       <c r="B94" t="n">
         <v>93505</v>
@@ -10613,10 +10645,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>668734</v>
+        <v>668764</v>
       </c>
       <c r="R94" t="n">
-        <v>6691864</v>
+        <v>6691884</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10674,13 +10706,13 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073781</t>
+          <t>https://artportalen.se/Sighting/137073780</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>137073782</v>
+        <v>137073781</v>
       </c>
       <c r="B95" t="n">
         <v>93505</v>
@@ -10715,10 +10747,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>668735</v>
+        <v>668734</v>
       </c>
       <c r="R95" t="n">
-        <v>6691883</v>
+        <v>6691864</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10776,13 +10808,13 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073782</t>
+          <t>https://artportalen.se/Sighting/137073781</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>137073783</v>
+        <v>137073782</v>
       </c>
       <c r="B96" t="n">
         <v>93505</v>
@@ -10817,10 +10849,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>668732</v>
+        <v>668735</v>
       </c>
       <c r="R96" t="n">
-        <v>6691852</v>
+        <v>6691883</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10878,13 +10910,13 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073783</t>
+          <t>https://artportalen.se/Sighting/137073782</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>137073784</v>
+        <v>137073783</v>
       </c>
       <c r="B97" t="n">
         <v>93505</v>
@@ -10919,10 +10951,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>668795</v>
+        <v>668732</v>
       </c>
       <c r="R97" t="n">
-        <v>6691923</v>
+        <v>6691852</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10980,13 +11012,13 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073784</t>
+          <t>https://artportalen.se/Sighting/137073783</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>137073785</v>
+        <v>137073784</v>
       </c>
       <c r="B98" t="n">
         <v>93505</v>
@@ -11021,10 +11053,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>668698</v>
+        <v>668795</v>
       </c>
       <c r="R98" t="n">
-        <v>6691736</v>
+        <v>6691923</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11082,13 +11114,13 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073785</t>
+          <t>https://artportalen.se/Sighting/137073784</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>137073786</v>
+        <v>137073785</v>
       </c>
       <c r="B99" t="n">
         <v>93505</v>
@@ -11123,13 +11155,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>668707</v>
+        <v>668698</v>
       </c>
       <c r="R99" t="n">
-        <v>6691654</v>
+        <v>6691736</v>
       </c>
       <c r="S99" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11184,13 +11216,13 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073786</t>
+          <t>https://artportalen.se/Sighting/137073785</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>137073787</v>
+        <v>137073786</v>
       </c>
       <c r="B100" t="n">
         <v>93505</v>
@@ -11225,13 +11257,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>668651</v>
+        <v>668707</v>
       </c>
       <c r="R100" t="n">
-        <v>6691678</v>
+        <v>6691654</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11286,13 +11318,13 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073787</t>
+          <t>https://artportalen.se/Sighting/137073786</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>137073788</v>
+        <v>137073787</v>
       </c>
       <c r="B101" t="n">
         <v>93505</v>
@@ -11327,10 +11359,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>668658</v>
+        <v>668651</v>
       </c>
       <c r="R101" t="n">
-        <v>6691654</v>
+        <v>6691678</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11388,13 +11420,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073788</t>
+          <t>https://artportalen.se/Sighting/137073787</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>137073789</v>
+        <v>137073788</v>
       </c>
       <c r="B102" t="n">
         <v>93505</v>
@@ -11429,10 +11461,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>668563</v>
+        <v>668658</v>
       </c>
       <c r="R102" t="n">
-        <v>6691653</v>
+        <v>6691654</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11490,13 +11522,13 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073789</t>
+          <t>https://artportalen.se/Sighting/137073788</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>137077585</v>
+        <v>137073789</v>
       </c>
       <c r="B103" t="n">
         <v>93505</v>
@@ -11524,31 +11556,20 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>668741</v>
+        <v>668563</v>
       </c>
       <c r="R103" t="n">
-        <v>6691885</v>
+        <v>6691653</v>
       </c>
       <c r="S103" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11580,42 +11601,36 @@
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Minst 40 frk i stor ring (del av ring)</t>
-        </is>
-      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Björn Bråvander, Ingemar Södergren, Klara Tellebo, Malin Hylland</t>
+          <t>Ingemar Södergren, Björn Bråvander, Malin Hylland, Klara Tellebo</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137077585</t>
+          <t>https://artportalen.se/Sighting/137073789</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>137077941</v>
+        <v>137077585</v>
       </c>
       <c r="B104" t="n">
         <v>93505</v>
@@ -11645,7 +11660,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -11661,10 +11676,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>668771</v>
+        <v>668741</v>
       </c>
       <c r="R104" t="n">
-        <v>6691879</v>
+        <v>6691885</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -11694,19 +11709,14 @@
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>13:38</t>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Minst 40 frk i stor ring (del av ring)</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11733,13 +11743,13 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137077941</t>
+          <t>https://artportalen.se/Sighting/137077585</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>137078025</v>
+        <v>137077941</v>
       </c>
       <c r="B105" t="n">
         <v>93505</v>
@@ -11769,7 +11779,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -11785,10 +11795,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>668819</v>
+        <v>668771</v>
       </c>
       <c r="R105" t="n">
-        <v>6691906</v>
+        <v>6691879</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -11820,7 +11830,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11830,7 +11840,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11857,13 +11867,13 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137078025</t>
+          <t>https://artportalen.se/Sighting/137077941</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>137078049</v>
+        <v>137078025</v>
       </c>
       <c r="B106" t="n">
         <v>93505</v>
@@ -11893,7 +11903,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -11909,10 +11919,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>668827</v>
+        <v>668819</v>
       </c>
       <c r="R106" t="n">
-        <v>6691900</v>
+        <v>6691906</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -11944,7 +11954,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11954,7 +11964,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11981,13 +11991,13 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137078049</t>
+          <t>https://artportalen.se/Sighting/137078025</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>137078081</v>
+        <v>137078049</v>
       </c>
       <c r="B107" t="n">
         <v>93505</v>
@@ -12017,7 +12027,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -12033,13 +12043,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>668809</v>
+        <v>668827</v>
       </c>
       <c r="R107" t="n">
-        <v>6691907</v>
+        <v>6691900</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12068,7 +12078,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12078,12 +12088,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>14:08</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Stråk med 30+ frk</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12110,16 +12115,16 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137078081</t>
+          <t>https://artportalen.se/Sighting/137078049</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>136824829</v>
+        <v>137078081</v>
       </c>
       <c r="B108" t="n">
-        <v>93507</v>
+        <v>93505</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12127,34 +12132,45 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5966</v>
+        <v>5964</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>668559</v>
+        <v>668809</v>
       </c>
       <c r="R108" t="n">
-        <v>6691668</v>
+        <v>6691907</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12181,12 +12197,27 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Stråk med 30+ frk</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12195,30 +12226,31 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Björn Bråvander, Ingemar Södergren, Klara Tellebo, Malin Hylland</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824829</t>
+          <t>https://artportalen.se/Sighting/137078081</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>136824830</v>
+        <v>136824829</v>
       </c>
       <c r="B109" t="n">
         <v>93507</v>
@@ -12253,10 +12285,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>668441</v>
+        <v>668559</v>
       </c>
       <c r="R109" t="n">
-        <v>6691846</v>
+        <v>6691668</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12314,13 +12346,13 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824830</t>
+          <t>https://artportalen.se/Sighting/136824829</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>136974101</v>
+        <v>136824830</v>
       </c>
       <c r="B110" t="n">
         <v>93507</v>
@@ -12355,10 +12387,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>668523</v>
+        <v>668441</v>
       </c>
       <c r="R110" t="n">
-        <v>6691688</v>
+        <v>6691846</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12385,12 +12417,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12416,13 +12448,13 @@
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136974101</t>
+          <t>https://artportalen.se/Sighting/136824830</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>136974102</v>
+        <v>136974101</v>
       </c>
       <c r="B111" t="n">
         <v>93507</v>
@@ -12457,10 +12489,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>668518</v>
+        <v>668523</v>
       </c>
       <c r="R111" t="n">
-        <v>6691672</v>
+        <v>6691688</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12518,13 +12550,13 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136974102</t>
+          <t>https://artportalen.se/Sighting/136974101</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>137073771</v>
+        <v>136974102</v>
       </c>
       <c r="B112" t="n">
         <v>93507</v>
@@ -12559,10 +12591,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>668646</v>
+        <v>668518</v>
       </c>
       <c r="R112" t="n">
-        <v>6691876</v>
+        <v>6691672</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12589,12 +12621,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12614,22 +12646,22 @@
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Björn Bråvander, Malin Hylland, Klara Tellebo</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073771</t>
+          <t>https://artportalen.se/Sighting/136974102</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127382931</v>
+        <v>137073771</v>
       </c>
       <c r="B113" t="n">
-        <v>79946</v>
+        <v>93507</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12637,21 +12669,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12661,13 +12693,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>668378</v>
+        <v>668646</v>
       </c>
       <c r="R113" t="n">
-        <v>6691942</v>
+        <v>6691876</v>
       </c>
       <c r="S113" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12691,12 +12723,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12707,21 +12739,6 @@
       </c>
       <c r="AG113" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ113" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK113" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO113" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
@@ -12731,60 +12748,57 @@
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Ingemar Södergren, Björn Bråvander, Malin Hylland, Klara Tellebo</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127382931</t>
+          <t>https://artportalen.se/Sighting/137073771</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128953977</v>
+        <v>127382931</v>
       </c>
       <c r="B114" t="n">
-        <v>80336</v>
+        <v>79946</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>668697</v>
+        <v>668378</v>
       </c>
       <c r="R114" t="n">
-        <v>6691561</v>
+        <v>6691942</v>
       </c>
       <c r="S114" t="n">
         <v>15</v>
@@ -12811,12 +12825,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12825,23 +12839,22 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -12858,13 +12871,13 @@
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128953977</t>
+          <t>https://artportalen.se/Sighting/127382931</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128953978</v>
+        <v>128953977</v>
       </c>
       <c r="B115" t="n">
         <v>80336</v>
@@ -12893,16 +12906,19 @@
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>668684</v>
+        <v>668697</v>
       </c>
       <c r="R115" t="n">
-        <v>6691557</v>
+        <v>6691561</v>
       </c>
       <c r="S115" t="n">
         <v>15</v>
@@ -12943,6 +12959,7 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12975,16 +12992,16 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128953978</t>
+          <t>https://artportalen.se/Sighting/128953977</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128953973</v>
+        <v>128953978</v>
       </c>
       <c r="B116" t="n">
-        <v>57950</v>
+        <v>80336</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12992,39 +13009,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>668704</v>
+        <v>668684</v>
       </c>
       <c r="R116" t="n">
-        <v>6691768</v>
+        <v>6691557</v>
       </c>
       <c r="S116" t="n">
         <v>15</v>
@@ -13068,6 +13080,21 @@
       <c r="AG116" t="b">
         <v>0</v>
       </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
@@ -13082,13 +13109,13 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128953973</t>
+          <t>https://artportalen.se/Sighting/128953978</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128953974</v>
+        <v>128953973</v>
       </c>
       <c r="B117" t="n">
         <v>57950</v>
@@ -13128,10 +13155,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>668675</v>
+        <v>668704</v>
       </c>
       <c r="R117" t="n">
-        <v>6691565</v>
+        <v>6691768</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -13189,16 +13216,16 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128953974</t>
+          <t>https://artportalen.se/Sighting/128953973</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128260539</v>
+        <v>128953974</v>
       </c>
       <c r="B118" t="n">
-        <v>57141</v>
+        <v>57950</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13206,21 +13233,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13235,13 +13262,13 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>668536</v>
+        <v>668675</v>
       </c>
       <c r="R118" t="n">
-        <v>6691824</v>
+        <v>6691565</v>
       </c>
       <c r="S118" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13265,17 +13292,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Balgrop med fjädrar</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13301,16 +13323,16 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260539</t>
+          <t>https://artportalen.se/Sighting/128953974</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>132894827</v>
+        <v>128260539</v>
       </c>
       <c r="B119" t="n">
-        <v>57162</v>
+        <v>57141</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13338,22 +13360,22 @@
       <c r="I119" t="inlineStr"/>
       <c r="M119" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Östensbo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>668548</v>
+        <v>668536</v>
       </c>
       <c r="R119" t="n">
-        <v>6691834</v>
+        <v>6691824</v>
       </c>
       <c r="S119" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13377,17 +13399,17 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Lämpligt tjäderhabitat</t>
+          <t>Balgrop med fjädrar</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13413,16 +13435,16 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132894827</t>
+          <t>https://artportalen.se/Sighting/128260539</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>136824810</v>
+        <v>132894827</v>
       </c>
       <c r="B120" t="n">
-        <v>57221</v>
+        <v>57162</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13448,20 +13470,24 @@
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>668526</v>
+        <v>668548</v>
       </c>
       <c r="R120" t="n">
-        <v>6691693</v>
+        <v>6691834</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13485,17 +13511,17 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Fjäder av tupp.</t>
+          <t>Lämpligt tjäderhabitat</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13521,16 +13547,16 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824810</t>
+          <t>https://artportalen.se/Sighting/132894827</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128953999</v>
+        <v>136824810</v>
       </c>
       <c r="B121" t="n">
-        <v>5179</v>
+        <v>57221</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13538,37 +13564,38 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>668676</v>
+        <v>668526</v>
       </c>
       <c r="R121" t="n">
-        <v>6691605</v>
+        <v>6691693</v>
       </c>
       <c r="S121" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13592,12 +13619,17 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Fjäder av tupp.</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13606,24 +13638,8 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ121" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK121" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO121" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
@@ -13639,16 +13655,16 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128953999</t>
+          <t>https://artportalen.se/Sighting/136824810</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125807887</v>
+        <v>128953999</v>
       </c>
       <c r="B122" t="n">
-        <v>4781</v>
+        <v>5179</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13656,34 +13672,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>102306</v>
+        <v>100526</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>668279</v>
+        <v>668676</v>
       </c>
       <c r="R122" t="n">
-        <v>6691905</v>
+        <v>6691605</v>
       </c>
       <c r="S122" t="n">
         <v>15</v>
@@ -13710,12 +13726,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13724,6 +13740,7 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -13756,13 +13773,13 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125807887</t>
+          <t>https://artportalen.se/Sighting/128953999</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125807888</v>
+        <v>125807887</v>
       </c>
       <c r="B123" t="n">
         <v>4781</v>
@@ -13797,7 +13814,7 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>668255</v>
+        <v>668279</v>
       </c>
       <c r="R123" t="n">
         <v>6691905</v>
@@ -13873,13 +13890,13 @@
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125807888</t>
+          <t>https://artportalen.se/Sighting/125807887</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127382960</v>
+        <v>125807888</v>
       </c>
       <c r="B124" t="n">
         <v>4781</v>
@@ -13910,14 +13927,14 @@
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>668228</v>
+        <v>668255</v>
       </c>
       <c r="R124" t="n">
-        <v>6691916</v>
+        <v>6691905</v>
       </c>
       <c r="S124" t="n">
         <v>15</v>
@@ -13944,12 +13961,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13990,13 +14007,13 @@
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127382960</t>
+          <t>https://artportalen.se/Sighting/125807888</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128260581</v>
+        <v>127382960</v>
       </c>
       <c r="B125" t="n">
         <v>4781</v>
@@ -14031,13 +14048,13 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>668437</v>
+        <v>668228</v>
       </c>
       <c r="R125" t="n">
-        <v>6691726</v>
+        <v>6691916</v>
       </c>
       <c r="S125" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -14061,12 +14078,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14107,13 +14124,13 @@
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260581</t>
+          <t>https://artportalen.se/Sighting/127382960</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128260582</v>
+        <v>128260581</v>
       </c>
       <c r="B126" t="n">
         <v>4781</v>
@@ -14148,10 +14165,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>668444</v>
+        <v>668437</v>
       </c>
       <c r="R126" t="n">
-        <v>6691724</v>
+        <v>6691726</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -14224,13 +14241,13 @@
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260582</t>
+          <t>https://artportalen.se/Sighting/128260581</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128260583</v>
+        <v>128260582</v>
       </c>
       <c r="B127" t="n">
         <v>4781</v>
@@ -14265,10 +14282,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>668540</v>
+        <v>668444</v>
       </c>
       <c r="R127" t="n">
-        <v>6691905</v>
+        <v>6691724</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -14341,13 +14358,13 @@
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260583</t>
+          <t>https://artportalen.se/Sighting/128260582</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128344139</v>
+        <v>128260583</v>
       </c>
       <c r="B128" t="n">
         <v>4781</v>
@@ -14378,17 +14395,17 @@
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>668595</v>
+        <v>668540</v>
       </c>
       <c r="R128" t="n">
-        <v>6691931</v>
+        <v>6691905</v>
       </c>
       <c r="S128" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -14428,31 +14445,46 @@
       </c>
       <c r="AG128" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ128" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK128" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO128" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128344139</t>
+          <t>https://artportalen.se/Sighting/128260583</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>136824221</v>
+        <v>128344139</v>
       </c>
       <c r="B129" t="n">
-        <v>4789</v>
+        <v>4781</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14480,14 +14512,14 @@
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>668354</v>
+        <v>668595</v>
       </c>
       <c r="R129" t="n">
-        <v>6691795</v>
+        <v>6691931</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14514,12 +14546,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14530,89 +14562,69 @@
       </c>
       <c r="AG129" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ129" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK129" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO129" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824221</t>
+          <t>https://artportalen.se/Sighting/128344139</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128260540</v>
+        <v>136824221</v>
       </c>
       <c r="B130" t="n">
-        <v>58114</v>
+        <v>4789</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>103021</v>
+        <v>102306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>668462</v>
+        <v>668354</v>
       </c>
       <c r="R130" t="n">
-        <v>6691745</v>
+        <v>6691795</v>
       </c>
       <c r="S130" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14636,12 +14648,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14652,6 +14664,21 @@
       </c>
       <c r="AG130" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK130" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
@@ -14667,13 +14694,13 @@
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260540</t>
+          <t>https://artportalen.se/Sighting/136824221</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128260541</v>
+        <v>128260540</v>
       </c>
       <c r="B131" t="n">
         <v>58114</v>
@@ -14702,24 +14729,21 @@
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
       <c r="M131" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>668559</v>
+        <v>668462</v>
       </c>
       <c r="R131" t="n">
-        <v>6691737</v>
+        <v>6691745</v>
       </c>
       <c r="S131" t="n">
         <v>25</v>
@@ -14777,16 +14801,16 @@
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260541</t>
+          <t>https://artportalen.se/Sighting/128260540</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>136824814</v>
+        <v>128260541</v>
       </c>
       <c r="B132" t="n">
-        <v>58196</v>
+        <v>58114</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14812,20 +14836,27 @@
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="M132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>668527</v>
+        <v>668559</v>
       </c>
       <c r="R132" t="n">
-        <v>6691698</v>
+        <v>6691737</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14849,12 +14880,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14880,54 +14911,55 @@
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824814</t>
+          <t>https://artportalen.se/Sighting/128260541</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125853673</v>
+        <v>136824814</v>
       </c>
       <c r="B133" t="n">
-        <v>99035</v>
+        <v>58196</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="M133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>668269</v>
+        <v>668527</v>
       </c>
       <c r="R133" t="n">
-        <v>6691918</v>
+        <v>6691698</v>
       </c>
       <c r="S133" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14951,12 +14983,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14971,24 +15003,24 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Eva-Lena1 Rådberg</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Eva-Lena1 Rådberg</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125853673</t>
+          <t>https://artportalen.se/Sighting/136824814</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125855915</v>
+        <v>125853673</v>
       </c>
       <c r="B134" t="n">
         <v>99035</v>
@@ -15019,17 +15051,17 @@
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>668328</v>
+        <v>668269</v>
       </c>
       <c r="R134" t="n">
-        <v>6691847</v>
+        <v>6691918</v>
       </c>
       <c r="S134" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -15073,24 +15105,24 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Eva-Lena1 Rådberg</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Eva-Lena1 Rådberg</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125855915</t>
+          <t>https://artportalen.se/Sighting/125853673</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128344142</v>
+        <v>125855915</v>
       </c>
       <c r="B135" t="n">
         <v>99035</v>
@@ -15121,17 +15153,17 @@
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>668540</v>
+        <v>668328</v>
       </c>
       <c r="R135" t="n">
-        <v>6691947</v>
+        <v>6691847</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15155,12 +15187,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15175,27 +15207,27 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128344142</t>
+          <t>https://artportalen.se/Sighting/125855915</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>136824822</v>
+        <v>128344142</v>
       </c>
       <c r="B136" t="n">
-        <v>99396</v>
+        <v>99035</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15203,34 +15235,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>219798</v>
+        <v>219790</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>668779</v>
+        <v>668540</v>
       </c>
       <c r="R136" t="n">
-        <v>6691909</v>
+        <v>6691947</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15257,12 +15289,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15277,24 +15309,24 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824822</t>
+          <t>https://artportalen.se/Sighting/128344142</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>137073756</v>
+        <v>136824822</v>
       </c>
       <c r="B137" t="n">
         <v>99396</v>
@@ -15329,10 +15361,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>668771</v>
+        <v>668779</v>
       </c>
       <c r="R137" t="n">
-        <v>6691857</v>
+        <v>6691909</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15359,12 +15391,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15384,19 +15416,19 @@
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Björn Bråvander, Malin Hylland, Klara Tellebo</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073756</t>
+          <t>https://artportalen.se/Sighting/136824822</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>137073757</v>
+        <v>137073756</v>
       </c>
       <c r="B138" t="n">
         <v>99396</v>
@@ -15431,10 +15463,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>668787</v>
+        <v>668771</v>
       </c>
       <c r="R138" t="n">
-        <v>6691924</v>
+        <v>6691857</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15492,13 +15524,13 @@
       <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073757</t>
+          <t>https://artportalen.se/Sighting/137073756</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>137077977</v>
+        <v>137073757</v>
       </c>
       <c r="B139" t="n">
         <v>99396</v>
@@ -15526,32 +15558,20 @@
           <t>(L.) Crantz</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>668802</v>
+        <v>668787</v>
       </c>
       <c r="R139" t="n">
-        <v>6691843</v>
+        <v>6691924</v>
       </c>
       <c r="S139" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -15578,55 +15598,44 @@
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="Z139" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="AB139" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Björn Bråvander, Ingemar Södergren, Klara Tellebo, Malin Hylland</t>
+          <t>Ingemar Södergren, Björn Bråvander, Malin Hylland, Klara Tellebo</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137077977</t>
+          <t>https://artportalen.se/Sighting/137073757</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>136824842</v>
+        <v>137077977</v>
       </c>
       <c r="B140" t="n">
-        <v>108457</v>
+        <v>99396</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15634,37 +15643,49 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>220083</v>
+        <v>219798</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>668688</v>
+        <v>668802</v>
       </c>
       <c r="R140" t="n">
-        <v>6691747</v>
+        <v>6691843</v>
       </c>
       <c r="S140" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -15688,12 +15709,22 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15702,33 +15733,34 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Björn Bråvander, Ingemar Södergren, Klara Tellebo, Malin Hylland</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824842</t>
+          <t>https://artportalen.se/Sighting/137077977</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>136824843</v>
+        <v>136824842</v>
       </c>
       <c r="B141" t="n">
-        <v>108457</v>
+        <v>108458</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15760,10 +15792,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>668780</v>
+        <v>668688</v>
       </c>
       <c r="R141" t="n">
-        <v>6691947</v>
+        <v>6691747</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15821,16 +15853,16 @@
       <c r="AY141" t="inlineStr"/>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824843</t>
+          <t>https://artportalen.se/Sighting/136824842</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>137077952</v>
+        <v>136824843</v>
       </c>
       <c r="B142" t="n">
-        <v>108457</v>
+        <v>108458</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15856,23 +15888,19 @@
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>668771</v>
+        <v>668780</v>
       </c>
       <c r="R142" t="n">
-        <v>6691879</v>
+        <v>6691947</v>
       </c>
       <c r="S142" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15896,22 +15924,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="Z142" t="inlineStr">
-        <is>
-          <t>13:38</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AB142" t="inlineStr">
-        <is>
-          <t>13:38</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15920,72 +15938,75 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
-      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Björn Bråvander, Ingemar Södergren, Klara Tellebo, Malin Hylland</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137077952</t>
+          <t>https://artportalen.se/Sighting/136824843</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>137073795</v>
+        <v>137077952</v>
       </c>
       <c r="B143" t="n">
-        <v>107141</v>
+        <v>108458</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>220785</v>
+        <v>220083</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>668707</v>
+        <v>668771</v>
       </c>
       <c r="R143" t="n">
-        <v>6691687</v>
+        <v>6691879</v>
       </c>
       <c r="S143" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -16012,91 +16033,93 @@
           <t>2026-10-04</t>
         </is>
       </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2026-10-04</t>
         </is>
       </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
       <c r="AD143" t="b">
         <v>0</v>
       </c>
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Björn Bråvander, Malin Hylland, Klara Tellebo</t>
+          <t>Björn Bråvander, Ingemar Södergren, Klara Tellebo, Malin Hylland</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073795</t>
+          <t>https://artportalen.se/Sighting/137077952</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128260575</v>
+        <v>137073795</v>
       </c>
       <c r="B144" t="n">
-        <v>99118</v>
+        <v>107142</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>220787</v>
+        <v>220785</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>668568</v>
+        <v>668707</v>
       </c>
       <c r="R144" t="n">
-        <v>6691681</v>
+        <v>6691687</v>
       </c>
       <c r="S144" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -16120,12 +16143,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16145,19 +16168,19 @@
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Ingemar Södergren, Björn Bråvander, Malin Hylland, Klara Tellebo</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260575</t>
+          <t>https://artportalen.se/Sighting/137073795</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128344136</v>
+        <v>128260575</v>
       </c>
       <c r="B145" t="n">
         <v>99118</v>
@@ -16185,20 +16208,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr"/>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>668558</v>
+        <v>668568</v>
       </c>
       <c r="R145" t="n">
-        <v>6691675</v>
+        <v>6691681</v>
       </c>
       <c r="S145" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -16228,11 +16260,6 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16247,27 +16274,27 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128344136</t>
+          <t>https://artportalen.se/Sighting/128260575</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>136974104</v>
+        <v>128344136</v>
       </c>
       <c r="B146" t="n">
-        <v>99418</v>
+        <v>99118</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16295,14 +16322,14 @@
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>668583</v>
+        <v>668558</v>
       </c>
       <c r="R146" t="n">
-        <v>6691676</v>
+        <v>6691675</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16329,12 +16356,17 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>21</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16349,65 +16381,65 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136974104</t>
+          <t>https://artportalen.se/Sighting/128344136</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>125855908</v>
+        <v>136974104</v>
       </c>
       <c r="B147" t="n">
-        <v>106244</v>
+        <v>99418</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>668294</v>
+        <v>668583</v>
       </c>
       <c r="R147" t="n">
-        <v>6691884</v>
+        <v>6691676</v>
       </c>
       <c r="S147" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -16431,12 +16463,12 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16451,24 +16483,24 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125855908</t>
+          <t>https://artportalen.se/Sighting/136974104</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128260577</v>
+        <v>125855908</v>
       </c>
       <c r="B148" t="n">
         <v>106244</v>
@@ -16499,17 +16531,17 @@
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>668565</v>
+        <v>668294</v>
       </c>
       <c r="R148" t="n">
-        <v>6691734</v>
+        <v>6691884</v>
       </c>
       <c r="S148" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -16533,12 +16565,12 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16553,24 +16585,24 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260577</t>
+          <t>https://artportalen.se/Sighting/125855908</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128344138</v>
+        <v>128260577</v>
       </c>
       <c r="B149" t="n">
         <v>106244</v>
@@ -16601,17 +16633,17 @@
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>668564</v>
+        <v>668565</v>
       </c>
       <c r="R149" t="n">
-        <v>6691753</v>
+        <v>6691734</v>
       </c>
       <c r="S149" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -16655,27 +16687,27 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128344138</t>
+          <t>https://artportalen.se/Sighting/128260577</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>132894835</v>
+        <v>128344138</v>
       </c>
       <c r="B150" t="n">
-        <v>106324</v>
+        <v>106244</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16703,17 +16735,17 @@
       <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Östensbo, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>668570</v>
+        <v>668564</v>
       </c>
       <c r="R150" t="n">
-        <v>6691835</v>
+        <v>6691753</v>
       </c>
       <c r="S150" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -16737,17 +16769,12 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16762,27 +16789,27 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132894835</t>
+          <t>https://artportalen.se/Sighting/128344138</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>136824837</v>
+        <v>132894835</v>
       </c>
       <c r="B151" t="n">
-        <v>106571</v>
+        <v>106324</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16810,17 +16837,17 @@
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo, Upl</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>668380</v>
+        <v>668570</v>
       </c>
       <c r="R151" t="n">
-        <v>6691865</v>
+        <v>6691835</v>
       </c>
       <c r="S151" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -16844,12 +16871,17 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16875,38 +16907,38 @@
       <c r="AY151" t="inlineStr"/>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824837</t>
+          <t>https://artportalen.se/Sighting/132894835</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>136824800</v>
+        <v>136824837</v>
       </c>
       <c r="B152" t="n">
-        <v>102550</v>
+        <v>106572</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>221235</v>
+        <v>221144</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16916,10 +16948,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>668779</v>
+        <v>668380</v>
       </c>
       <c r="R152" t="n">
-        <v>6691909</v>
+        <v>6691865</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16977,13 +17009,13 @@
       <c r="AY152" t="inlineStr"/>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824800</t>
+          <t>https://artportalen.se/Sighting/136824837</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>136824801</v>
+        <v>136824800</v>
       </c>
       <c r="B153" t="n">
         <v>102550</v>
@@ -17018,10 +17050,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>668791</v>
+        <v>668779</v>
       </c>
       <c r="R153" t="n">
-        <v>6691921</v>
+        <v>6691909</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17079,13 +17111,13 @@
       <c r="AY153" t="inlineStr"/>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824801</t>
+          <t>https://artportalen.se/Sighting/136824800</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>137073740</v>
+        <v>136824801</v>
       </c>
       <c r="B154" t="n">
         <v>102550</v>
@@ -17120,10 +17152,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>668809</v>
+        <v>668791</v>
       </c>
       <c r="R154" t="n">
-        <v>6691919</v>
+        <v>6691921</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17150,12 +17182,12 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17175,19 +17207,19 @@
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Björn Bråvander, Malin Hylland, Klara Tellebo</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073740</t>
+          <t>https://artportalen.se/Sighting/136824801</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>137073741</v>
+        <v>137073740</v>
       </c>
       <c r="B155" t="n">
         <v>102550</v>
@@ -17222,10 +17254,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>668733</v>
+        <v>668809</v>
       </c>
       <c r="R155" t="n">
-        <v>6691809</v>
+        <v>6691919</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17283,13 +17315,13 @@
       <c r="AY155" t="inlineStr"/>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073741</t>
+          <t>https://artportalen.se/Sighting/137073740</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>137073742</v>
+        <v>137073741</v>
       </c>
       <c r="B156" t="n">
         <v>102550</v>
@@ -17324,10 +17356,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>668574</v>
+        <v>668733</v>
       </c>
       <c r="R156" t="n">
-        <v>6691641</v>
+        <v>6691809</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17385,13 +17417,13 @@
       <c r="AY156" t="inlineStr"/>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073742</t>
+          <t>https://artportalen.se/Sighting/137073741</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>137078125</v>
+        <v>137073742</v>
       </c>
       <c r="B157" t="n">
         <v>102550</v>
@@ -17420,20 +17452,16 @@
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr"/>
-      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>668797</v>
+        <v>668574</v>
       </c>
       <c r="R157" t="n">
-        <v>6691921</v>
+        <v>6691641</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17463,90 +17491,83 @@
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AD157" t="b">
         <v>0</v>
       </c>
       <c r="AE157" t="b">
         <v>0</v>
       </c>
-      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Björn Bråvander, Ingemar Södergren, Klara Tellebo, Malin Hylland</t>
+          <t>Ingemar Södergren, Björn Bråvander, Malin Hylland, Klara Tellebo</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137078125</t>
+          <t>https://artportalen.se/Sighting/137073742</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>137073768</v>
+        <v>137078125</v>
       </c>
       <c r="B158" t="n">
-        <v>106926</v>
+        <v>102550</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>221570</v>
+        <v>221235</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Mörk lungört</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Pulmonaria obscura</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Dumort.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>668762</v>
+        <v>668797</v>
       </c>
       <c r="R158" t="n">
-        <v>6691861</v>
+        <v>6691921</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17576,44 +17597,55 @@
           <t>2026-10-04</t>
         </is>
       </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>2026-10-04</t>
         </is>
       </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AD158" t="b">
         <v>0</v>
       </c>
       <c r="AE158" t="b">
         <v>0</v>
       </c>
+      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Björn Bråvander, Malin Hylland, Klara Tellebo</t>
+          <t>Björn Bråvander, Ingemar Södergren, Klara Tellebo, Malin Hylland</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073768</t>
+          <t>https://artportalen.se/Sighting/137078125</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>137073769</v>
+        <v>137073768</v>
       </c>
       <c r="B159" t="n">
-        <v>106926</v>
+        <v>106927</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17645,10 +17677,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>668798</v>
+        <v>668762</v>
       </c>
       <c r="R159" t="n">
-        <v>6691889</v>
+        <v>6691861</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17706,16 +17738,16 @@
       <c r="AY159" t="inlineStr"/>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137073769</t>
+          <t>https://artportalen.se/Sighting/137073768</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128344123</v>
+        <v>137073769</v>
       </c>
       <c r="B160" t="n">
-        <v>104628</v>
+        <v>106927</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17723,34 +17755,34 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>222412</v>
+        <v>221570</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Mörk lungört</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Pulmonaria obscura</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Dumort.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo_1, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>668604</v>
+        <v>668798</v>
       </c>
       <c r="R160" t="n">
-        <v>6691663</v>
+        <v>6691889</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17777,12 +17809,12 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17797,27 +17829,27 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Tove Widén</t>
+          <t>Ingemar Södergren, Björn Bråvander, Malin Hylland, Klara Tellebo</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128344123</t>
+          <t>https://artportalen.se/Sighting/137073769</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>136824811</v>
+        <v>128344123</v>
       </c>
       <c r="B161" t="n">
-        <v>104951</v>
+        <v>104628</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17845,14 +17877,14 @@
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Ladängsskogen, Upl</t>
+          <t>Östensbo-Bennebo_1, Upl</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>668677</v>
+        <v>668604</v>
       </c>
       <c r="R161" t="n">
-        <v>6691727</v>
+        <v>6691663</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17879,12 +17911,12 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17899,27 +17931,27 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Tove Widén</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824811</t>
+          <t>https://artportalen.se/Sighting/128344123</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>136824812</v>
+        <v>136824811</v>
       </c>
       <c r="B162" t="n">
-        <v>104951</v>
+        <v>104952</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17951,10 +17983,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>668727</v>
+        <v>668677</v>
       </c>
       <c r="R162" t="n">
-        <v>6691836</v>
+        <v>6691727</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18012,16 +18044,16 @@
       <c r="AY162" t="inlineStr"/>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824812</t>
+          <t>https://artportalen.se/Sighting/136824811</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128260592</v>
+        <v>136824812</v>
       </c>
       <c r="B163" t="n">
-        <v>101326</v>
+        <v>104952</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18029,21 +18061,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -18053,13 +18085,13 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>668587</v>
+        <v>668727</v>
       </c>
       <c r="R163" t="n">
-        <v>6691690</v>
+        <v>6691836</v>
       </c>
       <c r="S163" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -18083,12 +18115,12 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18114,13 +18146,13 @@
       <c r="AY163" t="inlineStr"/>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260592</t>
+          <t>https://artportalen.se/Sighting/136824812</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128260593</v>
+        <v>128260592</v>
       </c>
       <c r="B164" t="n">
         <v>101326</v>
@@ -18155,10 +18187,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>668593</v>
+        <v>668587</v>
       </c>
       <c r="R164" t="n">
-        <v>6691674</v>
+        <v>6691690</v>
       </c>
       <c r="S164" t="n">
         <v>25</v>
@@ -18216,16 +18248,16 @@
       <c r="AY164" t="inlineStr"/>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260593</t>
+          <t>https://artportalen.se/Sighting/128260592</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128953994</v>
+        <v>128260593</v>
       </c>
       <c r="B165" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18257,13 +18289,13 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>668674</v>
+        <v>668593</v>
       </c>
       <c r="R165" t="n">
-        <v>6691735</v>
+        <v>6691674</v>
       </c>
       <c r="S165" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -18287,12 +18319,12 @@
       </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18318,13 +18350,13 @@
       <c r="AY165" t="inlineStr"/>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128953994</t>
+          <t>https://artportalen.se/Sighting/128260593</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128953995</v>
+        <v>128953994</v>
       </c>
       <c r="B166" t="n">
         <v>101325</v>
@@ -18359,10 +18391,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>668644</v>
+        <v>668674</v>
       </c>
       <c r="R166" t="n">
-        <v>6691674</v>
+        <v>6691735</v>
       </c>
       <c r="S166" t="n">
         <v>15</v>
@@ -18420,13 +18452,13 @@
       <c r="AY166" t="inlineStr"/>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128953995</t>
+          <t>https://artportalen.se/Sighting/128953994</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128953996</v>
+        <v>128953995</v>
       </c>
       <c r="B167" t="n">
         <v>101325</v>
@@ -18461,10 +18493,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>668650</v>
+        <v>668644</v>
       </c>
       <c r="R167" t="n">
-        <v>6691592</v>
+        <v>6691674</v>
       </c>
       <c r="S167" t="n">
         <v>15</v>
@@ -18522,13 +18554,13 @@
       <c r="AY167" t="inlineStr"/>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128953996</t>
+          <t>https://artportalen.se/Sighting/128953995</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128953997</v>
+        <v>128953996</v>
       </c>
       <c r="B168" t="n">
         <v>101325</v>
@@ -18563,10 +18595,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>668641</v>
+        <v>668650</v>
       </c>
       <c r="R168" t="n">
-        <v>6691647</v>
+        <v>6691592</v>
       </c>
       <c r="S168" t="n">
         <v>15</v>
@@ -18624,13 +18656,13 @@
       <c r="AY168" t="inlineStr"/>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128953997</t>
+          <t>https://artportalen.se/Sighting/128953996</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128953998</v>
+        <v>128953997</v>
       </c>
       <c r="B169" t="n">
         <v>101325</v>
@@ -18665,10 +18697,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>668653</v>
+        <v>668641</v>
       </c>
       <c r="R169" t="n">
-        <v>6691655</v>
+        <v>6691647</v>
       </c>
       <c r="S169" t="n">
         <v>15</v>
@@ -18726,16 +18758,16 @@
       <c r="AY169" t="inlineStr"/>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128953998</t>
+          <t>https://artportalen.se/Sighting/128953997</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>136824845</v>
+        <v>128953998</v>
       </c>
       <c r="B170" t="n">
-        <v>101634</v>
+        <v>101325</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18767,13 +18799,13 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>668498</v>
+        <v>668653</v>
       </c>
       <c r="R170" t="n">
-        <v>6691758</v>
+        <v>6691655</v>
       </c>
       <c r="S170" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -18797,12 +18829,12 @@
       </c>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18828,13 +18860,13 @@
       <c r="AY170" t="inlineStr"/>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824845</t>
+          <t>https://artportalen.se/Sighting/128953998</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>136824847</v>
+        <v>136824845</v>
       </c>
       <c r="B171" t="n">
         <v>101634</v>
@@ -18869,10 +18901,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>668588</v>
+        <v>668498</v>
       </c>
       <c r="R171" t="n">
-        <v>6691652</v>
+        <v>6691758</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18930,13 +18962,13 @@
       <c r="AY171" t="inlineStr"/>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824847</t>
+          <t>https://artportalen.se/Sighting/136824845</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>136824848</v>
+        <v>136824847</v>
       </c>
       <c r="B172" t="n">
         <v>101634</v>
@@ -18971,10 +19003,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>668632</v>
+        <v>668588</v>
       </c>
       <c r="R172" t="n">
-        <v>6691628</v>
+        <v>6691652</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19032,13 +19064,13 @@
       <c r="AY172" t="inlineStr"/>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824848</t>
+          <t>https://artportalen.se/Sighting/136824847</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>136824849</v>
+        <v>136824848</v>
       </c>
       <c r="B173" t="n">
         <v>101634</v>
@@ -19073,10 +19105,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>668654</v>
+        <v>668632</v>
       </c>
       <c r="R173" t="n">
-        <v>6691662</v>
+        <v>6691628</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19134,13 +19166,13 @@
       <c r="AY173" t="inlineStr"/>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824849</t>
+          <t>https://artportalen.se/Sighting/136824848</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>136824850</v>
+        <v>136824849</v>
       </c>
       <c r="B174" t="n">
         <v>101634</v>
@@ -19175,10 +19207,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>668651</v>
+        <v>668654</v>
       </c>
       <c r="R174" t="n">
-        <v>6691668</v>
+        <v>6691662</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19236,13 +19268,13 @@
       <c r="AY174" t="inlineStr"/>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824850</t>
+          <t>https://artportalen.se/Sighting/136824849</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>136824851</v>
+        <v>136824850</v>
       </c>
       <c r="B175" t="n">
         <v>101634</v>
@@ -19277,10 +19309,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>668681</v>
+        <v>668651</v>
       </c>
       <c r="R175" t="n">
-        <v>6691734</v>
+        <v>6691668</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19338,13 +19370,13 @@
       <c r="AY175" t="inlineStr"/>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824851</t>
+          <t>https://artportalen.se/Sighting/136824850</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>136824852</v>
+        <v>136824851</v>
       </c>
       <c r="B176" t="n">
         <v>101634</v>
@@ -19379,10 +19411,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>668688</v>
+        <v>668681</v>
       </c>
       <c r="R176" t="n">
-        <v>6691747</v>
+        <v>6691734</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19440,13 +19472,13 @@
       <c r="AY176" t="inlineStr"/>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824852</t>
+          <t>https://artportalen.se/Sighting/136824851</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>136824853</v>
+        <v>136824852</v>
       </c>
       <c r="B177" t="n">
         <v>101634</v>
@@ -19481,10 +19513,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>668715</v>
+        <v>668688</v>
       </c>
       <c r="R177" t="n">
-        <v>6691784</v>
+        <v>6691747</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19542,13 +19574,13 @@
       <c r="AY177" t="inlineStr"/>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824853</t>
+          <t>https://artportalen.se/Sighting/136824852</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>136824854</v>
+        <v>136824853</v>
       </c>
       <c r="B178" t="n">
         <v>101634</v>
@@ -19583,10 +19615,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>668727</v>
+        <v>668715</v>
       </c>
       <c r="R178" t="n">
-        <v>6691836</v>
+        <v>6691784</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19644,13 +19676,13 @@
       <c r="AY178" t="inlineStr"/>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824854</t>
+          <t>https://artportalen.se/Sighting/136824853</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>137077942</v>
+        <v>136824854</v>
       </c>
       <c r="B179" t="n">
         <v>101634</v>
@@ -19679,23 +19711,19 @@
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
-      <c r="J179" t="inlineStr"/>
-      <c r="K179" t="inlineStr"/>
-      <c r="L179" t="inlineStr"/>
-      <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>668771</v>
+        <v>668727</v>
       </c>
       <c r="R179" t="n">
-        <v>6691879</v>
+        <v>6691836</v>
       </c>
       <c r="S179" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -19719,22 +19747,12 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="Z179" t="inlineStr">
-        <is>
-          <t>13:38</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AB179" t="inlineStr">
-        <is>
-          <t>13:38</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19743,31 +19761,30 @@
       <c r="AE179" t="b">
         <v>0</v>
       </c>
-      <c r="AF179" t="inlineStr"/>
       <c r="AG179" t="b">
         <v>0</v>
       </c>
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Björn Bråvander, Ingemar Södergren, Klara Tellebo, Malin Hylland</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137077942</t>
+          <t>https://artportalen.se/Sighting/136824854</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>137078051</v>
+        <v>137077942</v>
       </c>
       <c r="B180" t="n">
         <v>101634</v>
@@ -19806,10 +19823,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>668827</v>
+        <v>668771</v>
       </c>
       <c r="R180" t="n">
-        <v>6691900</v>
+        <v>6691879</v>
       </c>
       <c r="S180" t="n">
         <v>5</v>
@@ -19839,9 +19856,19 @@
           <t>2026-10-04</t>
         </is>
       </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
       <c r="AA180" t="inlineStr">
         <is>
           <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB180" t="inlineStr">
+        <is>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19868,16 +19895,16 @@
       <c r="AY180" t="inlineStr"/>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137078051</t>
+          <t>https://artportalen.se/Sighting/137077942</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>136824825</v>
+        <v>137078051</v>
       </c>
       <c r="B181" t="n">
-        <v>99224</v>
+        <v>101634</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19885,37 +19912,41 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>223049</v>
+        <v>222498</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr"/>
+      <c r="N181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>668715</v>
+        <v>668827</v>
       </c>
       <c r="R181" t="n">
-        <v>6691784</v>
+        <v>6691900</v>
       </c>
       <c r="S181" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -19939,12 +19970,12 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -19953,33 +19984,34 @@
       <c r="AE181" t="b">
         <v>0</v>
       </c>
+      <c r="AF181" t="inlineStr"/>
       <c r="AG181" t="b">
         <v>0</v>
       </c>
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Björn Bråvander</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Björn Bråvander, Ingemar Södergren, Klara Tellebo, Malin Hylland</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136824825</t>
+          <t>https://artportalen.se/Sighting/137078051</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>128953986</v>
+        <v>136824825</v>
       </c>
       <c r="B182" t="n">
-        <v>80392</v>
+        <v>99224</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19987,21 +20019,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>229497</v>
+        <v>223049</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -20011,13 +20043,13 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>668686</v>
+        <v>668715</v>
       </c>
       <c r="R182" t="n">
-        <v>6691559</v>
+        <v>6691784</v>
       </c>
       <c r="S182" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -20041,12 +20073,12 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -20057,21 +20089,6 @@
       </c>
       <c r="AG182" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ182" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK182" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO182" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
@@ -20087,38 +20104,38 @@
       <c r="AY182" t="inlineStr"/>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128953986</t>
+          <t>https://artportalen.se/Sighting/136824825</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>136974125</v>
+        <v>128953986</v>
       </c>
       <c r="B183" t="n">
-        <v>87555</v>
+        <v>80392</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>249228</v>
+        <v>229497</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Frøslev &amp; al.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -20128,13 +20145,13 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>668444</v>
+        <v>668686</v>
       </c>
       <c r="R183" t="n">
-        <v>6691727</v>
+        <v>6691559</v>
       </c>
       <c r="S183" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -20158,17 +20175,12 @@
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AC183" t="inlineStr">
-        <is>
-          <t>KOH brun på hatten. Ingen tydlig reaktion i övrigt. Vit mycelsträng. Ingen tydlig doft.</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -20179,6 +20191,21 @@
       </c>
       <c r="AG183" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ183" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK183" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO183" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
@@ -20194,16 +20221,16 @@
       <c r="AY183" t="inlineStr"/>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136974125</t>
+          <t>https://artportalen.se/Sighting/128953986</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>137076843</v>
+        <v>136974125</v>
       </c>
       <c r="B184" t="n">
-        <v>91643</v>
+        <v>87555</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20211,48 +20238,37 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>256703</v>
+        <v>249228</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J184" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K184" t="inlineStr"/>
-      <c r="N184" t="inlineStr"/>
+          <t>Frøslev &amp; al.</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>668593</v>
+        <v>668444</v>
       </c>
       <c r="R184" t="n">
-        <v>6691679</v>
+        <v>6691727</v>
       </c>
       <c r="S184" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -20276,22 +20292,17 @@
       </c>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="Z184" t="inlineStr">
-        <is>
-          <t>16:27</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AB184" t="inlineStr">
-        <is>
-          <t>16:27</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>KOH brun på hatten. Ingen tydlig reaktion i övrigt. Vit mycelsträng. Ingen tydlig doft.</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -20300,48 +20311,33 @@
       <c r="AE184" t="b">
         <v>0</v>
       </c>
-      <c r="AF184" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
       <c r="AG184" t="b">
         <v>0</v>
-      </c>
-      <c r="AI184" t="inlineStr">
-        <is>
-          <t>Luckig kalkbarrskog; under tall och gran</t>
-        </is>
-      </c>
-      <c r="AR184" t="inlineStr">
-        <is>
-          <t>Kollekt sparad</t>
-        </is>
       </c>
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Björn Bråvander</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Björn Bråvander, Ingemar Södergren, Klara Tellebo, Malin Hylland</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137076843</t>
+          <t>https://artportalen.se/Sighting/136974125</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>137078162</v>
+        <v>137076843</v>
       </c>
       <c r="B185" t="n">
-        <v>87578</v>
+        <v>91643</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20349,26 +20345,26 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6003295</v>
+        <v>256703</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -20384,10 +20380,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>668792</v>
+        <v>668593</v>
       </c>
       <c r="R185" t="n">
-        <v>6691927</v>
+        <v>6691679</v>
       </c>
       <c r="S185" t="n">
         <v>5</v>
@@ -20419,7 +20415,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -20429,7 +20425,7 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -20438,9 +20434,23 @@
       <c r="AE185" t="b">
         <v>0</v>
       </c>
-      <c r="AF185" t="inlineStr"/>
+      <c r="AF185" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG185" t="b">
         <v>0</v>
+      </c>
+      <c r="AI185" t="inlineStr">
+        <is>
+          <t>Luckig kalkbarrskog; under tall och gran</t>
+        </is>
+      </c>
+      <c r="AR185" t="inlineStr">
+        <is>
+          <t>Kollekt sparad</t>
+        </is>
       </c>
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
@@ -20455,6 +20465,130 @@
       </c>
       <c r="AY185" t="inlineStr"/>
       <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137076843</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>137078162</v>
+      </c>
+      <c r="B186" t="n">
+        <v>87578</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr"/>
+      <c r="N186" t="inlineStr"/>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q186" t="n">
+        <v>668792</v>
+      </c>
+      <c r="R186" t="n">
+        <v>6691927</v>
+      </c>
+      <c r="S186" t="n">
+        <v>5</v>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB186" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AD186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF186" t="inlineStr"/>
+      <c r="AG186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT186" t="inlineStr"/>
+      <c r="AW186" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX186" t="inlineStr">
+        <is>
+          <t>Björn Bråvander, Ingemar Södergren, Klara Tellebo, Malin Hylland</t>
+        </is>
+      </c>
+      <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137078162</t>
         </is>
@@ -20646,6 +20780,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 19253-2026 artfynd.xlsx
+++ b/artfynd/A 19253-2026 artfynd.xlsx
@@ -1850,7 +1850,7 @@
         <v>137073743</v>
       </c>
       <c r="B13" t="n">
-        <v>97655</v>
+        <v>97667</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>137073744</v>
       </c>
       <c r="B14" t="n">
-        <v>97655</v>
+        <v>97667</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>136974111</v>
       </c>
       <c r="B16" t="n">
-        <v>85750</v>
+        <v>85761</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>137077964</v>
       </c>
       <c r="B17" t="n">
-        <v>87428</v>
+        <v>87439</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>137100339</v>
       </c>
       <c r="B18" t="n">
-        <v>87635</v>
+        <v>87646</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>137073745</v>
       </c>
       <c r="B23" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>137073746</v>
       </c>
       <c r="B24" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>137078005</v>
       </c>
       <c r="B25" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>137073793</v>
       </c>
       <c r="B27" t="n">
-        <v>92843</v>
+        <v>92855</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>137078053</v>
       </c>
       <c r="B32" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>137073749</v>
       </c>
       <c r="B35" t="n">
-        <v>96753</v>
+        <v>96765</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>137073750</v>
       </c>
       <c r="B36" t="n">
-        <v>96753</v>
+        <v>96765</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>137073751</v>
       </c>
       <c r="B37" t="n">
-        <v>96753</v>
+        <v>96765</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>136974096</v>
       </c>
       <c r="B43" t="n">
-        <v>91945</v>
+        <v>91957</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>137411764</v>
       </c>
       <c r="B44" t="n">
-        <v>87644</v>
+        <v>87655</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>136974097</v>
       </c>
       <c r="B45" t="n">
-        <v>87607</v>
+        <v>87618</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         <v>137077497</v>
       </c>
       <c r="B46" t="n">
-        <v>87607</v>
+        <v>87618</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>136974098</v>
       </c>
       <c r="B48" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         <v>137073761</v>
       </c>
       <c r="B49" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>137073762</v>
       </c>
       <c r="B50" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         <v>137073763</v>
       </c>
       <c r="B51" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>137073764</v>
       </c>
       <c r="B52" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         <v>137073765</v>
       </c>
       <c r="B53" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6351,7 +6351,7 @@
         <v>137073766</v>
       </c>
       <c r="B54" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>137073767</v>
       </c>
       <c r="B55" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         <v>137077917</v>
       </c>
       <c r="B56" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6679,7 +6679,7 @@
         <v>137078067</v>
       </c>
       <c r="B57" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6803,7 +6803,7 @@
         <v>137078239</v>
       </c>
       <c r="B58" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>137073794</v>
       </c>
       <c r="B59" t="n">
-        <v>92565</v>
+        <v>92577</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7681,7 +7681,7 @@
         <v>137073758</v>
       </c>
       <c r="B66" t="n">
-        <v>93481</v>
+        <v>93493</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>137073759</v>
       </c>
       <c r="B67" t="n">
-        <v>93481</v>
+        <v>93493</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         <v>137077540</v>
       </c>
       <c r="B69" t="n">
-        <v>89332</v>
+        <v>89343</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         <v>137073747</v>
       </c>
       <c r="B73" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8519,7 +8519,7 @@
         <v>137073748</v>
       </c>
       <c r="B74" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         <v>137078402</v>
       </c>
       <c r="B75" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         <v>137073773</v>
       </c>
       <c r="B83" t="n">
-        <v>91676</v>
+        <v>91688</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         <v>136974114</v>
       </c>
       <c r="B87" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         <v>136974115</v>
       </c>
       <c r="B88" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10103,7 +10103,7 @@
         <v>136974117</v>
       </c>
       <c r="B89" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10205,7 +10205,7 @@
         <v>136974118</v>
       </c>
       <c r="B90" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>137073777</v>
       </c>
       <c r="B91" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10409,7 +10409,7 @@
         <v>137073778</v>
       </c>
       <c r="B92" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
         <v>137073779</v>
       </c>
       <c r="B93" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>137073780</v>
       </c>
       <c r="B94" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>137073781</v>
       </c>
       <c r="B95" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10817,7 +10817,7 @@
         <v>137073782</v>
       </c>
       <c r="B96" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10919,7 +10919,7 @@
         <v>137073783</v>
       </c>
       <c r="B97" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11021,7 +11021,7 @@
         <v>137073784</v>
       </c>
       <c r="B98" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11123,7 +11123,7 @@
         <v>137073785</v>
       </c>
       <c r="B99" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11225,7 +11225,7 @@
         <v>137073786</v>
       </c>
       <c r="B100" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11327,7 +11327,7 @@
         <v>137073787</v>
       </c>
       <c r="B101" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         <v>137073788</v>
       </c>
       <c r="B102" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>137073789</v>
       </c>
       <c r="B103" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11633,7 +11633,7 @@
         <v>137077585</v>
       </c>
       <c r="B104" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11752,7 +11752,7 @@
         <v>137077941</v>
       </c>
       <c r="B105" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         <v>137078025</v>
       </c>
       <c r="B106" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>137078049</v>
       </c>
       <c r="B107" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12124,7 +12124,7 @@
         <v>137078081</v>
       </c>
       <c r="B108" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         <v>136974101</v>
       </c>
       <c r="B111" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12559,7 +12559,7 @@
         <v>136974102</v>
       </c>
       <c r="B112" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12661,7 +12661,7 @@
         <v>137073771</v>
       </c>
       <c r="B113" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>137073756</v>
       </c>
       <c r="B138" t="n">
-        <v>99396</v>
+        <v>99408</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15533,7 +15533,7 @@
         <v>137073757</v>
       </c>
       <c r="B139" t="n">
-        <v>99396</v>
+        <v>99408</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>137077977</v>
       </c>
       <c r="B140" t="n">
-        <v>99396</v>
+        <v>99408</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15964,7 +15964,7 @@
         <v>137077952</v>
       </c>
       <c r="B143" t="n">
-        <v>108458</v>
+        <v>108470</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16081,7 +16081,7 @@
         <v>137073795</v>
       </c>
       <c r="B144" t="n">
-        <v>107142</v>
+        <v>107154</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         <v>136974104</v>
       </c>
       <c r="B147" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17222,7 +17222,7 @@
         <v>137073740</v>
       </c>
       <c r="B155" t="n">
-        <v>102550</v>
+        <v>102562</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         <v>137073741</v>
       </c>
       <c r="B156" t="n">
-        <v>102550</v>
+        <v>102562</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17426,7 +17426,7 @@
         <v>137073742</v>
       </c>
       <c r="B157" t="n">
-        <v>102550</v>
+        <v>102562</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17528,7 +17528,7 @@
         <v>137078125</v>
       </c>
       <c r="B158" t="n">
-        <v>102550</v>
+        <v>102562</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17645,7 +17645,7 @@
         <v>137073768</v>
       </c>
       <c r="B159" t="n">
-        <v>106927</v>
+        <v>106939</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17747,7 +17747,7 @@
         <v>137073769</v>
       </c>
       <c r="B160" t="n">
-        <v>106927</v>
+        <v>106939</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19787,7 +19787,7 @@
         <v>137077942</v>
       </c>
       <c r="B180" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19904,7 +19904,7 @@
         <v>137078051</v>
       </c>
       <c r="B181" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20230,7 +20230,7 @@
         <v>136974125</v>
       </c>
       <c r="B184" t="n">
-        <v>87555</v>
+        <v>87566</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20337,7 +20337,7 @@
         <v>137076843</v>
       </c>
       <c r="B185" t="n">
-        <v>91643</v>
+        <v>91655</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20475,7 +20475,7 @@
         <v>137078162</v>
       </c>
       <c r="B186" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>

--- a/artfynd/A 19253-2026 artfynd.xlsx
+++ b/artfynd/A 19253-2026 artfynd.xlsx
@@ -1850,7 +1850,7 @@
         <v>137073743</v>
       </c>
       <c r="B13" t="n">
-        <v>97667</v>
+        <v>97668</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>137073744</v>
       </c>
       <c r="B14" t="n">
-        <v>97667</v>
+        <v>97668</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>136974111</v>
       </c>
       <c r="B16" t="n">
-        <v>85761</v>
+        <v>85762</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>137077964</v>
       </c>
       <c r="B17" t="n">
-        <v>87439</v>
+        <v>87440</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>137100339</v>
       </c>
       <c r="B18" t="n">
-        <v>87646</v>
+        <v>87647</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>137073745</v>
       </c>
       <c r="B23" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>137073746</v>
       </c>
       <c r="B24" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>137078005</v>
       </c>
       <c r="B25" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>137073793</v>
       </c>
       <c r="B27" t="n">
-        <v>92855</v>
+        <v>92856</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>137078053</v>
       </c>
       <c r="B32" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>137073749</v>
       </c>
       <c r="B35" t="n">
-        <v>96765</v>
+        <v>96766</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>137073750</v>
       </c>
       <c r="B36" t="n">
-        <v>96765</v>
+        <v>96766</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>137073751</v>
       </c>
       <c r="B37" t="n">
-        <v>96765</v>
+        <v>96766</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>136974096</v>
       </c>
       <c r="B43" t="n">
-        <v>91957</v>
+        <v>91958</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>137411764</v>
       </c>
       <c r="B44" t="n">
-        <v>87655</v>
+        <v>87656</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>136974097</v>
       </c>
       <c r="B45" t="n">
-        <v>87618</v>
+        <v>87619</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         <v>137077497</v>
       </c>
       <c r="B46" t="n">
-        <v>87618</v>
+        <v>87619</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>136974098</v>
       </c>
       <c r="B48" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         <v>137073761</v>
       </c>
       <c r="B49" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>137073762</v>
       </c>
       <c r="B50" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         <v>137073763</v>
       </c>
       <c r="B51" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>137073764</v>
       </c>
       <c r="B52" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         <v>137073765</v>
       </c>
       <c r="B53" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6351,7 +6351,7 @@
         <v>137073766</v>
       </c>
       <c r="B54" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>137073767</v>
       </c>
       <c r="B55" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         <v>137077917</v>
       </c>
       <c r="B56" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6679,7 +6679,7 @@
         <v>137078067</v>
       </c>
       <c r="B57" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6803,7 +6803,7 @@
         <v>137078239</v>
       </c>
       <c r="B58" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>137073794</v>
       </c>
       <c r="B59" t="n">
-        <v>92577</v>
+        <v>92578</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7681,7 +7681,7 @@
         <v>137073758</v>
       </c>
       <c r="B66" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>137073759</v>
       </c>
       <c r="B67" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         <v>137077540</v>
       </c>
       <c r="B69" t="n">
-        <v>89343</v>
+        <v>89344</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         <v>137073747</v>
       </c>
       <c r="B73" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8519,7 +8519,7 @@
         <v>137073748</v>
       </c>
       <c r="B74" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         <v>137078402</v>
       </c>
       <c r="B75" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         <v>137073773</v>
       </c>
       <c r="B83" t="n">
-        <v>91688</v>
+        <v>91689</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         <v>136974114</v>
       </c>
       <c r="B87" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         <v>136974115</v>
       </c>
       <c r="B88" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10103,7 +10103,7 @@
         <v>136974117</v>
       </c>
       <c r="B89" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10205,7 +10205,7 @@
         <v>136974118</v>
       </c>
       <c r="B90" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>137073777</v>
       </c>
       <c r="B91" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10409,7 +10409,7 @@
         <v>137073778</v>
       </c>
       <c r="B92" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
         <v>137073779</v>
       </c>
       <c r="B93" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>137073780</v>
       </c>
       <c r="B94" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>137073781</v>
       </c>
       <c r="B95" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10817,7 +10817,7 @@
         <v>137073782</v>
       </c>
       <c r="B96" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10919,7 +10919,7 @@
         <v>137073783</v>
       </c>
       <c r="B97" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11021,7 +11021,7 @@
         <v>137073784</v>
       </c>
       <c r="B98" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11123,7 +11123,7 @@
         <v>137073785</v>
       </c>
       <c r="B99" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11225,7 +11225,7 @@
         <v>137073786</v>
       </c>
       <c r="B100" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11327,7 +11327,7 @@
         <v>137073787</v>
       </c>
       <c r="B101" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         <v>137073788</v>
       </c>
       <c r="B102" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>137073789</v>
       </c>
       <c r="B103" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11633,7 +11633,7 @@
         <v>137077585</v>
       </c>
       <c r="B104" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11752,7 +11752,7 @@
         <v>137077941</v>
       </c>
       <c r="B105" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         <v>137078025</v>
       </c>
       <c r="B106" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>137078049</v>
       </c>
       <c r="B107" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12124,7 +12124,7 @@
         <v>137078081</v>
       </c>
       <c r="B108" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         <v>136974101</v>
       </c>
       <c r="B111" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12559,7 +12559,7 @@
         <v>136974102</v>
       </c>
       <c r="B112" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12661,7 +12661,7 @@
         <v>137073771</v>
       </c>
       <c r="B113" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>137073756</v>
       </c>
       <c r="B138" t="n">
-        <v>99408</v>
+        <v>99409</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15533,7 +15533,7 @@
         <v>137073757</v>
       </c>
       <c r="B139" t="n">
-        <v>99408</v>
+        <v>99409</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>137077977</v>
       </c>
       <c r="B140" t="n">
-        <v>99408</v>
+        <v>99409</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15964,7 +15964,7 @@
         <v>137077952</v>
       </c>
       <c r="B143" t="n">
-        <v>108470</v>
+        <v>108471</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16081,7 +16081,7 @@
         <v>137073795</v>
       </c>
       <c r="B144" t="n">
-        <v>107154</v>
+        <v>107155</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         <v>136974104</v>
       </c>
       <c r="B147" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17222,7 +17222,7 @@
         <v>137073740</v>
       </c>
       <c r="B155" t="n">
-        <v>102562</v>
+        <v>102563</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         <v>137073741</v>
       </c>
       <c r="B156" t="n">
-        <v>102562</v>
+        <v>102563</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17426,7 +17426,7 @@
         <v>137073742</v>
       </c>
       <c r="B157" t="n">
-        <v>102562</v>
+        <v>102563</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17528,7 +17528,7 @@
         <v>137078125</v>
       </c>
       <c r="B158" t="n">
-        <v>102562</v>
+        <v>102563</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17645,7 +17645,7 @@
         <v>137073768</v>
       </c>
       <c r="B159" t="n">
-        <v>106939</v>
+        <v>106940</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17747,7 +17747,7 @@
         <v>137073769</v>
       </c>
       <c r="B160" t="n">
-        <v>106939</v>
+        <v>106940</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19787,7 +19787,7 @@
         <v>137077942</v>
       </c>
       <c r="B180" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19904,7 +19904,7 @@
         <v>137078051</v>
       </c>
       <c r="B181" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20230,7 +20230,7 @@
         <v>136974125</v>
       </c>
       <c r="B184" t="n">
-        <v>87566</v>
+        <v>87567</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20337,7 +20337,7 @@
         <v>137076843</v>
       </c>
       <c r="B185" t="n">
-        <v>91655</v>
+        <v>91656</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20475,7 +20475,7 @@
         <v>137078162</v>
       </c>
       <c r="B186" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>

--- a/artfynd/A 19253-2026 artfynd.xlsx
+++ b/artfynd/A 19253-2026 artfynd.xlsx
@@ -1850,7 +1850,7 @@
         <v>137073743</v>
       </c>
       <c r="B13" t="n">
-        <v>97668</v>
+        <v>97671</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>137073744</v>
       </c>
       <c r="B14" t="n">
-        <v>97668</v>
+        <v>97671</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>136974111</v>
       </c>
       <c r="B16" t="n">
-        <v>85762</v>
+        <v>85765</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>137077964</v>
       </c>
       <c r="B17" t="n">
-        <v>87440</v>
+        <v>87443</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>137100339</v>
       </c>
       <c r="B18" t="n">
-        <v>87647</v>
+        <v>87650</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>137073745</v>
       </c>
       <c r="B23" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>137073746</v>
       </c>
       <c r="B24" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>137078005</v>
       </c>
       <c r="B25" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>137073793</v>
       </c>
       <c r="B27" t="n">
-        <v>92856</v>
+        <v>92859</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>137078053</v>
       </c>
       <c r="B32" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>137073749</v>
       </c>
       <c r="B35" t="n">
-        <v>96766</v>
+        <v>96769</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>137073750</v>
       </c>
       <c r="B36" t="n">
-        <v>96766</v>
+        <v>96769</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>137073751</v>
       </c>
       <c r="B37" t="n">
-        <v>96766</v>
+        <v>96769</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>136974096</v>
       </c>
       <c r="B43" t="n">
-        <v>91958</v>
+        <v>91961</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>137411764</v>
       </c>
       <c r="B44" t="n">
-        <v>87656</v>
+        <v>87659</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>136974097</v>
       </c>
       <c r="B45" t="n">
-        <v>87619</v>
+        <v>87622</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         <v>137077497</v>
       </c>
       <c r="B46" t="n">
-        <v>87619</v>
+        <v>87622</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>136974098</v>
       </c>
       <c r="B48" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         <v>137073761</v>
       </c>
       <c r="B49" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>137073762</v>
       </c>
       <c r="B50" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         <v>137073763</v>
       </c>
       <c r="B51" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>137073764</v>
       </c>
       <c r="B52" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         <v>137073765</v>
       </c>
       <c r="B53" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6351,7 +6351,7 @@
         <v>137073766</v>
       </c>
       <c r="B54" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>137073767</v>
       </c>
       <c r="B55" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         <v>137077917</v>
       </c>
       <c r="B56" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6679,7 +6679,7 @@
         <v>137078067</v>
       </c>
       <c r="B57" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6803,7 +6803,7 @@
         <v>137078239</v>
       </c>
       <c r="B58" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>137073794</v>
       </c>
       <c r="B59" t="n">
-        <v>92578</v>
+        <v>92581</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7681,7 +7681,7 @@
         <v>137073758</v>
       </c>
       <c r="B66" t="n">
-        <v>93494</v>
+        <v>93497</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>137073759</v>
       </c>
       <c r="B67" t="n">
-        <v>93494</v>
+        <v>93497</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         <v>137077540</v>
       </c>
       <c r="B69" t="n">
-        <v>89344</v>
+        <v>89347</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         <v>137073747</v>
       </c>
       <c r="B73" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8519,7 +8519,7 @@
         <v>137073748</v>
       </c>
       <c r="B74" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         <v>137078402</v>
       </c>
       <c r="B75" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         <v>137073773</v>
       </c>
       <c r="B83" t="n">
-        <v>91689</v>
+        <v>91692</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         <v>136974114</v>
       </c>
       <c r="B87" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         <v>136974115</v>
       </c>
       <c r="B88" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10103,7 +10103,7 @@
         <v>136974117</v>
       </c>
       <c r="B89" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10205,7 +10205,7 @@
         <v>136974118</v>
       </c>
       <c r="B90" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>137073777</v>
       </c>
       <c r="B91" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10409,7 +10409,7 @@
         <v>137073778</v>
       </c>
       <c r="B92" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
         <v>137073779</v>
       </c>
       <c r="B93" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>137073780</v>
       </c>
       <c r="B94" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>137073781</v>
       </c>
       <c r="B95" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10817,7 +10817,7 @@
         <v>137073782</v>
       </c>
       <c r="B96" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10919,7 +10919,7 @@
         <v>137073783</v>
       </c>
       <c r="B97" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11021,7 +11021,7 @@
         <v>137073784</v>
       </c>
       <c r="B98" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11123,7 +11123,7 @@
         <v>137073785</v>
       </c>
       <c r="B99" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11225,7 +11225,7 @@
         <v>137073786</v>
       </c>
       <c r="B100" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11327,7 +11327,7 @@
         <v>137073787</v>
       </c>
       <c r="B101" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         <v>137073788</v>
       </c>
       <c r="B102" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>137073789</v>
       </c>
       <c r="B103" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11633,7 +11633,7 @@
         <v>137077585</v>
       </c>
       <c r="B104" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11752,7 +11752,7 @@
         <v>137077941</v>
       </c>
       <c r="B105" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         <v>137078025</v>
       </c>
       <c r="B106" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>137078049</v>
       </c>
       <c r="B107" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12124,7 +12124,7 @@
         <v>137078081</v>
       </c>
       <c r="B108" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         <v>136974101</v>
       </c>
       <c r="B111" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12559,7 +12559,7 @@
         <v>136974102</v>
       </c>
       <c r="B112" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12661,7 +12661,7 @@
         <v>137073771</v>
       </c>
       <c r="B113" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>137073756</v>
       </c>
       <c r="B138" t="n">
-        <v>99409</v>
+        <v>99412</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15533,7 +15533,7 @@
         <v>137073757</v>
       </c>
       <c r="B139" t="n">
-        <v>99409</v>
+        <v>99412</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>137077977</v>
       </c>
       <c r="B140" t="n">
-        <v>99409</v>
+        <v>99412</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15964,7 +15964,7 @@
         <v>137077952</v>
       </c>
       <c r="B143" t="n">
-        <v>108471</v>
+        <v>108474</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16081,7 +16081,7 @@
         <v>137073795</v>
       </c>
       <c r="B144" t="n">
-        <v>107155</v>
+        <v>107158</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         <v>136974104</v>
       </c>
       <c r="B147" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17222,7 +17222,7 @@
         <v>137073740</v>
       </c>
       <c r="B155" t="n">
-        <v>102563</v>
+        <v>102566</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         <v>137073741</v>
       </c>
       <c r="B156" t="n">
-        <v>102563</v>
+        <v>102566</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17426,7 +17426,7 @@
         <v>137073742</v>
       </c>
       <c r="B157" t="n">
-        <v>102563</v>
+        <v>102566</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17528,7 +17528,7 @@
         <v>137078125</v>
       </c>
       <c r="B158" t="n">
-        <v>102563</v>
+        <v>102566</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17645,7 +17645,7 @@
         <v>137073768</v>
       </c>
       <c r="B159" t="n">
-        <v>106940</v>
+        <v>106943</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17747,7 +17747,7 @@
         <v>137073769</v>
       </c>
       <c r="B160" t="n">
-        <v>106940</v>
+        <v>106943</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19787,7 +19787,7 @@
         <v>137077942</v>
       </c>
       <c r="B180" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19904,7 +19904,7 @@
         <v>137078051</v>
       </c>
       <c r="B181" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20230,7 +20230,7 @@
         <v>136974125</v>
       </c>
       <c r="B184" t="n">
-        <v>87567</v>
+        <v>87570</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20337,7 +20337,7 @@
         <v>137076843</v>
       </c>
       <c r="B185" t="n">
-        <v>91656</v>
+        <v>91659</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20475,7 +20475,7 @@
         <v>137078162</v>
       </c>
       <c r="B186" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>

--- a/artfynd/A 19253-2026 artfynd.xlsx
+++ b/artfynd/A 19253-2026 artfynd.xlsx
@@ -2182,7 +2182,7 @@
         <v>136974111</v>
       </c>
       <c r="B16" t="n">
-        <v>85765</v>
+        <v>85766</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>136974096</v>
       </c>
       <c r="B43" t="n">
-        <v>91961</v>
+        <v>91962</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>136974097</v>
       </c>
       <c r="B45" t="n">
-        <v>87622</v>
+        <v>87623</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>136974098</v>
       </c>
       <c r="B48" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         <v>136974114</v>
       </c>
       <c r="B87" t="n">
-        <v>93521</v>
+        <v>93522</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         <v>136974115</v>
       </c>
       <c r="B88" t="n">
-        <v>93521</v>
+        <v>93522</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10103,7 +10103,7 @@
         <v>136974117</v>
       </c>
       <c r="B89" t="n">
-        <v>93521</v>
+        <v>93522</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10205,7 +10205,7 @@
         <v>136974118</v>
       </c>
       <c r="B90" t="n">
-        <v>93521</v>
+        <v>93522</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         <v>136974101</v>
       </c>
       <c r="B111" t="n">
-        <v>93523</v>
+        <v>93524</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12559,7 +12559,7 @@
         <v>136974102</v>
       </c>
       <c r="B112" t="n">
-        <v>93523</v>
+        <v>93524</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         <v>136974104</v>
       </c>
       <c r="B147" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -20230,7 +20230,7 @@
         <v>136974125</v>
       </c>
       <c r="B184" t="n">
-        <v>87570</v>
+        <v>87571</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>

--- a/artfynd/A 19253-2026 artfynd.xlsx
+++ b/artfynd/A 19253-2026 artfynd.xlsx
@@ -1850,7 +1850,7 @@
         <v>137073743</v>
       </c>
       <c r="B13" t="n">
-        <v>97671</v>
+        <v>97675</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>137073744</v>
       </c>
       <c r="B14" t="n">
-        <v>97671</v>
+        <v>97675</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>136974111</v>
       </c>
       <c r="B16" t="n">
-        <v>85766</v>
+        <v>85769</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>137077964</v>
       </c>
       <c r="B17" t="n">
-        <v>87443</v>
+        <v>87447</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>137100339</v>
       </c>
       <c r="B18" t="n">
-        <v>87650</v>
+        <v>87654</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>137073745</v>
       </c>
       <c r="B23" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>137073746</v>
       </c>
       <c r="B24" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>137078005</v>
       </c>
       <c r="B25" t="n">
-        <v>92617</v>
+        <v>92621</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>137073793</v>
       </c>
       <c r="B27" t="n">
-        <v>92859</v>
+        <v>92863</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>137078053</v>
       </c>
       <c r="B32" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>137073749</v>
       </c>
       <c r="B35" t="n">
-        <v>96769</v>
+        <v>96773</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>137073750</v>
       </c>
       <c r="B36" t="n">
-        <v>96769</v>
+        <v>96773</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>137073751</v>
       </c>
       <c r="B37" t="n">
-        <v>96769</v>
+        <v>96773</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>136974096</v>
       </c>
       <c r="B43" t="n">
-        <v>91962</v>
+        <v>91965</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>137411764</v>
       </c>
       <c r="B44" t="n">
-        <v>87659</v>
+        <v>87663</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>136974097</v>
       </c>
       <c r="B45" t="n">
-        <v>87623</v>
+        <v>87626</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         <v>137077497</v>
       </c>
       <c r="B46" t="n">
-        <v>87622</v>
+        <v>87626</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>136974098</v>
       </c>
       <c r="B48" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         <v>137073761</v>
       </c>
       <c r="B49" t="n">
-        <v>87393</v>
+        <v>87397</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>137073762</v>
       </c>
       <c r="B50" t="n">
-        <v>87393</v>
+        <v>87397</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         <v>137073763</v>
       </c>
       <c r="B51" t="n">
-        <v>87393</v>
+        <v>87397</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>137073764</v>
       </c>
       <c r="B52" t="n">
-        <v>87393</v>
+        <v>87397</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         <v>137073765</v>
       </c>
       <c r="B53" t="n">
-        <v>87393</v>
+        <v>87397</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6351,7 +6351,7 @@
         <v>137073766</v>
       </c>
       <c r="B54" t="n">
-        <v>87393</v>
+        <v>87397</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>137073767</v>
       </c>
       <c r="B55" t="n">
-        <v>87393</v>
+        <v>87397</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         <v>137077917</v>
       </c>
       <c r="B56" t="n">
-        <v>87393</v>
+        <v>87397</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6679,7 +6679,7 @@
         <v>137078067</v>
       </c>
       <c r="B57" t="n">
-        <v>87393</v>
+        <v>87397</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6803,7 +6803,7 @@
         <v>137078239</v>
       </c>
       <c r="B58" t="n">
-        <v>87393</v>
+        <v>87397</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>137073794</v>
       </c>
       <c r="B59" t="n">
-        <v>92581</v>
+        <v>92585</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7681,7 +7681,7 @@
         <v>137073758</v>
       </c>
       <c r="B66" t="n">
-        <v>93497</v>
+        <v>93501</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>137073759</v>
       </c>
       <c r="B67" t="n">
-        <v>93497</v>
+        <v>93501</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         <v>137077540</v>
       </c>
       <c r="B69" t="n">
-        <v>89347</v>
+        <v>89351</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         <v>137073747</v>
       </c>
       <c r="B73" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8519,7 +8519,7 @@
         <v>137073748</v>
       </c>
       <c r="B74" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         <v>137078402</v>
       </c>
       <c r="B75" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         <v>137073773</v>
       </c>
       <c r="B83" t="n">
-        <v>91692</v>
+        <v>91696</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         <v>136974114</v>
       </c>
       <c r="B87" t="n">
-        <v>93522</v>
+        <v>93525</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         <v>136974115</v>
       </c>
       <c r="B88" t="n">
-        <v>93522</v>
+        <v>93525</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10103,7 +10103,7 @@
         <v>136974117</v>
       </c>
       <c r="B89" t="n">
-        <v>93522</v>
+        <v>93525</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10205,7 +10205,7 @@
         <v>136974118</v>
       </c>
       <c r="B90" t="n">
-        <v>93522</v>
+        <v>93525</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>137073777</v>
       </c>
       <c r="B91" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10409,7 +10409,7 @@
         <v>137073778</v>
       </c>
       <c r="B92" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
         <v>137073779</v>
       </c>
       <c r="B93" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>137073780</v>
       </c>
       <c r="B94" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>137073781</v>
       </c>
       <c r="B95" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10817,7 +10817,7 @@
         <v>137073782</v>
       </c>
       <c r="B96" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10919,7 +10919,7 @@
         <v>137073783</v>
       </c>
       <c r="B97" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11021,7 +11021,7 @@
         <v>137073784</v>
       </c>
       <c r="B98" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11123,7 +11123,7 @@
         <v>137073785</v>
       </c>
       <c r="B99" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11225,7 +11225,7 @@
         <v>137073786</v>
       </c>
       <c r="B100" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11327,7 +11327,7 @@
         <v>137073787</v>
       </c>
       <c r="B101" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         <v>137073788</v>
       </c>
       <c r="B102" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>137073789</v>
       </c>
       <c r="B103" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11633,7 +11633,7 @@
         <v>137077585</v>
       </c>
       <c r="B104" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11752,7 +11752,7 @@
         <v>137077941</v>
       </c>
       <c r="B105" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         <v>137078025</v>
       </c>
       <c r="B106" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>137078049</v>
       </c>
       <c r="B107" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12124,7 +12124,7 @@
         <v>137078081</v>
       </c>
       <c r="B108" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         <v>136974101</v>
       </c>
       <c r="B111" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12559,7 +12559,7 @@
         <v>136974102</v>
       </c>
       <c r="B112" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12661,7 +12661,7 @@
         <v>137073771</v>
       </c>
       <c r="B113" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>137073756</v>
       </c>
       <c r="B138" t="n">
-        <v>99412</v>
+        <v>99416</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15533,7 +15533,7 @@
         <v>137073757</v>
       </c>
       <c r="B139" t="n">
-        <v>99412</v>
+        <v>99416</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>137077977</v>
       </c>
       <c r="B140" t="n">
-        <v>99412</v>
+        <v>99416</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15964,7 +15964,7 @@
         <v>137077952</v>
       </c>
       <c r="B143" t="n">
-        <v>108474</v>
+        <v>108480</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16081,7 +16081,7 @@
         <v>137073795</v>
       </c>
       <c r="B144" t="n">
-        <v>107158</v>
+        <v>107164</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         <v>136974104</v>
       </c>
       <c r="B147" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17222,7 +17222,7 @@
         <v>137073740</v>
       </c>
       <c r="B155" t="n">
-        <v>102566</v>
+        <v>102570</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         <v>137073741</v>
       </c>
       <c r="B156" t="n">
-        <v>102566</v>
+        <v>102570</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17426,7 +17426,7 @@
         <v>137073742</v>
       </c>
       <c r="B157" t="n">
-        <v>102566</v>
+        <v>102570</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17528,7 +17528,7 @@
         <v>137078125</v>
       </c>
       <c r="B158" t="n">
-        <v>102566</v>
+        <v>102570</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17645,7 +17645,7 @@
         <v>137073768</v>
       </c>
       <c r="B159" t="n">
-        <v>106943</v>
+        <v>106949</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17747,7 +17747,7 @@
         <v>137073769</v>
       </c>
       <c r="B160" t="n">
-        <v>106943</v>
+        <v>106949</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19787,7 +19787,7 @@
         <v>137077942</v>
       </c>
       <c r="B180" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19904,7 +19904,7 @@
         <v>137078051</v>
       </c>
       <c r="B181" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20230,7 +20230,7 @@
         <v>136974125</v>
       </c>
       <c r="B184" t="n">
-        <v>87571</v>
+        <v>87574</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20337,7 +20337,7 @@
         <v>137076843</v>
       </c>
       <c r="B185" t="n">
-        <v>91659</v>
+        <v>91663</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20475,7 +20475,7 @@
         <v>137078162</v>
       </c>
       <c r="B186" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
